--- a/assignments/qr/excels/remarks.xlsx
+++ b/assignments/qr/excels/remarks.xlsx
@@ -3212,7 +3212,7 @@
       </c>
       <c r="R25" s="7" t="inlineStr">
         <is>
-          <t>010</t>
+          <t>011</t>
         </is>
       </c>
     </row>
@@ -6418,7 +6418,7 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>010</t>
+          <t>011</t>
         </is>
       </c>
       <c r="U90" t="inlineStr">

--- a/assignments/qr/excels/remarks.xlsx
+++ b/assignments/qr/excels/remarks.xlsx
@@ -274,7 +274,7 @@
     </comment>
     <comment ref="N9" authorId="0" shapeId="0">
       <text>
-        <t>-place (00:04:49), -place (00:05:00), -place (00:05:04), +const (00:00:00), +mapContainer (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +mapContainer (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +btn (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +btn (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +marker (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +marker (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +data (00:00:00), +if (00:00:00), +( (00:00:00), +data (00:00:00), +. (00:00:00), +top (00:00:00), +&amp; (00:00:00), +&amp; (00:00:00), +data (00:00:00), +. (00:00:00), +left (00:00:00), +) (00:00:00), +{ (00:00:00), +data (00:00:00), +data (00:00:00), +} (00:00:00), +if (00:00:00), +( (00:00:00), +data (00:00:00), +. (00:00:00), +name (00:00:00), +) (00:00:00), +{ (00:00:00), +showProduct (00:00:00), +( (00:00:00), +text (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +function (00:00:00), +showProduct (00:00:00), +( (00:00:00), +data (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +obj (00:00:00), += (00:00:00), +JSON (00:00:00), +. (00:00:00), +parse (00:00:00), +( (00:00:00), +data (00:00:00), +) (00:00:00), +; (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +name (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +Name (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +( (00:00:00), +obj (00:00:00), +. (00:00:00), +name (00:00:00), +| (00:00:00), +| (00:00:00), +" (00:00:00), +Yes (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +stock (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +In (00:00:00), +store (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +( (00:00:00), +obj (00:00:00), +. (00:00:00), +in (00:00:00), +_ (00:00:00), +store (00:00:00), +! (00:00:00), += (00:00:00), += (00:00:00), +undefined (00:00:00), +? (00:00:00), +obj (00:00:00), +. (00:00:00), +in (00:00:00), +_ (00:00:00), +store (00:00:00), +: (00:00:00), +" (00:00:00), +No (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +price (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +Price (00:00:00), +: (00:00:00), +€ (00:00:00), +" (00:00:00), ++ (00:00:00), +( (00:00:00), +obj (00:00:00), +. (00:00:00), +price (00:00:00), +! (00:00:00), += (00:00:00), += (00:00:00), +undefined (00:00:00), +? (00:00:00), +obj (00:00:00), +. (00:00:00), +price (00:00:00), +: (00:00:00), +" (00:00:00), +No (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+        <t>-place (00:04:49) ~0.20, -place (00:05:00) ~0.20, -place (00:05:04) ~0.20, +const (00:00:00), +mapContainer (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +mapContainer (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +btn (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +btn (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +marker (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +marker (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +data (00:00:00), +if (00:00:00), +( (00:00:00), +data (00:00:00), +. (00:00:00), +top (00:00:00), +&amp; (00:00:00), +&amp; (00:00:00), +data (00:00:00), +. (00:00:00), +left (00:00:00), +) (00:00:00), +{ (00:00:00), +data (00:00:00), +data (00:00:00), +} (00:00:00), +if (00:00:00), +( (00:00:00), +data (00:00:00), +. (00:00:00), +name (00:00:00), +) (00:00:00), +{ (00:00:00), +showProduct (00:00:00), +( (00:00:00), +text (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +function (00:00:00), +showProduct (00:00:00), +( (00:00:00), +data (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +obj (00:00:00), += (00:00:00), +JSON (00:00:00), +. (00:00:00), +parse (00:00:00), +( (00:00:00), +data (00:00:00), +) (00:00:00), +; (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +name (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +Name (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +( (00:00:00), +obj (00:00:00), +. (00:00:00), +name (00:00:00), +| (00:00:00), +| (00:00:00), +" (00:00:00), +Yes (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +stock (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +In (00:00:00), +store (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +( (00:00:00), +obj (00:00:00), +. (00:00:00), +in (00:00:00), +_ (00:00:00), +store (00:00:00), +! (00:00:00), += (00:00:00), += (00:00:00), +undefined (00:00:00), +? (00:00:00), +obj (00:00:00), +. (00:00:00), +in (00:00:00), +_ (00:00:00), +store (00:00:00), +: (00:00:00), +" (00:00:00), +No (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +price (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +Price (00:00:00), +: (00:00:00), +€ (00:00:00), +" (00:00:00), ++ (00:00:00), +( (00:00:00), +obj (00:00:00), +. (00:00:00), +price (00:00:00), +! (00:00:00), += (00:00:00), += (00:00:00), +undefined (00:00:00), +? (00:00:00), +obj (00:00:00), +. (00:00:00), +price (00:00:00), +: (00:00:00), +" (00:00:00), +No (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00)</t>
       </text>
     </comment>
     <comment ref="P9" authorId="0" shapeId="0">
@@ -309,7 +309,7 @@
     </comment>
     <comment ref="N12" authorId="0" shapeId="0">
       <text>
-        <t>-place (00:04:49), -showMarkerAt (00:04:58), -( (00:04:59), -place (00:05:00), -. (00:05:01), -top (00:05:02), -, (00:05:03), -place (00:05:04), -. (00:05:05), -left (00:05:06), -) (00:05:07), -; (00:05:08), +item (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +itemName (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Name (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +name (00:00:00), +; (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +itemStatus (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +In (00:00:00), +store (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +( (00:00:00), +item (00:00:00), +. (00:00:00), +in (00:00:00), +_ (00:00:00), +store (00:00:00), +? (00:00:00), +" (00:00:00), +Yes (00:00:00), +" (00:00:00), +: (00:00:00), +" (00:00:00), +No (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +itemPrice (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Price (00:00:00), +: (00:00:00), +€ (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +price (00:00:00), +; (00:00:00)</t>
+        <t>-place (00:04:49) ~0.00, -showMarkerAt (00:04:58), -( (00:04:59), -place (00:05:00), -. (00:05:01), -top (00:05:02), -, (00:05:03), -place (00:05:04), -. (00:05:05), -left (00:05:06), -) (00:05:07), -; (00:05:08), +item (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +itemName (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Name (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +name (00:00:00), +; (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +itemStatus (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +In (00:00:00), +store (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +( (00:00:00), +item (00:00:00), +. (00:00:00), +in (00:00:00), +_ (00:00:00), +store (00:00:00), +? (00:00:00), +" (00:00:00), +Yes (00:00:00), +" (00:00:00), +: (00:00:00), +" (00:00:00), +No (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +itemPrice (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Price (00:00:00), +: (00:00:00), +€ (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +price (00:00:00), +; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="P12" authorId="0" shapeId="0">
@@ -399,7 +399,7 @@
     </comment>
     <comment ref="J21" authorId="0" shapeId="0">
       <text>
-        <t>-SCAN (00:08:43), +Scan (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +inventory (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +style (00:00:00), += (00:00:00), +" (00:00:00), +margin (00:00:00), +- (00:00:00), +bottom (00:00:00), +: (00:00:00), +3px (00:00:00), +; (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Stock (00:00:00), +Information (00:00:00), +: (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +name (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +price (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +inStock (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
+        <t>-SCAN (00:08:43) ~0.25, +Scan (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +inventory (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +style (00:00:00), += (00:00:00), +" (00:00:00), +margin (00:00:00), +- (00:00:00), +bottom (00:00:00), +: (00:00:00), +3px (00:00:00), +; (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Stock (00:00:00), +Information (00:00:00), +: (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +name (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +price (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +inStock (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="L21" authorId="0" shapeId="0">
@@ -409,7 +409,7 @@
     </comment>
     <comment ref="N21" authorId="0" shapeId="0">
       <text>
-        <t>-CANCEL (00:03:43), -SCAN (00:04:08), +const (00:00:00), +inventory (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +inventory (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +mapContainer (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +mapContainer (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +btn (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +btn (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +marker (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +marker (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +inventory (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +display (00:00:00), += (00:00:00), +" (00:00:00), +none (00:00:00), +" (00:00:00), +; (00:00:00), +Cancel (00:00:00), +inventory (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +display (00:00:00), += (00:00:00), +" (00:00:00), +flex (00:00:00), +" (00:00:00), +; (00:00:00), +Scan (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +text (00:00:00), +) (00:00:00), +; (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +name (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +' (00:00:00), +Item (00:00:00), +name (00:00:00), +: (00:00:00), +' (00:00:00), ++ (00:00:00), +place (00:00:00), +. (00:00:00), +name (00:00:00), +; (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +price (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +innerHTML (00:00:00), += (00:00:00), +' (00:00:00), +Price (00:00:00), +( (00:00:00), +&amp; (00:00:00), +# (00:00:00), +x20AC (00:00:00), +) (00:00:00), +: (00:00:00), +' (00:00:00), ++ (00:00:00), +place (00:00:00), +. (00:00:00), +price (00:00:00), +; (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +inStock (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +' (00:00:00), +In (00:00:00), +Stock (00:00:00), +: (00:00:00), +' (00:00:00), ++ (00:00:00), +Number (00:00:00), +( (00:00:00), +place (00:00:00), +. (00:00:00), +inStock (00:00:00), +) (00:00:00), +; (00:00:00)</t>
+        <t>-CANCEL (00:03:43) ~0.17, -SCAN (00:04:08) ~0.25, +const (00:00:00), +inventory (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +inventory (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +mapContainer (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +mapContainer (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +btn (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +btn (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +marker (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +marker (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +inventory (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +display (00:00:00), += (00:00:00), +" (00:00:00), +none (00:00:00), +" (00:00:00), +; (00:00:00), +Cancel (00:00:00), +inventory (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +display (00:00:00), += (00:00:00), +" (00:00:00), +flex (00:00:00), +" (00:00:00), +; (00:00:00), +Scan (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +text (00:00:00), +) (00:00:00), +; (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +name (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +' (00:00:00), +Item (00:00:00), +name (00:00:00), +: (00:00:00), +' (00:00:00), ++ (00:00:00), +place (00:00:00), +. (00:00:00), +name (00:00:00), +; (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +price (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +innerHTML (00:00:00), += (00:00:00), +' (00:00:00), +Price (00:00:00), +( (00:00:00), +&amp; (00:00:00), +# (00:00:00), +x20AC (00:00:00), +) (00:00:00), +: (00:00:00), +' (00:00:00), ++ (00:00:00), +place (00:00:00), +. (00:00:00), +price (00:00:00), +; (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +inStock (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +' (00:00:00), +In (00:00:00), +Stock (00:00:00), +: (00:00:00), +' (00:00:00), ++ (00:00:00), +Number (00:00:00), +( (00:00:00), +place (00:00:00), +. (00:00:00), +inStock (00:00:00), +) (00:00:00), +; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="D24" authorId="0" shapeId="0">
@@ -429,7 +429,7 @@
     </comment>
     <comment ref="J24" authorId="0" shapeId="0">
       <text>
-        <t>-onclick (00:08:35), +onClick (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +paragraphContainer (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
+        <t>-onclick (00:08:35) ~0.86, +onClick (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +paragraphContainer (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="L24" authorId="0" shapeId="0">
@@ -469,7 +469,7 @@
     </comment>
     <comment ref="N25" authorId="0" shapeId="0">
       <text>
-        <t>-place (00:04:49), -place (00:05:00), -place (00:05:04), +data (00:00:00), +if (00:00:00), +( (00:00:00), +data (00:00:00), +. (00:00:00), +top (00:00:00), +&amp; (00:00:00), +&amp; (00:00:00), +data (00:00:00), +. (00:00:00), +left (00:00:00), +) (00:00:00), +{ (00:00:00), +data (00:00:00), +data (00:00:00), +} (00:00:00), +if (00:00:00), +( (00:00:00), +data (00:00:00), +. (00:00:00), +name (00:00:00), +) (00:00:00), +{ (00:00:00), +showInventory (00:00:00), +( (00:00:00), +data (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +function (00:00:00), +showInventory (00:00:00), +( (00:00:00), +data (00:00:00), +) (00:00:00), +{ (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +itemName (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Name (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +data (00:00:00), +. (00:00:00), +name (00:00:00), +; (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +itemStore (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +In (00:00:00), +store (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +( (00:00:00), +data (00:00:00), +. (00:00:00), +in (00:00:00), +_ (00:00:00), +store (00:00:00), +? (00:00:00), +" (00:00:00), +Yes (00:00:00), +" (00:00:00), +: (00:00:00), +" (00:00:00), +No (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +itemPrice (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Price (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +data (00:00:00), +. (00:00:00), +price (00:00:00), ++ (00:00:00), +" (00:00:00), +€ (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+        <t>-place (00:04:49) ~0.20, -place (00:05:00) ~0.20, -place (00:05:04) ~0.20, +data (00:00:00), +if (00:00:00), +( (00:00:00), +data (00:00:00), +. (00:00:00), +top (00:00:00), +&amp; (00:00:00), +&amp; (00:00:00), +data (00:00:00), +. (00:00:00), +left (00:00:00), +) (00:00:00), +{ (00:00:00), +data (00:00:00), +data (00:00:00), +} (00:00:00), +if (00:00:00), +( (00:00:00), +data (00:00:00), +. (00:00:00), +name (00:00:00), +) (00:00:00), +{ (00:00:00), +showInventory (00:00:00), +( (00:00:00), +data (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +function (00:00:00), +showInventory (00:00:00), +( (00:00:00), +data (00:00:00), +) (00:00:00), +{ (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +itemName (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Name (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +data (00:00:00), +. (00:00:00), +name (00:00:00), +; (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +itemStore (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +In (00:00:00), +store (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +( (00:00:00), +data (00:00:00), +. (00:00:00), +in (00:00:00), +_ (00:00:00), +store (00:00:00), +? (00:00:00), +" (00:00:00), +Yes (00:00:00), +" (00:00:00), +: (00:00:00), +" (00:00:00), +No (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +itemPrice (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Price (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +data (00:00:00), +. (00:00:00), +price (00:00:00), ++ (00:00:00), +" (00:00:00), +€ (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00)</t>
       </text>
     </comment>
     <comment ref="P25" authorId="0" shapeId="0">
@@ -494,7 +494,7 @@
     </comment>
     <comment ref="J28" authorId="0" shapeId="0">
       <text>
-        <t>-Positioning (00:07:06), -Positioning (00:07:38), -&lt; (00:07:43), -div (00:07:44), -id (00:07:45), -= (00:07:46), -" (00:07:47), -mapContainer (00:07:48), -" (00:07:49), -&gt; (00:07:50), -&lt; (00:07:51), -img (00:07:52), -src (00:07:53), -= (00:07:54), -" (00:07:55), -map (00:07:56), -. (00:07:57), -png (00:07:58), -" (00:07:59), -id (00:08:00), -= (00:08:01), -" (00:08:02), -map (00:08:03), -" (00:08:04), -alt (00:08:05), -= (00:08:06), -" (00:08:07), -map (00:08:08), -" (00:08:09), -/ (00:08:10), -&gt; (00:08:11), -&lt; (00:08:12), -div (00:08:13), -id (00:08:14), -= (00:08:15), -" (00:08:16), -marker (00:08:17), -" (00:08:18), -&gt; (00:08:19), -&lt; (00:08:20), -/ (00:08:21), -div (00:08:22), -&gt; (00:08:23), -&lt; (00:08:24), -/ (00:08:25), -div (00:08:26), -&gt; (00:08:27), -btn (00:08:33), -onclick (00:08:35), -= (00:08:36), -" (00:08:37), -toggleScanner (00:08:38), -( (00:08:39), -) (00:08:40), -" (00:08:41), -SCAN (00:08:43), -&lt; (00:08:48), -div (00:08:49), -id (00:08:50), -= (00:08:51), -" (00:08:52), -camera (00:08:53), -" (00:08:54), -&gt; (00:08:55), -&lt; (00:08:56), -/ (00:08:57), -div (00:08:58), -&gt; (00:08:59), -type (00:09:17), -= (00:09:18), -" (00:09:19), -text (00:09:20), -/ (00:09:21), -javascript (00:09:22), -" (00:09:23), +Inventory (00:00:00), +Scanner (00:00:00), +Inventory (00:00:00), +Scanner (00:00:00), +scanBtn (00:00:00), +Scan (00:00:00), +QR (00:00:00), +Code (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +reader (00:00:00), +" (00:00:00), +style (00:00:00), += (00:00:00), +" (00:00:00), +width (00:00:00), +: (00:00:00), +300px (00:00:00), +; (00:00:00), +margin (00:00:00), +- (00:00:00), +top (00:00:00), +: (00:00:00), +20px (00:00:00), +; (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +h2 (00:00:00), +&gt; (00:00:00), +Item (00:00:00), +Information (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +h2 (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +name (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +store (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +price (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00)</t>
+        <t>-Positioning (00:07:06) ~0.09, -Positioning (00:07:38) ~0.09, -&lt; (00:07:43), -div (00:07:44), -id (00:07:45), -= (00:07:46), -" (00:07:47), -mapContainer (00:07:48), -" (00:07:49), -&gt; (00:07:50), -&lt; (00:07:51), -img (00:07:52), -src (00:07:53), -= (00:07:54), -" (00:07:55), -map (00:07:56), -. (00:07:57), -png (00:07:58), -" (00:07:59), -id (00:08:00), -= (00:08:01), -" (00:08:02), -map (00:08:03), -" (00:08:04), -alt (00:08:05), -= (00:08:06), -" (00:08:07), -map (00:08:08), -" (00:08:09), -/ (00:08:10), -&gt; (00:08:11), -&lt; (00:08:12), -div (00:08:13), -id (00:08:14), -= (00:08:15), -" (00:08:16), -marker (00:08:17), -" (00:08:18), -&gt; (00:08:19), -&lt; (00:08:20), -/ (00:08:21), -div (00:08:22), -&gt; (00:08:23), -&lt; (00:08:24), -/ (00:08:25), -div (00:08:26), -&gt; (00:08:27), -btn (00:08:33) ~0.29, -onclick (00:08:35), -= (00:08:36), -" (00:08:37), -toggleScanner (00:08:38), -( (00:08:39), -) (00:08:40), -" (00:08:41), -SCAN (00:08:43) ~0.25, -&lt; (00:08:48), -div (00:08:49), -id (00:08:50), -= (00:08:51), -" (00:08:52), -camera (00:08:53), -" (00:08:54), -&gt; (00:08:55), -&lt; (00:08:56), -/ (00:08:57), -div (00:08:58), -&gt; (00:08:59), -type (00:09:17), -= (00:09:18), -" (00:09:19), -text (00:09:20), -/ (00:09:21), -javascript (00:09:22), -" (00:09:23), +Inventory (00:00:00), +Scanner (00:00:00), +Inventory (00:00:00), +Scanner (00:00:00), +scanBtn (00:00:00), +Scan (00:00:00), +QR (00:00:00), +Code (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +reader (00:00:00), +" (00:00:00), +style (00:00:00), += (00:00:00), +" (00:00:00), +width (00:00:00), +: (00:00:00), +300px (00:00:00), +; (00:00:00), +margin (00:00:00), +- (00:00:00), +top (00:00:00), +: (00:00:00), +20px (00:00:00), +; (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +h2 (00:00:00), +&gt; (00:00:00), +Item (00:00:00), +Information (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +h2 (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +name (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +store (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +price (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="L28" authorId="0" shapeId="0">
@@ -559,7 +559,7 @@
     </comment>
     <comment ref="J31" authorId="0" shapeId="0">
       <text>
-        <t>-QR (00:07:05), -Positioning (00:07:38), +Qr (00:00:00), +Positionining (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +inventoryBox (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +h2 (00:00:00), +&gt; (00:00:00), +Inventory (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +h2 (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemName (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemStock (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemPrice (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
+        <t>-QR (00:07:05) ~0.50, -Positioning (00:07:38) ~0.85, +Qr (00:00:00), +Positionining (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +inventoryBox (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +h2 (00:00:00), +&gt; (00:00:00), +Inventory (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +h2 (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemName (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemStock (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemPrice (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="L31" authorId="0" shapeId="0">
@@ -589,17 +589,17 @@
     </comment>
     <comment ref="J36" authorId="0" shapeId="0">
       <text>
-        <t>-Positioning (00:07:06), -Positioning (00:07:38), +Inventory (00:00:00), +System (00:00:00), +Inventory (00:00:00), +System (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +inventoryInfo (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemName (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +inStore (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +price (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
+        <t>-Positioning (00:07:06) ~0.09, -Positioning (00:07:38) ~0.09, +Inventory (00:00:00), +System (00:00:00), +Inventory (00:00:00), +System (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +inventoryInfo (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemName (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +inStore (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +price (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="L36" authorId="0" shapeId="0">
       <text>
-        <t>-# (00:00:07), -280 (00:00:08), +red (00:00:00), +margin (00:00:00), +: (00:00:00), +10px (00:00:00), +0 (00:00:00), +; (00:00:00), +# (00:00:00), +btn (00:00:00), +{ (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +var (00:00:00), +( (00:00:00), +- (00:00:00), +- (00:00:00), +theme (00:00:00), +) (00:00:00), +; (00:00:00), +color (00:00:00), +: (00:00:00), +white (00:00:00), +; (00:00:00), +border (00:00:00), +: (00:00:00), +none (00:00:00), +; (00:00:00), +padding (00:00:00), +: (00:00:00), +12px (00:00:00), +24px (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +16px (00:00:00), +; (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +8px (00:00:00), +; (00:00:00), +cursor (00:00:00), +: (00:00:00), +pointer (00:00:00), +; (00:00:00), +transition (00:00:00), +: (00:00:00), +all (00:00:00), +0 (00:00:00), +. (00:00:00), +3s (00:00:00), +ease (00:00:00), +; (00:00:00), +box (00:00:00), +- (00:00:00), +shadow (00:00:00), +: (00:00:00), +0 (00:00:00), +4px (00:00:00), +6px (00:00:00), +rgba (00:00:00), +( (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +. (00:00:00), +2 (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +btn (00:00:00), +: (00:00:00), +hover (00:00:00), +{ (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +white (00:00:00), +; (00:00:00), +color (00:00:00), +: (00:00:00), +var (00:00:00), +( (00:00:00), +- (00:00:00), +- (00:00:00), +theme (00:00:00), +) (00:00:00), +; (00:00:00), +box (00:00:00), +- (00:00:00), +shadow (00:00:00), +: (00:00:00), +0 (00:00:00), +6px (00:00:00), +10px (00:00:00), +rgba (00:00:00), +( (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +. (00:00:00), +3 (00:00:00), +) (00:00:00), +; (00:00:00), +transform (00:00:00), +: (00:00:00), +scale (00:00:00), +( (00:00:00), +1 (00:00:00), +. (00:00:00), +05 (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +inventoryInfo (00:00:00), +{ (00:00:00), +margin (00:00:00), +- (00:00:00), +top (00:00:00), +: (00:00:00), +20px (00:00:00), +; (00:00:00), +text (00:00:00), +- (00:00:00), +align (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +inventoryInfo (00:00:00), +p (00:00:00), +{ (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +18px (00:00:00), +; (00:00:00), +margin (00:00:00), +: (00:00:00), +5px (00:00:00), +0 (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+        <t>-# (00:00:07), -280 (00:00:08) ~0.00, +red (00:00:00), +margin (00:00:00), +: (00:00:00), +10px (00:00:00), +0 (00:00:00), +; (00:00:00), +# (00:00:00), +btn (00:00:00), +{ (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +var (00:00:00), +( (00:00:00), +- (00:00:00), +- (00:00:00), +theme (00:00:00), +) (00:00:00), +; (00:00:00), +color (00:00:00), +: (00:00:00), +white (00:00:00), +; (00:00:00), +border (00:00:00), +: (00:00:00), +none (00:00:00), +; (00:00:00), +padding (00:00:00), +: (00:00:00), +12px (00:00:00), +24px (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +16px (00:00:00), +; (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +8px (00:00:00), +; (00:00:00), +cursor (00:00:00), +: (00:00:00), +pointer (00:00:00), +; (00:00:00), +transition (00:00:00), +: (00:00:00), +all (00:00:00), +0 (00:00:00), +. (00:00:00), +3s (00:00:00), +ease (00:00:00), +; (00:00:00), +box (00:00:00), +- (00:00:00), +shadow (00:00:00), +: (00:00:00), +0 (00:00:00), +4px (00:00:00), +6px (00:00:00), +rgba (00:00:00), +( (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +. (00:00:00), +2 (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +btn (00:00:00), +: (00:00:00), +hover (00:00:00), +{ (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +white (00:00:00), +; (00:00:00), +color (00:00:00), +: (00:00:00), +var (00:00:00), +( (00:00:00), +- (00:00:00), +- (00:00:00), +theme (00:00:00), +) (00:00:00), +; (00:00:00), +box (00:00:00), +- (00:00:00), +shadow (00:00:00), +: (00:00:00), +0 (00:00:00), +6px (00:00:00), +10px (00:00:00), +rgba (00:00:00), +( (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +. (00:00:00), +3 (00:00:00), +) (00:00:00), +; (00:00:00), +transform (00:00:00), +: (00:00:00), +scale (00:00:00), +( (00:00:00), +1 (00:00:00), +. (00:00:00), +05 (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +inventoryInfo (00:00:00), +{ (00:00:00), +margin (00:00:00), +- (00:00:00), +top (00:00:00), +: (00:00:00), +20px (00:00:00), +; (00:00:00), +text (00:00:00), +- (00:00:00), +align (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +inventoryInfo (00:00:00), +p (00:00:00), +{ (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +18px (00:00:00), +; (00:00:00), +margin (00:00:00), +: (00:00:00), +5px (00:00:00), +0 (00:00:00), +; (00:00:00), +} (00:00:00)</t>
       </text>
     </comment>
     <comment ref="N36" authorId="0" shapeId="0">
       <text>
-        <t>-place (00:04:49), -showMarkerAt (00:04:58), -( (00:04:59), -place (00:05:00), -. (00:05:01), -top (00:05:02), -, (00:05:03), -place (00:05:04), -. (00:05:05), -left (00:05:06), -) (00:05:07), -; (00:05:08), +const (00:00:00), +mapContainer (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +mapContainer (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +btn (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +btn (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +try (00:00:00), +{ (00:00:00), +item (00:00:00), +showInventory (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +catch (00:00:00), +( (00:00:00), +err (00:00:00), +) (00:00:00), +{ (00:00:00), +console (00:00:00), +. (00:00:00), +error (00:00:00), +( (00:00:00), +" (00:00:00), +Invalid (00:00:00), +QR (00:00:00), +code (00:00:00), +data (00:00:00), +" (00:00:00), +, (00:00:00), +err (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +function (00:00:00), +showInventory (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +{ (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +itemName (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Name (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +( (00:00:00), +item (00:00:00), +. (00:00:00), +name (00:00:00), +| (00:00:00), +| (00:00:00), +" (00:00:00), +Unknown (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +inStore (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +In (00:00:00), +Store (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +( (00:00:00), +item (00:00:00), +. (00:00:00), +in (00:00:00), +_ (00:00:00), +store (00:00:00), +? (00:00:00), +" (00:00:00), +Yes (00:00:00), +" (00:00:00), +: (00:00:00), +" (00:00:00), +No (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +price (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Price (00:00:00), +: (00:00:00), +€ (00:00:00), +" (00:00:00), ++ (00:00:00), +( (00:00:00), +item (00:00:00), +. (00:00:00), +price (00:00:00), +| (00:00:00), +| (00:00:00), +" (00:00:00), +0 (00:00:00), +. (00:00:00), +00 (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +function (00:00:00), +showMarkerAt (00:00:00), +( (00:00:00), +top (00:00:00), +, (00:00:00), +left (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +marker (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +marker (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +marker (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +top (00:00:00), += (00:00:00), +top (00:00:00), +; (00:00:00), +marker (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +left (00:00:00), += (00:00:00), +left (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+        <t>-place (00:04:49) ~0.00, -showMarkerAt (00:04:58), -( (00:04:59), -place (00:05:00), -. (00:05:01), -top (00:05:02), -, (00:05:03), -place (00:05:04), -. (00:05:05), -left (00:05:06), -) (00:05:07), -; (00:05:08), +const (00:00:00), +mapContainer (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +mapContainer (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +btn (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +btn (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +try (00:00:00), +{ (00:00:00), +item (00:00:00), +showInventory (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +catch (00:00:00), +( (00:00:00), +err (00:00:00), +) (00:00:00), +{ (00:00:00), +console (00:00:00), +. (00:00:00), +error (00:00:00), +( (00:00:00), +" (00:00:00), +Invalid (00:00:00), +QR (00:00:00), +code (00:00:00), +data (00:00:00), +" (00:00:00), +, (00:00:00), +err (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +function (00:00:00), +showInventory (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +{ (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +itemName (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Name (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +( (00:00:00), +item (00:00:00), +. (00:00:00), +name (00:00:00), +| (00:00:00), +| (00:00:00), +" (00:00:00), +Unknown (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +inStore (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +In (00:00:00), +Store (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +( (00:00:00), +item (00:00:00), +. (00:00:00), +in (00:00:00), +_ (00:00:00), +store (00:00:00), +? (00:00:00), +" (00:00:00), +Yes (00:00:00), +" (00:00:00), +: (00:00:00), +" (00:00:00), +No (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +price (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Price (00:00:00), +: (00:00:00), +€ (00:00:00), +" (00:00:00), ++ (00:00:00), +( (00:00:00), +item (00:00:00), +. (00:00:00), +price (00:00:00), +| (00:00:00), +| (00:00:00), +" (00:00:00), +0 (00:00:00), +. (00:00:00), +00 (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +function (00:00:00), +showMarkerAt (00:00:00), +( (00:00:00), +top (00:00:00), +, (00:00:00), +left (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +marker (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +marker (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +marker (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +top (00:00:00), += (00:00:00), +top (00:00:00), +; (00:00:00), +marker (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +left (00:00:00), += (00:00:00), +left (00:00:00), +; (00:00:00), +} (00:00:00)</t>
       </text>
     </comment>
     <comment ref="P36" authorId="0" shapeId="0">
@@ -659,12 +659,12 @@
     </comment>
     <comment ref="L42" authorId="0" shapeId="0">
       <text>
-        <t>-280 (00:00:08), -body (00:00:17), -{ (00:00:18), -display (00:00:19), -: (00:00:20), -flex (00:00:21), -; (00:00:22), -flex (00:00:23), -- (00:00:24), -direction (00:00:25), -: (00:00:26), -column (00:00:27), -; (00:00:28), -align (00:00:29), -- (00:00:30), -items (00:00:31), -: (00:00:32), -center (00:00:33), -; (00:00:34), -margin (00:00:35), -: (00:00:36), -0 (00:00:37), -; (00:00:38), -} (00:00:39), -h1 (00:00:40), -{ (00:00:41), -font (00:00:42), -- (00:00:43), -family (00:00:44), -: (00:00:45), -" (00:00:46), -Arial (00:00:47), -" (00:00:48), -; (00:00:49), -color (00:00:50), -: (00:00:51), -var (00:00:52), -( (00:00:53), -- (00:00:54), -- (00:00:55), -theme (00:00:56), -) (00:00:57), -; (00:00:58), -} (00:00:59), -# (00:01:00), -map (00:01:01), -{ (00:01:02), -width (00:01:03), -: (00:01:04), -100 (00:01:05), -% (00:01:06), -; (00:01:07), -} (00:01:08), -# (00:01:09), -marker (00:01:10), -{ (00:01:11), -width (00:01:12), -: (00:01:13), -3vw (00:01:14), -; (00:01:15), -height (00:01:26), -: (00:01:27), -3vw (00:01:28), -; (00:01:29), -background (00:01:30), -- (00:01:31), -color (00:01:32), -: (00:01:33), -black (00:01:34), -; (00:01:35), -border (00:01:36), -- (00:01:37), -radius (00:01:38), -: (00:01:39), -50 (00:01:40), -% (00:01:41), -; (00:01:42), -outline (00:01:43), -: (00:01:44), -5px (00:01:45), -solid (00:01:46), -var (00:01:47), -( (00:01:48), -- (00:01:49), -- (00:01:50), -theme (00:01:51), -) (00:01:52), -; (00:01:53), -border (00:02:03), -: (00:02:04), -5px (00:02:05), -solid (00:02:06), -white (00:02:07), -; (00:02:08), -position (00:02:16), -: (00:02:17), -absolute (00:02:18), -; (00:02:19), -top (00:02:20), -: (00:02:21), -0 (00:02:22), -; (00:02:23), -left (00:02:24), -: (00:02:25), -0 (00:02:26), -; (00:02:27), -transform (00:02:28), -: (00:02:29), -translate (00:02:30), -( (00:02:31), -- (00:02:32), -50 (00:02:33), -% (00:02:34), -, (00:02:35), -- (00:02:36), -50 (00:02:37), -% (00:02:38), -) (00:02:39), -; (00:02:40), -} (00:02:41), -# (00:02:42), -mapContainer (00:02:43), -{ (00:02:44), -position (00:02:45), -: (00:02:46), -relative (00:02:47), -; (00:02:48), -display (00:02:49), -: (00:02:50), -none (00:02:51), -; (00:02:52), -} (00:02:53), -# (00:02:54), -camera (00:02:55), -{ (00:02:56), -width (00:02:57), -: (00:02:58), -100 (00:02:59), -% (00:03:00), -; (00:03:01), -} (00:03:02), +000000 (00:00:00), +# (00:00:00), +btn (00:00:00), +{ (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +var (00:00:00), +( (00:00:00), +- (00:00:00), +- (00:00:00), +theme (00:00:00), +) (00:00:00), +; (00:00:00), +color (00:00:00), +: (00:00:00), +white (00:00:00), +; (00:00:00), +border (00:00:00), +: (00:00:00), +none (00:00:00), +; (00:00:00), +padding (00:00:00), +: (00:00:00), +12px (00:00:00), +30px (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +18px (00:00:00), +; (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +8px (00:00:00), +; (00:00:00), +transition (00:00:00), +: (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +0 (00:00:00), +. (00:00:00), +3s (00:00:00), +ease (00:00:00), +, (00:00:00), +transform (00:00:00), +0 (00:00:00), +. (00:00:00), +2s (00:00:00), +ease (00:00:00), +, (00:00:00), +box (00:00:00), +- (00:00:00), +shadow (00:00:00), +0 (00:00:00), +. (00:00:00), +3s (00:00:00), +ease (00:00:00), +; (00:00:00), +box (00:00:00), +- (00:00:00), +shadow (00:00:00), +: (00:00:00), +0 (00:00:00), +4px (00:00:00), +8px (00:00:00), +rgba (00:00:00), +( (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +. (00:00:00), +1 (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +btn (00:00:00), +: (00:00:00), +hover (00:00:00), +{ (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +333333 (00:00:00), +; (00:00:00), +transform (00:00:00), +: (00:00:00), +scale (00:00:00), +( (00:00:00), +1 (00:00:00), +. (00:00:00), +1 (00:00:00), +) (00:00:00), +; (00:00:00), +cursor (00:00:00), +: (00:00:00), +pointer (00:00:00), +; (00:00:00), +box (00:00:00), +- (00:00:00), +shadow (00:00:00), +: (00:00:00), +0 (00:00:00), +6px (00:00:00), +15px (00:00:00), +rgba (00:00:00), +( (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +. (00:00:00), +2 (00:00:00), +) (00:00:00), +; (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +fff (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +btn (00:00:00), +: (00:00:00), +active (00:00:00), +{ (00:00:00), +transform (00:00:00), +: (00:00:00), +scale (00:00:00), +( (00:00:00), +1 (00:00:00), +) (00:00:00), +; (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +var (00:00:00), +( (00:00:00), +- (00:00:00), +- (00:00:00), +theme (00:00:00), +) (00:00:00), +; (00:00:00), +box (00:00:00), +- (00:00:00), +shadow (00:00:00), +: (00:00:00), +0 (00:00:00), +4px (00:00:00), +8px (00:00:00), +rgba (00:00:00), +( (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +. (00:00:00), +1 (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+        <t>-280 (00:00:08) ~0.17, -body (00:00:17), -{ (00:00:18), -display (00:00:19), -: (00:00:20), -flex (00:00:21), -; (00:00:22), -flex (00:00:23), -- (00:00:24), -direction (00:00:25), -: (00:00:26), -column (00:00:27), -; (00:00:28), -align (00:00:29), -- (00:00:30), -items (00:00:31), -: (00:00:32), -center (00:00:33), -; (00:00:34), -margin (00:00:35), -: (00:00:36), -0 (00:00:37), -; (00:00:38), -} (00:00:39), -h1 (00:00:40), -{ (00:00:41), -font (00:00:42), -- (00:00:43), -family (00:00:44), -: (00:00:45), -" (00:00:46), -Arial (00:00:47), -" (00:00:48), -; (00:00:49), -color (00:00:50), -: (00:00:51), -var (00:00:52), -( (00:00:53), -- (00:00:54), -- (00:00:55), -theme (00:00:56), -) (00:00:57), -; (00:00:58), -} (00:00:59), -# (00:01:00), -map (00:01:01), -{ (00:01:02), -width (00:01:03), -: (00:01:04), -100 (00:01:05), -% (00:01:06), -; (00:01:07), -} (00:01:08), -# (00:01:09), -marker (00:01:10), -{ (00:01:11), -width (00:01:12), -: (00:01:13), -3vw (00:01:14), -; (00:01:15), -height (00:01:26), -: (00:01:27), -3vw (00:01:28), -; (00:01:29), -background (00:01:30), -- (00:01:31), -color (00:01:32), -: (00:01:33), -black (00:01:34), -; (00:01:35), -border (00:01:36), -- (00:01:37), -radius (00:01:38), -: (00:01:39), -50 (00:01:40), -% (00:01:41), -; (00:01:42), -outline (00:01:43), -: (00:01:44), -5px (00:01:45), -solid (00:01:46), -var (00:01:47), -( (00:01:48), -- (00:01:49), -- (00:01:50), -theme (00:01:51), -) (00:01:52), -; (00:01:53), -border (00:02:03), -: (00:02:04), -5px (00:02:05), -solid (00:02:06), -white (00:02:07), -; (00:02:08), -position (00:02:16), -: (00:02:17), -absolute (00:02:18), -; (00:02:19), -top (00:02:20), -: (00:02:21), -0 (00:02:22), -; (00:02:23), -left (00:02:24), -: (00:02:25), -0 (00:02:26), -; (00:02:27), -transform (00:02:28), -: (00:02:29), -translate (00:02:30), -( (00:02:31), -- (00:02:32), -50 (00:02:33), -% (00:02:34), -, (00:02:35), -- (00:02:36), -50 (00:02:37), -% (00:02:38), -) (00:02:39), -; (00:02:40), -} (00:02:41), -# (00:02:42), -mapContainer (00:02:43), -{ (00:02:44), -position (00:02:45), -: (00:02:46), -relative (00:02:47), -; (00:02:48), -display (00:02:49), -: (00:02:50), -none (00:02:51), -; (00:02:52), -} (00:02:53), -# (00:02:54), -camera (00:02:55), -{ (00:02:56), -width (00:02:57), -: (00:02:58), -100 (00:02:59), -% (00:03:00), -; (00:03:01), -} (00:03:02), +000000 (00:00:00), +# (00:00:00), +btn (00:00:00), +{ (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +var (00:00:00), +( (00:00:00), +- (00:00:00), +- (00:00:00), +theme (00:00:00), +) (00:00:00), +; (00:00:00), +color (00:00:00), +: (00:00:00), +white (00:00:00), +; (00:00:00), +border (00:00:00), +: (00:00:00), +none (00:00:00), +; (00:00:00), +padding (00:00:00), +: (00:00:00), +12px (00:00:00), +30px (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +18px (00:00:00), +; (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +8px (00:00:00), +; (00:00:00), +transition (00:00:00), +: (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +0 (00:00:00), +. (00:00:00), +3s (00:00:00), +ease (00:00:00), +, (00:00:00), +transform (00:00:00), +0 (00:00:00), +. (00:00:00), +2s (00:00:00), +ease (00:00:00), +, (00:00:00), +box (00:00:00), +- (00:00:00), +shadow (00:00:00), +0 (00:00:00), +. (00:00:00), +3s (00:00:00), +ease (00:00:00), +; (00:00:00), +box (00:00:00), +- (00:00:00), +shadow (00:00:00), +: (00:00:00), +0 (00:00:00), +4px (00:00:00), +8px (00:00:00), +rgba (00:00:00), +( (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +. (00:00:00), +1 (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +btn (00:00:00), +: (00:00:00), +hover (00:00:00), +{ (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +333333 (00:00:00), +; (00:00:00), +transform (00:00:00), +: (00:00:00), +scale (00:00:00), +( (00:00:00), +1 (00:00:00), +. (00:00:00), +1 (00:00:00), +) (00:00:00), +; (00:00:00), +cursor (00:00:00), +: (00:00:00), +pointer (00:00:00), +; (00:00:00), +box (00:00:00), +- (00:00:00), +shadow (00:00:00), +: (00:00:00), +0 (00:00:00), +6px (00:00:00), +15px (00:00:00), +rgba (00:00:00), +( (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +. (00:00:00), +2 (00:00:00), +) (00:00:00), +; (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +fff (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +btn (00:00:00), +: (00:00:00), +active (00:00:00), +{ (00:00:00), +transform (00:00:00), +: (00:00:00), +scale (00:00:00), +( (00:00:00), +1 (00:00:00), +) (00:00:00), +; (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +var (00:00:00), +( (00:00:00), +- (00:00:00), +- (00:00:00), +theme (00:00:00), +) (00:00:00), +; (00:00:00), +box (00:00:00), +- (00:00:00), +shadow (00:00:00), +: (00:00:00), +0 (00:00:00), +4px (00:00:00), +8px (00:00:00), +rgba (00:00:00), +( (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +. (00:00:00), +1 (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00)</t>
       </text>
     </comment>
     <comment ref="N42" authorId="0" shapeId="0">
       <text>
-        <t>-const (00:03:03), -new (00:03:06), -Html5Qrcode (00:03:07), -( (00:03:08), -" (00:03:09), -camera (00:03:10), -" (00:03:11), -) (00:03:12), -; (00:03:13), -reader (00:04:28), -. (00:04:29), -start (00:04:30), -( (00:04:31), -{ (00:04:32), -facingMode (00:04:33), -: (00:04:34), -" (00:04:35), -environment (00:04:36), -" (00:04:37), -} (00:04:38), -, (00:04:39), -{ (00:04:40), -} (00:04:41), -, (00:04:42), -function (00:04:43), -( (00:04:44), -text (00:04:45), -) (00:04:46), -{ (00:04:47), -const (00:04:48), -place (00:04:49), -= (00:04:50), -JSON (00:04:51), -. (00:04:52), -parse (00:04:53), -( (00:04:54), -text (00:04:55), -) (00:04:56), -; (00:04:57), -showMarkerAt (00:04:58), -( (00:04:59), -place (00:05:00), -. (00:05:01), -top (00:05:02), -, (00:05:03), -place (00:05:04), -. (00:05:05), -left (00:05:06), -) (00:05:07), -; (00:05:08), -toggleScanner (00:05:09), -( (00:05:10), -) (00:05:11), -; (00:05:12), -} (00:05:13), -) (00:05:14), -. (00:05:15), -catch (00:05:16), -( (00:05:17), -function (00:05:18), -( (00:05:19), -err (00:05:20), -) (00:05:21), -{ (00:05:22), -console (00:05:23), -. (00:05:24), -error (00:05:25), -( (00:05:26), -err (00:05:27), -) (00:05:28), -; (00:05:29), -} (00:05:30), -) (00:05:31), -; (00:05:32), -stop (00:05:41), -function (00:05:46), -showMarkerAt (00:05:47), -( (00:05:48), -top (00:05:49), -, (00:05:50), -left (00:05:51), -) (00:05:52), -{ (00:05:53), -marker (00:05:54), -. (00:05:55), -style (00:05:56), -. (00:05:57), -top (00:05:58), -= (00:05:59), -top (00:06:00), -; (00:06:01), -marker (00:06:02), -. (00:06:03), -style (00:06:04), -. (00:06:05), -left (00:06:06), -= (00:06:07), -left (00:06:08), -; (00:06:09), -} (00:06:10), +let (00:00:00), +null (00:00:00), +reader (00:00:00), += (00:00:00), +new (00:00:00), +Html5QrcodeScanner (00:00:00), +( (00:00:00), +" (00:00:00), +qr (00:00:00), +- (00:00:00), +reader (00:00:00), +" (00:00:00), +, (00:00:00), +{ (00:00:00), +fps (00:00:00), +: (00:00:00), +10 (00:00:00), +, (00:00:00), +qrbox (00:00:00), +: (00:00:00), +250 (00:00:00), +} (00:00:00), +) (00:00:00), +; (00:00:00), +reader (00:00:00), +. (00:00:00), +render (00:00:00), +( (00:00:00), +onScanSuccess (00:00:00), +, (00:00:00), +onScanError (00:00:00), +) (00:00:00), +; (00:00:00), +function (00:00:00), +onScanSuccess (00:00:00), +( (00:00:00), +decodedText (00:00:00), +, (00:00:00), +decodedResult (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +item (00:00:00), += (00:00:00), +JSON (00:00:00), +. (00:00:00), +parse (00:00:00), +( (00:00:00), +decodedText (00:00:00), +) (00:00:00), +; (00:00:00), +displayItemDetails (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +; (00:00:00), +toggleScanner (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +function (00:00:00), +onScanError (00:00:00), +( (00:00:00), +errorMessage (00:00:00), +) (00:00:00), +{ (00:00:00), +console (00:00:00), +. (00:00:00), +error (00:00:00), +( (00:00:00), +" (00:00:00), +Error (00:00:00), +scanning (00:00:00), +QR (00:00:00), +code (00:00:00), +: (00:00:00), +" (00:00:00), +, (00:00:00), +errorMessage (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +clear (00:00:00), +function (00:00:00), +displayItemDetails (00:00:00), +( (00:00:00), +data (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +nameParagraph (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +item (00:00:00), +- (00:00:00), +name (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +inStockParagraph (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +in (00:00:00), +- (00:00:00), +stock (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +priceParagraph (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +price (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +nameParagraph (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +Name (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +data (00:00:00), +. (00:00:00), +name (00:00:00), +; (00:00:00), +inStockParagraph (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +In (00:00:00), +Stock (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +( (00:00:00), +data (00:00:00), +. (00:00:00), +inStock (00:00:00), +? (00:00:00), +" (00:00:00), +Yes (00:00:00), +" (00:00:00), +: (00:00:00), +" (00:00:00), +No (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +priceParagraph (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +Price (00:00:00), +: (00:00:00), +€ (00:00:00), +" (00:00:00), ++ (00:00:00), +data (00:00:00), +. (00:00:00), +price (00:00:00), +. (00:00:00), +toFixed (00:00:00), +( (00:00:00), +2 (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+        <t>-const (00:03:03) ~0.20, -new (00:03:06), -Html5Qrcode (00:03:07), -( (00:03:08), -" (00:03:09), -camera (00:03:10), -" (00:03:11), -) (00:03:12), -; (00:03:13), -reader (00:04:28), -. (00:04:29), -start (00:04:30), -( (00:04:31), -{ (00:04:32), -facingMode (00:04:33), -: (00:04:34), -" (00:04:35), -environment (00:04:36), -" (00:04:37), -} (00:04:38), -, (00:04:39), -{ (00:04:40), -} (00:04:41), -, (00:04:42), -function (00:04:43), -( (00:04:44), -text (00:04:45), -) (00:04:46), -{ (00:04:47), -const (00:04:48), -place (00:04:49), -= (00:04:50), -JSON (00:04:51), -. (00:04:52), -parse (00:04:53), -( (00:04:54), -text (00:04:55), -) (00:04:56), -; (00:04:57), -showMarkerAt (00:04:58), -( (00:04:59), -place (00:05:00), -. (00:05:01), -top (00:05:02), -, (00:05:03), -place (00:05:04), -. (00:05:05), -left (00:05:06), -) (00:05:07), -; (00:05:08), -toggleScanner (00:05:09), -( (00:05:10), -) (00:05:11), -; (00:05:12), -} (00:05:13), -) (00:05:14), -. (00:05:15), -catch (00:05:16), -( (00:05:17), -function (00:05:18), -( (00:05:19), -err (00:05:20), -) (00:05:21), -{ (00:05:22), -console (00:05:23), -. (00:05:24), -error (00:05:25), -( (00:05:26), -err (00:05:27), -) (00:05:28), -; (00:05:29), -} (00:05:30), -) (00:05:31), -; (00:05:32), -stop (00:05:41) ~0.00, -function (00:05:46), -showMarkerAt (00:05:47), -( (00:05:48), -top (00:05:49), -, (00:05:50), -left (00:05:51), -) (00:05:52), -{ (00:05:53), -marker (00:05:54), -. (00:05:55), -style (00:05:56), -. (00:05:57), -top (00:05:58), -= (00:05:59), -top (00:06:00), -; (00:06:01), -marker (00:06:02), -. (00:06:03), -style (00:06:04), -. (00:06:05), -left (00:06:06), -= (00:06:07), -left (00:06:08), -; (00:06:09), -} (00:06:10), +let (00:00:00), +null (00:00:00), +reader (00:00:00), += (00:00:00), +new (00:00:00), +Html5QrcodeScanner (00:00:00), +( (00:00:00), +" (00:00:00), +qr (00:00:00), +- (00:00:00), +reader (00:00:00), +" (00:00:00), +, (00:00:00), +{ (00:00:00), +fps (00:00:00), +: (00:00:00), +10 (00:00:00), +, (00:00:00), +qrbox (00:00:00), +: (00:00:00), +250 (00:00:00), +} (00:00:00), +) (00:00:00), +; (00:00:00), +reader (00:00:00), +. (00:00:00), +render (00:00:00), +( (00:00:00), +onScanSuccess (00:00:00), +, (00:00:00), +onScanError (00:00:00), +) (00:00:00), +; (00:00:00), +function (00:00:00), +onScanSuccess (00:00:00), +( (00:00:00), +decodedText (00:00:00), +, (00:00:00), +decodedResult (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +item (00:00:00), += (00:00:00), +JSON (00:00:00), +. (00:00:00), +parse (00:00:00), +( (00:00:00), +decodedText (00:00:00), +) (00:00:00), +; (00:00:00), +displayItemDetails (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +; (00:00:00), +toggleScanner (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +function (00:00:00), +onScanError (00:00:00), +( (00:00:00), +errorMessage (00:00:00), +) (00:00:00), +{ (00:00:00), +console (00:00:00), +. (00:00:00), +error (00:00:00), +( (00:00:00), +" (00:00:00), +Error (00:00:00), +scanning (00:00:00), +QR (00:00:00), +code (00:00:00), +: (00:00:00), +" (00:00:00), +, (00:00:00), +errorMessage (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +clear (00:00:00), +function (00:00:00), +displayItemDetails (00:00:00), +( (00:00:00), +data (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +nameParagraph (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +item (00:00:00), +- (00:00:00), +name (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +inStockParagraph (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +in (00:00:00), +- (00:00:00), +stock (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +priceParagraph (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +price (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +nameParagraph (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +Name (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +data (00:00:00), +. (00:00:00), +name (00:00:00), +; (00:00:00), +inStockParagraph (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +In (00:00:00), +Stock (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +( (00:00:00), +data (00:00:00), +. (00:00:00), +inStock (00:00:00), +? (00:00:00), +" (00:00:00), +Yes (00:00:00), +" (00:00:00), +: (00:00:00), +" (00:00:00), +No (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +priceParagraph (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +Price (00:00:00), +: (00:00:00), +€ (00:00:00), +" (00:00:00), ++ (00:00:00), +data (00:00:00), +. (00:00:00), +price (00:00:00), +. (00:00:00), +toFixed (00:00:00), +( (00:00:00), +2 (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00)</t>
       </text>
     </comment>
     <comment ref="D45" authorId="0" shapeId="0">
@@ -694,7 +694,7 @@
     </comment>
     <comment ref="N45" authorId="0" shapeId="0">
       <text>
-        <t>-place (00:04:49), -place (00:05:00), -place (00:05:04), +item (00:00:00), +item (00:00:00), +item (00:00:00), +showInventory (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +; (00:00:00), +function (00:00:00), +showInventory (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +{ (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +name (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Name (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +name (00:00:00), +; (00:00:00), +if (00:00:00), +( (00:00:00), +item (00:00:00), +. (00:00:00), +inStock (00:00:00), +) (00:00:00), +{ (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +stock (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +in (00:00:00), +stock (00:00:00), +: (00:00:00), +Yes (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00), +else (00:00:00), +{ (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +stock (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +in (00:00:00), +stock (00:00:00), +: (00:00:00), +No (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +price (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Price (00:00:00), +: (00:00:00), +€ (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +price (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+        <t>-place (00:04:49) ~0.00, -place (00:05:00) ~0.00, -place (00:05:04) ~0.00, +item (00:00:00), +item (00:00:00), +item (00:00:00), +showInventory (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +; (00:00:00), +function (00:00:00), +showInventory (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +{ (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +name (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Name (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +name (00:00:00), +; (00:00:00), +if (00:00:00), +( (00:00:00), +item (00:00:00), +. (00:00:00), +inStock (00:00:00), +) (00:00:00), +{ (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +stock (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +in (00:00:00), +stock (00:00:00), +: (00:00:00), +Yes (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00), +else (00:00:00), +{ (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +stock (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +in (00:00:00), +stock (00:00:00), +: (00:00:00), +No (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +price (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Price (00:00:00), +: (00:00:00), +€ (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +price (00:00:00), +; (00:00:00), +} (00:00:00)</t>
       </text>
     </comment>
     <comment ref="D46" authorId="0" shapeId="0">
@@ -714,7 +714,7 @@
     </comment>
     <comment ref="J46" authorId="0" shapeId="0">
       <text>
-        <t>-Positioning (00:07:06), -Positioning (00:07:38), +Inventory (00:00:00), +System (00:00:00), +Inventory (00:00:00), +System (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +inventory (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemName (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemStock (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemPrice (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
+        <t>-Positioning (00:07:06) ~0.09, -Positioning (00:07:38) ~0.09, +Inventory (00:00:00), +System (00:00:00), +Inventory (00:00:00), +System (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +inventory (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemName (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemStock (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemPrice (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="L46" authorId="0" shapeId="0">
@@ -779,7 +779,7 @@
     </comment>
     <comment ref="J48" authorId="0" shapeId="0">
       <text>
-        <t>-Positioning (00:07:06), -Positioning (00:07:38), +Inventory (00:00:00), +System (00:00:00), +Inventory (00:00:00), +System (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +name (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +store (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +price (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00)</t>
+        <t>-Positioning (00:07:06) ~0.09, -Positioning (00:07:38) ~0.09, +Inventory (00:00:00), +System (00:00:00), +Inventory (00:00:00), +System (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +name (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +store (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +price (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="L48" authorId="0" shapeId="0">
@@ -789,7 +789,7 @@
     </comment>
     <comment ref="N48" authorId="0" shapeId="0">
       <text>
-        <t>-place (00:04:49), -place (00:05:00), -place (00:05:04), +item (00:00:00), +item (00:00:00), +item (00:00:00), +showItemInfo (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +; (00:00:00), +function (00:00:00), +showItemInfo (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +{ (00:00:00), +name (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Name (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +name (00:00:00), +; (00:00:00), +store (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +In (00:00:00), +store (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +( (00:00:00), +item (00:00:00), +. (00:00:00), +in (00:00:00), +_ (00:00:00), +store (00:00:00), +? (00:00:00), +" (00:00:00), +Yes (00:00:00), +" (00:00:00), +: (00:00:00), +" (00:00:00), +No (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +price (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Price (00:00:00), +: (00:00:00), +€ (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +price (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+        <t>-place (00:04:49) ~0.00, -place (00:05:00) ~0.00, -place (00:05:04) ~0.00, +item (00:00:00), +item (00:00:00), +item (00:00:00), +showItemInfo (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +; (00:00:00), +function (00:00:00), +showItemInfo (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +{ (00:00:00), +name (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Name (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +name (00:00:00), +; (00:00:00), +store (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +In (00:00:00), +store (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +( (00:00:00), +item (00:00:00), +. (00:00:00), +in (00:00:00), +_ (00:00:00), +store (00:00:00), +? (00:00:00), +" (00:00:00), +Yes (00:00:00), +" (00:00:00), +: (00:00:00), +" (00:00:00), +No (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +price (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Price (00:00:00), +: (00:00:00), +€ (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +price (00:00:00), +; (00:00:00), +} (00:00:00)</t>
       </text>
     </comment>
     <comment ref="P48" authorId="0" shapeId="0">
@@ -814,7 +814,7 @@
     </comment>
     <comment ref="J50" authorId="0" shapeId="0">
       <text>
-        <t>-viewport (00:06:42), +viewpoint (00:00:00), +&lt; (00:00:00), +style (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +style (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +inventory (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +script (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +script (00:00:00), +&gt; (00:00:00)</t>
+        <t>-viewport (00:06:42) ~0.78, +viewpoint (00:00:00), +&lt; (00:00:00), +style (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +style (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +inventory (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +script (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +script (00:00:00), +&gt; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="L50" authorId="0" shapeId="0">
@@ -849,7 +849,7 @@
     </comment>
     <comment ref="J51" authorId="0" shapeId="0">
       <text>
-        <t>-onclick (00:08:35), +onClick (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +inventory (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +name (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +stock (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +price (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
+        <t>-onclick (00:08:35) ~0.86, +onClick (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +inventory (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +name (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +stock (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +price (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="L51" authorId="0" shapeId="0">
@@ -859,7 +859,7 @@
     </comment>
     <comment ref="N51" authorId="0" shapeId="0">
       <text>
-        <t>-place (00:04:49), -place (00:05:00), -place (00:05:04), +item (00:00:00), +item (00:00:00), +item (00:00:00), +displayInventory (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +; (00:00:00), +function (00:00:00), +displayInventory (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +name (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +name (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +stock (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +stock (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +price (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +price (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +name (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +Name (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +name (00:00:00), +; (00:00:00), +stock (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +In (00:00:00), +stock (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +( (00:00:00), +item (00:00:00), +. (00:00:00), +inStock (00:00:00), +? (00:00:00), +" (00:00:00), +yes (00:00:00), +" (00:00:00), +: (00:00:00), +" (00:00:00), +no (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +price (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +Price (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +price (00:00:00), ++ (00:00:00), +" (00:00:00), +€ (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+        <t>-place (00:04:49) ~0.00, -place (00:05:00) ~0.00, -place (00:05:04) ~0.00, +item (00:00:00), +item (00:00:00), +item (00:00:00), +displayInventory (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +; (00:00:00), +function (00:00:00), +displayInventory (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +name (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +name (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +stock (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +stock (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +price (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +price (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +name (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +Name (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +name (00:00:00), +; (00:00:00), +stock (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +In (00:00:00), +stock (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +( (00:00:00), +item (00:00:00), +. (00:00:00), +inStock (00:00:00), +? (00:00:00), +" (00:00:00), +yes (00:00:00), +" (00:00:00), +: (00:00:00), +" (00:00:00), +no (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +price (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +Price (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +price (00:00:00), ++ (00:00:00), +" (00:00:00), +€ (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00)</t>
       </text>
     </comment>
     <comment ref="D56" authorId="0" shapeId="0">
@@ -879,7 +879,7 @@
     </comment>
     <comment ref="J56" authorId="0" shapeId="0">
       <text>
-        <t>-SCAN (00:08:43), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +name (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +stock (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +price (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +style (00:00:00), += (00:00:00), +" (00:00:00), +- (00:00:00), +- (00:00:00), +theme (00:00:00), +: (00:00:00), +# (00:00:00), +ffc0cb (00:00:00), +" (00:00:00), +Scan (00:00:00)</t>
+        <t>-SCAN (00:08:43) ~0.25, +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +name (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +stock (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +price (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +style (00:00:00), += (00:00:00), +" (00:00:00), +- (00:00:00), +- (00:00:00), +theme (00:00:00), +: (00:00:00), +# (00:00:00), +ffc0cb (00:00:00), +" (00:00:00), +Scan (00:00:00)</t>
       </text>
     </comment>
     <comment ref="L56" authorId="0" shapeId="0">
@@ -954,7 +954,7 @@
     </comment>
     <comment ref="N61" authorId="0" shapeId="0">
       <text>
-        <t>-place (00:04:49), -place (00:05:00), -place (00:05:04), +item (00:00:00), +item (00:00:00), +item (00:00:00), +displayItemInfo (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +; (00:00:00), +function (00:00:00), +displayItemInfo (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +{ (00:00:00), +name (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Name (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +name (00:00:00), +; (00:00:00), +inStore (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +In (00:00:00), +store (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +( (00:00:00), +item (00:00:00), +. (00:00:00), +in (00:00:00), +_ (00:00:00), +store (00:00:00), +? (00:00:00), +" (00:00:00), +Yes (00:00:00), +" (00:00:00), +: (00:00:00), +" (00:00:00), +No (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +price (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Price (00:00:00), +: (00:00:00), +€ (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +price (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+        <t>-place (00:04:49) ~0.00, -place (00:05:00) ~0.00, -place (00:05:04) ~0.00, +item (00:00:00), +item (00:00:00), +item (00:00:00), +displayItemInfo (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +; (00:00:00), +function (00:00:00), +displayItemInfo (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +{ (00:00:00), +name (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Name (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +name (00:00:00), +; (00:00:00), +inStore (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +In (00:00:00), +store (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +( (00:00:00), +item (00:00:00), +. (00:00:00), +in (00:00:00), +_ (00:00:00), +store (00:00:00), +? (00:00:00), +" (00:00:00), +Yes (00:00:00), +" (00:00:00), +: (00:00:00), +" (00:00:00), +No (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +price (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Price (00:00:00), +: (00:00:00), +€ (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +price (00:00:00), +; (00:00:00), +} (00:00:00)</t>
       </text>
     </comment>
     <comment ref="P61" authorId="0" shapeId="0">
@@ -964,7 +964,7 @@
     </comment>
     <comment ref="D62" authorId="0" shapeId="0">
       <text>
-        <t>Short name part(s) not auto-redacted (verify manually): De, Unexpected file type: map.png, Removed onlinetext.txt (identity-revealing links)</t>
+        <t>Short name part(s) not auto-redacted, Unexpected file type: map.png, Removed onlinetext.txt (identity-revealing links)</t>
       </text>
     </comment>
     <comment ref="E62" authorId="0" shapeId="0">
@@ -979,7 +979,7 @@
     </comment>
     <comment ref="J62" authorId="0" shapeId="0">
       <text>
-        <t>-DOCTYPE (00:06:13), +doctype (00:00:00), +/ (00:00:00), +/ (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +inventory (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemName (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Item (00:00:00), +Name (00:00:00), +: (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemStock (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Available (00:00:00), +in (00:00:00), +Store (00:00:00), +: (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemPrice (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Item (00:00:00), +Price (00:00:00), +: (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
+        <t>-DOCTYPE (00:06:13) ~0.00, +doctype (00:00:00), +/ (00:00:00), +/ (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +inventory (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemName (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Item (00:00:00), +Name (00:00:00), +: (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemStock (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Available (00:00:00), +in (00:00:00), +Store (00:00:00), +: (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemPrice (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Item (00:00:00), +Price (00:00:00), +: (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="L62" authorId="0" shapeId="0">
@@ -1019,7 +1019,7 @@
     </comment>
     <comment ref="N66" authorId="0" shapeId="0">
       <text>
-        <t>-place (00:04:49), -place (00:05:00), -place (00:05:04), +const (00:00:00), +inventory (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +inventory (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +data (00:00:00), +data (00:00:00), +data (00:00:00), +const (00:00:00), +itemDiv (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +createElement (00:00:00), +( (00:00:00), +" (00:00:00), +div (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +name (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +createElement (00:00:00), +( (00:00:00), +" (00:00:00), +p (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +name (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +Name (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +data (00:00:00), +. (00:00:00), +name (00:00:00), +; (00:00:00), +const (00:00:00), +stock (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +createElement (00:00:00), +( (00:00:00), +" (00:00:00), +p (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +stock (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +In (00:00:00), +Store (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +( (00:00:00), +data (00:00:00), +. (00:00:00), +in (00:00:00), +_ (00:00:00), +store (00:00:00), +? (00:00:00), +" (00:00:00), +Yes (00:00:00), +" (00:00:00), +: (00:00:00), +" (00:00:00), +No (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +price (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +createElement (00:00:00), +( (00:00:00), +" (00:00:00), +p (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +price (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +Price (00:00:00), +: (00:00:00), +€ (00:00:00), +" (00:00:00), ++ (00:00:00), +data (00:00:00), +. (00:00:00), +price (00:00:00), +; (00:00:00), +itemDiv (00:00:00), +. (00:00:00), +appendChild (00:00:00), +( (00:00:00), +name (00:00:00), +) (00:00:00), +; (00:00:00), +itemDiv (00:00:00), +. (00:00:00), +appendChild (00:00:00), +( (00:00:00), +stock (00:00:00), +) (00:00:00), +; (00:00:00), +itemDiv (00:00:00), +. (00:00:00), +appendChild (00:00:00), +( (00:00:00), +price (00:00:00), +) (00:00:00), +; (00:00:00), +inventory (00:00:00), +. (00:00:00), +appendChild (00:00:00), +( (00:00:00), +itemDiv (00:00:00), +) (00:00:00), +; (00:00:00)</t>
+        <t>-place (00:04:49) ~0.20, -place (00:05:00) ~0.20, -place (00:05:04) ~0.20, +const (00:00:00), +inventory (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +inventory (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +data (00:00:00), +data (00:00:00), +data (00:00:00), +const (00:00:00), +itemDiv (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +createElement (00:00:00), +( (00:00:00), +" (00:00:00), +div (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +name (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +createElement (00:00:00), +( (00:00:00), +" (00:00:00), +p (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +name (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +Name (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +data (00:00:00), +. (00:00:00), +name (00:00:00), +; (00:00:00), +const (00:00:00), +stock (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +createElement (00:00:00), +( (00:00:00), +" (00:00:00), +p (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +stock (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +In (00:00:00), +Store (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +( (00:00:00), +data (00:00:00), +. (00:00:00), +in (00:00:00), +_ (00:00:00), +store (00:00:00), +? (00:00:00), +" (00:00:00), +Yes (00:00:00), +" (00:00:00), +: (00:00:00), +" (00:00:00), +No (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +price (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +createElement (00:00:00), +( (00:00:00), +" (00:00:00), +p (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +price (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +Price (00:00:00), +: (00:00:00), +€ (00:00:00), +" (00:00:00), ++ (00:00:00), +data (00:00:00), +. (00:00:00), +price (00:00:00), +; (00:00:00), +itemDiv (00:00:00), +. (00:00:00), +appendChild (00:00:00), +( (00:00:00), +name (00:00:00), +) (00:00:00), +; (00:00:00), +itemDiv (00:00:00), +. (00:00:00), +appendChild (00:00:00), +( (00:00:00), +stock (00:00:00), +) (00:00:00), +; (00:00:00), +itemDiv (00:00:00), +. (00:00:00), +appendChild (00:00:00), +( (00:00:00), +price (00:00:00), +) (00:00:00), +; (00:00:00), +inventory (00:00:00), +. (00:00:00), +appendChild (00:00:00), +( (00:00:00), +itemDiv (00:00:00), +) (00:00:00), +; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="P66" authorId="0" shapeId="0">
@@ -1044,12 +1044,12 @@
     </comment>
     <comment ref="J68" authorId="0" shapeId="0">
       <text>
-        <t>-Positioning (00:07:06), -Positioning (00:07:38), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +HEAD (00:00:00), +&lt; (00:00:00), +! (00:00:00), +DOCTYPE (00:00:00), +html (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +html (00:00:00), +lang (00:00:00), += (00:00:00), +" (00:00:00), +en (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +head (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +meta (00:00:00), +charset (00:00:00), += (00:00:00), +" (00:00:00), +UTF (00:00:00), +- (00:00:00), +8 (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +meta (00:00:00), +name (00:00:00), += (00:00:00), +" (00:00:00), +viewport (00:00:00), +" (00:00:00), +content (00:00:00), += (00:00:00), +" (00:00:00), +width (00:00:00), += (00:00:00), +device (00:00:00), +- (00:00:00), +width (00:00:00), +, (00:00:00), +initial (00:00:00), +- (00:00:00), +scale (00:00:00), += (00:00:00), +1 (00:00:00), +. (00:00:00), +0 (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +title (00:00:00), +&gt; (00:00:00), +QR (00:00:00), +Inventory (00:00:00), +System (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +title (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +link (00:00:00), +rel (00:00:00), += (00:00:00), +" (00:00:00), +stylesheet (00:00:00), +" (00:00:00), +href (00:00:00), += (00:00:00), +" (00:00:00), +123456 (00:00:00), +- (00:00:00), +p (00:00:00), +. (00:00:00), +css (00:00:00), +" (00:00:00), +/ (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +head (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +body (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +h1 (00:00:00), +&gt; (00:00:00), +QR (00:00:00), +Inventory (00:00:00), +System (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +h1 (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +mapContainer (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +img (00:00:00), +src (00:00:00), += (00:00:00), +" (00:00:00), +map (00:00:00), +. (00:00:00), +png (00:00:00), +" (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +map (00:00:00), +" (00:00:00), +alt (00:00:00), += (00:00:00), +" (00:00:00), +map (00:00:00), +" (00:00:00), +/ (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +marker (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +button (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +btn (00:00:00), +" (00:00:00), +onclick (00:00:00), += (00:00:00), +" (00:00:00), +toggleScanner (00:00:00), +( (00:00:00), +) (00:00:00), +" (00:00:00), +&gt; (00:00:00), +SCAN (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +button (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +inventory (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +camera (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +script (00:00:00), +src (00:00:00), += (00:00:00), +" (00:00:00), +https (00:00:00), +: (00:00:00), +/ (00:00:00), +/ (00:00:00), +unpkg (00:00:00), +. (00:00:00), +com (00:00:00), +/ (00:00:00), +html5 (00:00:00), +- (00:00:00), +qrcode (00:00:00), +" (00:00:00), +type (00:00:00), += (00:00:00), +" (00:00:00), +text (00:00:00), +/ (00:00:00), +javascript (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +script (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +script (00:00:00), +src (00:00:00), += (00:00:00), +" (00:00:00), +123456 (00:00:00), +- (00:00:00), +p (00:00:00), +. (00:00:00), +js (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +script (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +body (00:00:00), +&gt; (00:00:00), += (00:00:00), += (00:00:00), += (00:00:00), += (00:00:00), += (00:00:00), += (00:00:00), += (00:00:00), +Inventory (00:00:00), +System (00:00:00), +Inventory (00:00:00), +System (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +inventory (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +4503462fa4f894817eb35001cb59a566f24c4879 (00:00:00)</t>
+        <t>-Positioning (00:07:06) ~0.09, -Positioning (00:07:38) ~0.09, +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +HEAD (00:00:00), +&lt; (00:00:00), +! (00:00:00), +DOCTYPE (00:00:00), +html (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +html (00:00:00), +lang (00:00:00), += (00:00:00), +" (00:00:00), +en (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +head (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +meta (00:00:00), +charset (00:00:00), += (00:00:00), +" (00:00:00), +UTF (00:00:00), +- (00:00:00), +8 (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +meta (00:00:00), +name (00:00:00), += (00:00:00), +" (00:00:00), +viewport (00:00:00), +" (00:00:00), +content (00:00:00), += (00:00:00), +" (00:00:00), +width (00:00:00), += (00:00:00), +device (00:00:00), +- (00:00:00), +width (00:00:00), +, (00:00:00), +initial (00:00:00), +- (00:00:00), +scale (00:00:00), += (00:00:00), +1 (00:00:00), +. (00:00:00), +0 (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +title (00:00:00), +&gt; (00:00:00), +QR (00:00:00), +Inventory (00:00:00), +System (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +title (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +link (00:00:00), +rel (00:00:00), += (00:00:00), +" (00:00:00), +stylesheet (00:00:00), +" (00:00:00), +href (00:00:00), += (00:00:00), +" (00:00:00), +123456 (00:00:00), +- (00:00:00), +p (00:00:00), +. (00:00:00), +css (00:00:00), +" (00:00:00), +/ (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +head (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +body (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +h1 (00:00:00), +&gt; (00:00:00), +QR (00:00:00), +Inventory (00:00:00), +System (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +h1 (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +mapContainer (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +img (00:00:00), +src (00:00:00), += (00:00:00), +" (00:00:00), +map (00:00:00), +. (00:00:00), +png (00:00:00), +" (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +map (00:00:00), +" (00:00:00), +alt (00:00:00), += (00:00:00), +" (00:00:00), +map (00:00:00), +" (00:00:00), +/ (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +marker (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +button (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +btn (00:00:00), +" (00:00:00), +onclick (00:00:00), += (00:00:00), +" (00:00:00), +toggleScanner (00:00:00), +( (00:00:00), +) (00:00:00), +" (00:00:00), +&gt; (00:00:00), +SCAN (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +button (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +inventory (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +camera (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +script (00:00:00), +src (00:00:00), += (00:00:00), +" (00:00:00), +https (00:00:00), +: (00:00:00), +/ (00:00:00), +/ (00:00:00), +unpkg (00:00:00), +. (00:00:00), +com (00:00:00), +/ (00:00:00), +html5 (00:00:00), +- (00:00:00), +qrcode (00:00:00), +" (00:00:00), +type (00:00:00), += (00:00:00), +" (00:00:00), +text (00:00:00), +/ (00:00:00), +javascript (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +script (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +script (00:00:00), +src (00:00:00), += (00:00:00), +" (00:00:00), +123456 (00:00:00), +- (00:00:00), +p (00:00:00), +. (00:00:00), +js (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +script (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +body (00:00:00), +&gt; (00:00:00), += (00:00:00), += (00:00:00), += (00:00:00), += (00:00:00), += (00:00:00), += (00:00:00), += (00:00:00), +Inventory (00:00:00), +System (00:00:00), +Inventory (00:00:00), +System (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +inventory (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +4503462fa4f894817eb35001cb59a566f24c4879 (00:00:00)</t>
       </text>
     </comment>
     <comment ref="L68" authorId="0" shapeId="0">
       <text>
-        <t>-black (00:01:34), -white (00:02:07), +yellow (00:00:00), +red (00:00:00), +button (00:00:00), +{ (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +var (00:00:00), +( (00:00:00), +- (00:00:00), +- (00:00:00), +theme (00:00:00), +) (00:00:00), +; (00:00:00), +color (00:00:00), +: (00:00:00), +white (00:00:00), +; (00:00:00), +cursor (00:00:00), +: (00:00:00), +pointer (00:00:00), +; (00:00:00), +transition (00:00:00), +: (00:00:00), +all (00:00:00), +2s (00:00:00), +ease (00:00:00), +; (00:00:00), +} (00:00:00), +button (00:00:00), +: (00:00:00), +hover (00:00:00), +{ (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +blue (00:00:00), +; (00:00:00), +transform (00:00:00), +: (00:00:00), +scale (00:00:00), +( (00:00:00), +2 (00:00:00), +. (00:00:00), +2 (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +inventory (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +80 (00:00:00), +% (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +family (00:00:00), +: (00:00:00), +' (00:00:00), +Times (00:00:00), +New (00:00:00), +Roman (00:00:00), +' (00:00:00), +, (00:00:00), +Times (00:00:00), +, (00:00:00), +serif (00:00:00), +, (00:00:00), +sans (00:00:00), +- (00:00:00), +serif (00:00:00), +; (00:00:00), +border (00:00:00), +: (00:00:00), +1px (00:00:00), +solid (00:00:00), +var (00:00:00), +( (00:00:00), +- (00:00:00), +- (00:00:00), +theme (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +inventory (00:00:00), +p (00:00:00), +{ (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +red (00:00:00), +; (00:00:00), +text (00:00:00), +- (00:00:00), +align (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +} (00:00:00), +: (00:00:00), +root (00:00:00), +{ (00:00:00), +- (00:00:00), +- (00:00:00), +theme (00:00:00), +: (00:00:00), +# (00:00:00), +280 (00:00:00), +; (00:00:00), +} (00:00:00), +body (00:00:00), +{ (00:00:00), +display (00:00:00), +: (00:00:00), +flex (00:00:00), +; (00:00:00), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +margin (00:00:00), +: (00:00:00), +0 (00:00:00), +; (00:00:00), +} (00:00:00), +h1 (00:00:00), +{ (00:00:00), +font (00:00:00), +- (00:00:00), +family (00:00:00), +: (00:00:00), +" (00:00:00), +Arial (00:00:00), +" (00:00:00), +; (00:00:00), +color (00:00:00), +: (00:00:00), +var (00:00:00), +( (00:00:00), +- (00:00:00), +- (00:00:00), +theme (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +map (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +100 (00:00:00), +% (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +marker (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +3vw (00:00:00), +; (00:00:00), +height (00:00:00), +: (00:00:00), +3vw (00:00:00), +; (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +yellow (00:00:00), +; (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +50 (00:00:00), +% (00:00:00), +; (00:00:00), +outline (00:00:00), +: (00:00:00), +5px (00:00:00), +solid (00:00:00), +var (00:00:00), +( (00:00:00), +- (00:00:00), +- (00:00:00), +theme (00:00:00), +) (00:00:00), +; (00:00:00), +border (00:00:00), +: (00:00:00), +5px (00:00:00), +solid (00:00:00), +red (00:00:00), +; (00:00:00), +position (00:00:00), +: (00:00:00), +absolute (00:00:00), +; (00:00:00), +top (00:00:00), +: (00:00:00), +0 (00:00:00), +; (00:00:00), +left (00:00:00), +: (00:00:00), +0 (00:00:00), +; (00:00:00), +transform (00:00:00), +: (00:00:00), +translate (00:00:00), +( (00:00:00), +- (00:00:00), +50 (00:00:00), +% (00:00:00), +, (00:00:00), +- (00:00:00), +50 (00:00:00), +% (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +mapContainer (00:00:00), +{ (00:00:00), +position (00:00:00), +: (00:00:00), +relative (00:00:00), +; (00:00:00), +display (00:00:00), +: (00:00:00), +none (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +camera (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +100 (00:00:00), +% (00:00:00), +; (00:00:00), +} (00:00:00), +button (00:00:00), +{ (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +var (00:00:00), +( (00:00:00), +- (00:00:00), +- (00:00:00), +theme (00:00:00), +) (00:00:00), +; (00:00:00), +color (00:00:00), +: (00:00:00), +white (00:00:00), +; (00:00:00), +cursor (00:00:00), +: (00:00:00), +pointer (00:00:00), +; (00:00:00), +transition (00:00:00), +: (00:00:00), +all (00:00:00), +2s (00:00:00), +ease (00:00:00), +; (00:00:00), +} (00:00:00), +button (00:00:00), +: (00:00:00), +hover (00:00:00), +{ (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +blue (00:00:00), +; (00:00:00), +transform (00:00:00), +: (00:00:00), +scale (00:00:00), +( (00:00:00), +2 (00:00:00), +. (00:00:00), +2 (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +inventory (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +80 (00:00:00), +% (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +family (00:00:00), +: (00:00:00), +' (00:00:00), +Times (00:00:00), +New (00:00:00), +Roman (00:00:00), +' (00:00:00), +, (00:00:00), +Times (00:00:00), +, (00:00:00), +serif (00:00:00), +, (00:00:00), +sans (00:00:00), +- (00:00:00), +serif (00:00:00), +; (00:00:00), +border (00:00:00), +: (00:00:00), +1px (00:00:00), +solid (00:00:00), +var (00:00:00), +( (00:00:00), +- (00:00:00), +- (00:00:00), +theme (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +inventory (00:00:00), +p (00:00:00), +{ (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +red (00:00:00), +; (00:00:00), +text (00:00:00), +- (00:00:00), +align (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +} (00:00:00), +: (00:00:00), +root (00:00:00), +{ (00:00:00), +- (00:00:00), +- (00:00:00), +theme (00:00:00), +: (00:00:00), +# (00:00:00), +280 (00:00:00), +; (00:00:00), +} (00:00:00), +body (00:00:00), +{ (00:00:00), +display (00:00:00), +: (00:00:00), +flex (00:00:00), +; (00:00:00), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +margin (00:00:00), +: (00:00:00), +0 (00:00:00), +; (00:00:00), +} (00:00:00), +h1 (00:00:00), +{ (00:00:00), +font (00:00:00), +- (00:00:00), +family (00:00:00), +: (00:00:00), +" (00:00:00), +Arial (00:00:00), +" (00:00:00), +; (00:00:00), +color (00:00:00), +: (00:00:00), +var (00:00:00), +( (00:00:00), +- (00:00:00), +- (00:00:00), +theme (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +map (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +100 (00:00:00), +% (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +marker (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +3vw (00:00:00), +; (00:00:00), +height (00:00:00), +: (00:00:00), +3vw (00:00:00), +; (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +black (00:00:00), +; (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +50 (00:00:00), +% (00:00:00), +; (00:00:00), +outline (00:00:00), +: (00:00:00), +5px (00:00:00), +solid (00:00:00), +var (00:00:00), +( (00:00:00), +- (00:00:00), +- (00:00:00), +theme (00:00:00), +) (00:00:00), +; (00:00:00), +border (00:00:00), +: (00:00:00), +5px (00:00:00), +solid (00:00:00), +white (00:00:00), +; (00:00:00), +position (00:00:00), +: (00:00:00), +absolute (00:00:00), +; (00:00:00), +top (00:00:00), +: (00:00:00), +0 (00:00:00), +; (00:00:00), +left (00:00:00), +: (00:00:00), +0 (00:00:00), +; (00:00:00), +transform (00:00:00), +: (00:00:00), +translate (00:00:00), +( (00:00:00), +- (00:00:00), +50 (00:00:00), +% (00:00:00), +, (00:00:00), +- (00:00:00), +50 (00:00:00), +% (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +mapContainer (00:00:00), +{ (00:00:00), +position (00:00:00), +: (00:00:00), +relative (00:00:00), +; (00:00:00), +display (00:00:00), +: (00:00:00), +none (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +camera (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +100 (00:00:00), +% (00:00:00), +; (00:00:00), +} (00:00:00), +button (00:00:00), +{ (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +var (00:00:00), +( (00:00:00), +- (00:00:00), +- (00:00:00), +theme (00:00:00), +) (00:00:00), +; (00:00:00), +color (00:00:00), +: (00:00:00), +white (00:00:00), +; (00:00:00), +cursor (00:00:00), +: (00:00:00), +pointer (00:00:00), +; (00:00:00), +transition (00:00:00), +: (00:00:00), +all (00:00:00), +2s (00:00:00), +ease (00:00:00), +; (00:00:00), +} (00:00:00), +button (00:00:00), +: (00:00:00), +hover (00:00:00), +{ (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +blue (00:00:00), +; (00:00:00), +transform (00:00:00), +: (00:00:00), +scale (00:00:00), +( (00:00:00), +2 (00:00:00), +. (00:00:00), +2 (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+        <t>-black (00:01:34) ~0.17, -white (00:02:07) ~0.00, +yellow (00:00:00), +red (00:00:00), +button (00:00:00), +{ (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +var (00:00:00), +( (00:00:00), +- (00:00:00), +- (00:00:00), +theme (00:00:00), +) (00:00:00), +; (00:00:00), +color (00:00:00), +: (00:00:00), +white (00:00:00), +; (00:00:00), +cursor (00:00:00), +: (00:00:00), +pointer (00:00:00), +; (00:00:00), +transition (00:00:00), +: (00:00:00), +all (00:00:00), +2s (00:00:00), +ease (00:00:00), +; (00:00:00), +} (00:00:00), +button (00:00:00), +: (00:00:00), +hover (00:00:00), +{ (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +blue (00:00:00), +; (00:00:00), +transform (00:00:00), +: (00:00:00), +scale (00:00:00), +( (00:00:00), +2 (00:00:00), +. (00:00:00), +2 (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +inventory (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +80 (00:00:00), +% (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +family (00:00:00), +: (00:00:00), +' (00:00:00), +Times (00:00:00), +New (00:00:00), +Roman (00:00:00), +' (00:00:00), +, (00:00:00), +Times (00:00:00), +, (00:00:00), +serif (00:00:00), +, (00:00:00), +sans (00:00:00), +- (00:00:00), +serif (00:00:00), +; (00:00:00), +border (00:00:00), +: (00:00:00), +1px (00:00:00), +solid (00:00:00), +var (00:00:00), +( (00:00:00), +- (00:00:00), +- (00:00:00), +theme (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +inventory (00:00:00), +p (00:00:00), +{ (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +red (00:00:00), +; (00:00:00), +text (00:00:00), +- (00:00:00), +align (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +} (00:00:00), +: (00:00:00), +root (00:00:00), +{ (00:00:00), +- (00:00:00), +- (00:00:00), +theme (00:00:00), +: (00:00:00), +# (00:00:00), +280 (00:00:00), +; (00:00:00), +} (00:00:00), +body (00:00:00), +{ (00:00:00), +display (00:00:00), +: (00:00:00), +flex (00:00:00), +; (00:00:00), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +margin (00:00:00), +: (00:00:00), +0 (00:00:00), +; (00:00:00), +} (00:00:00), +h1 (00:00:00), +{ (00:00:00), +font (00:00:00), +- (00:00:00), +family (00:00:00), +: (00:00:00), +" (00:00:00), +Arial (00:00:00), +" (00:00:00), +; (00:00:00), +color (00:00:00), +: (00:00:00), +var (00:00:00), +( (00:00:00), +- (00:00:00), +- (00:00:00), +theme (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +map (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +100 (00:00:00), +% (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +marker (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +3vw (00:00:00), +; (00:00:00), +height (00:00:00), +: (00:00:00), +3vw (00:00:00), +; (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +yellow (00:00:00), +; (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +50 (00:00:00), +% (00:00:00), +; (00:00:00), +outline (00:00:00), +: (00:00:00), +5px (00:00:00), +solid (00:00:00), +var (00:00:00), +( (00:00:00), +- (00:00:00), +- (00:00:00), +theme (00:00:00), +) (00:00:00), +; (00:00:00), +border (00:00:00), +: (00:00:00), +5px (00:00:00), +solid (00:00:00), +red (00:00:00), +; (00:00:00), +position (00:00:00), +: (00:00:00), +absolute (00:00:00), +; (00:00:00), +top (00:00:00), +: (00:00:00), +0 (00:00:00), +; (00:00:00), +left (00:00:00), +: (00:00:00), +0 (00:00:00), +; (00:00:00), +transform (00:00:00), +: (00:00:00), +translate (00:00:00), +( (00:00:00), +- (00:00:00), +50 (00:00:00), +% (00:00:00), +, (00:00:00), +- (00:00:00), +50 (00:00:00), +% (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +mapContainer (00:00:00), +{ (00:00:00), +position (00:00:00), +: (00:00:00), +relative (00:00:00), +; (00:00:00), +display (00:00:00), +: (00:00:00), +none (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +camera (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +100 (00:00:00), +% (00:00:00), +; (00:00:00), +} (00:00:00), +button (00:00:00), +{ (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +var (00:00:00), +( (00:00:00), +- (00:00:00), +- (00:00:00), +theme (00:00:00), +) (00:00:00), +; (00:00:00), +color (00:00:00), +: (00:00:00), +white (00:00:00), +; (00:00:00), +cursor (00:00:00), +: (00:00:00), +pointer (00:00:00), +; (00:00:00), +transition (00:00:00), +: (00:00:00), +all (00:00:00), +2s (00:00:00), +ease (00:00:00), +; (00:00:00), +} (00:00:00), +button (00:00:00), +: (00:00:00), +hover (00:00:00), +{ (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +blue (00:00:00), +; (00:00:00), +transform (00:00:00), +: (00:00:00), +scale (00:00:00), +( (00:00:00), +2 (00:00:00), +. (00:00:00), +2 (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +inventory (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +80 (00:00:00), +% (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +family (00:00:00), +: (00:00:00), +' (00:00:00), +Times (00:00:00), +New (00:00:00), +Roman (00:00:00), +' (00:00:00), +, (00:00:00), +Times (00:00:00), +, (00:00:00), +serif (00:00:00), +, (00:00:00), +sans (00:00:00), +- (00:00:00), +serif (00:00:00), +; (00:00:00), +border (00:00:00), +: (00:00:00), +1px (00:00:00), +solid (00:00:00), +var (00:00:00), +( (00:00:00), +- (00:00:00), +- (00:00:00), +theme (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +inventory (00:00:00), +p (00:00:00), +{ (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +red (00:00:00), +; (00:00:00), +text (00:00:00), +- (00:00:00), +align (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +} (00:00:00), +: (00:00:00), +root (00:00:00), +{ (00:00:00), +- (00:00:00), +- (00:00:00), +theme (00:00:00), +: (00:00:00), +# (00:00:00), +280 (00:00:00), +; (00:00:00), +} (00:00:00), +body (00:00:00), +{ (00:00:00), +display (00:00:00), +: (00:00:00), +flex (00:00:00), +; (00:00:00), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +margin (00:00:00), +: (00:00:00), +0 (00:00:00), +; (00:00:00), +} (00:00:00), +h1 (00:00:00), +{ (00:00:00), +font (00:00:00), +- (00:00:00), +family (00:00:00), +: (00:00:00), +" (00:00:00), +Arial (00:00:00), +" (00:00:00), +; (00:00:00), +color (00:00:00), +: (00:00:00), +var (00:00:00), +( (00:00:00), +- (00:00:00), +- (00:00:00), +theme (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +map (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +100 (00:00:00), +% (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +marker (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +3vw (00:00:00), +; (00:00:00), +height (00:00:00), +: (00:00:00), +3vw (00:00:00), +; (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +black (00:00:00), +; (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +50 (00:00:00), +% (00:00:00), +; (00:00:00), +outline (00:00:00), +: (00:00:00), +5px (00:00:00), +solid (00:00:00), +var (00:00:00), +( (00:00:00), +- (00:00:00), +- (00:00:00), +theme (00:00:00), +) (00:00:00), +; (00:00:00), +border (00:00:00), +: (00:00:00), +5px (00:00:00), +solid (00:00:00), +white (00:00:00), +; (00:00:00), +position (00:00:00), +: (00:00:00), +absolute (00:00:00), +; (00:00:00), +top (00:00:00), +: (00:00:00), +0 (00:00:00), +; (00:00:00), +left (00:00:00), +: (00:00:00), +0 (00:00:00), +; (00:00:00), +transform (00:00:00), +: (00:00:00), +translate (00:00:00), +( (00:00:00), +- (00:00:00), +50 (00:00:00), +% (00:00:00), +, (00:00:00), +- (00:00:00), +50 (00:00:00), +% (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +mapContainer (00:00:00), +{ (00:00:00), +position (00:00:00), +: (00:00:00), +relative (00:00:00), +; (00:00:00), +display (00:00:00), +: (00:00:00), +none (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +camera (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +100 (00:00:00), +% (00:00:00), +; (00:00:00), +} (00:00:00), +button (00:00:00), +{ (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +var (00:00:00), +( (00:00:00), +- (00:00:00), +- (00:00:00), +theme (00:00:00), +) (00:00:00), +; (00:00:00), +color (00:00:00), +: (00:00:00), +white (00:00:00), +; (00:00:00), +cursor (00:00:00), +: (00:00:00), +pointer (00:00:00), +; (00:00:00), +transition (00:00:00), +: (00:00:00), +all (00:00:00), +2s (00:00:00), +ease (00:00:00), +; (00:00:00), +} (00:00:00), +button (00:00:00), +: (00:00:00), +hover (00:00:00), +{ (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +blue (00:00:00), +; (00:00:00), +transform (00:00:00), +: (00:00:00), +scale (00:00:00), +( (00:00:00), +2 (00:00:00), +. (00:00:00), +2 (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00)</t>
       </text>
     </comment>
     <comment ref="N68" authorId="0" shapeId="0">
@@ -1089,7 +1089,7 @@
     </comment>
     <comment ref="N70" authorId="0" shapeId="0">
       <text>
-        <t>-place (00:04:49), -place (00:05:00), -place (00:05:04), +data (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +item (00:00:00), +- (00:00:00), +name (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +Name (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +data (00:00:00), +. (00:00:00), +name (00:00:00), +; (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +item (00:00:00), +- (00:00:00), +stock (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +In (00:00:00), +store (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +( (00:00:00), +data (00:00:00), +. (00:00:00), +in (00:00:00), +_ (00:00:00), +store (00:00:00), +? (00:00:00), +" (00:00:00), +Yes (00:00:00), +" (00:00:00), +: (00:00:00), +" (00:00:00), +No (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +item (00:00:00), +- (00:00:00), +price (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +Price (00:00:00), +: (00:00:00), +€ (00:00:00), +" (00:00:00), ++ (00:00:00), +data (00:00:00), +. (00:00:00), +price (00:00:00), +; (00:00:00), +data (00:00:00), +data (00:00:00)</t>
+        <t>-place (00:04:49) ~0.20, -place (00:05:00) ~0.20, -place (00:05:04) ~0.20, +data (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +item (00:00:00), +- (00:00:00), +name (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +Name (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +data (00:00:00), +. (00:00:00), +name (00:00:00), +; (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +item (00:00:00), +- (00:00:00), +stock (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +In (00:00:00), +store (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +( (00:00:00), +data (00:00:00), +. (00:00:00), +in (00:00:00), +_ (00:00:00), +store (00:00:00), +? (00:00:00), +" (00:00:00), +Yes (00:00:00), +" (00:00:00), +: (00:00:00), +" (00:00:00), +No (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +item (00:00:00), +- (00:00:00), +price (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +Price (00:00:00), +: (00:00:00), +€ (00:00:00), +" (00:00:00), ++ (00:00:00), +data (00:00:00), +. (00:00:00), +price (00:00:00), +; (00:00:00), +data (00:00:00), +data (00:00:00)</t>
       </text>
     </comment>
     <comment ref="P70" authorId="0" shapeId="0">
@@ -1149,7 +1149,7 @@
     </comment>
     <comment ref="J72" authorId="0" shapeId="0">
       <text>
-        <t>-Positioning (00:07:06), -Positioning (00:07:38), +Inventory (00:00:00), +System (00:00:00), +Inventory (00:00:00), +System (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +name (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +store (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +price (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00)</t>
+        <t>-Positioning (00:07:06) ~0.09, -Positioning (00:07:38) ~0.09, +Inventory (00:00:00), +System (00:00:00), +Inventory (00:00:00), +System (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +name (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +store (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +price (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="L72" authorId="0" shapeId="0">
@@ -1159,7 +1159,7 @@
     </comment>
     <comment ref="N72" authorId="0" shapeId="0">
       <text>
-        <t>-place (00:04:49), -place (00:05:00), -place (00:05:04), +item (00:00:00), +item (00:00:00), +item (00:00:00), +showItemInfo (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +; (00:00:00), +function (00:00:00), +showItemInfo (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +{ (00:00:00), +name (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Name (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +name (00:00:00), +; (00:00:00), +store (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +In (00:00:00), +store (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +( (00:00:00), +item (00:00:00), +. (00:00:00), +in (00:00:00), +_ (00:00:00), +store (00:00:00), +? (00:00:00), +" (00:00:00), +Yes (00:00:00), +" (00:00:00), +: (00:00:00), +" (00:00:00), +No (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +price (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Price (00:00:00), +: (00:00:00), +€ (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +price (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+        <t>-place (00:04:49) ~0.00, -place (00:05:00) ~0.00, -place (00:05:04) ~0.00, +item (00:00:00), +item (00:00:00), +item (00:00:00), +showItemInfo (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +; (00:00:00), +function (00:00:00), +showItemInfo (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +{ (00:00:00), +name (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Name (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +name (00:00:00), +; (00:00:00), +store (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +In (00:00:00), +store (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +( (00:00:00), +item (00:00:00), +. (00:00:00), +in (00:00:00), +_ (00:00:00), +store (00:00:00), +? (00:00:00), +" (00:00:00), +Yes (00:00:00), +" (00:00:00), +: (00:00:00), +" (00:00:00), +No (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +price (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Price (00:00:00), +: (00:00:00), +€ (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +price (00:00:00), +; (00:00:00), +} (00:00:00)</t>
       </text>
     </comment>
     <comment ref="P72" authorId="0" shapeId="0">
@@ -1184,7 +1184,7 @@
     </comment>
     <comment ref="J73" authorId="0" shapeId="0">
       <text>
-        <t>-Positioning (00:07:06), -Positioning (00:07:38), -&lt; (00:07:43), -div (00:07:44), -id (00:07:45), -= (00:07:46), -" (00:07:47), -mapContainer (00:07:48), -" (00:07:49), -&gt; (00:07:50), -&lt; (00:07:51), -img (00:07:52), -src (00:07:53), -= (00:07:54), -" (00:07:55), -map (00:07:56), -. (00:07:57), -png (00:07:58), -" (00:07:59), -id (00:08:00), -= (00:08:01), -" (00:08:02), -map (00:08:03), -" (00:08:04), -alt (00:08:05), -= (00:08:06), -" (00:08:07), -map (00:08:08), -" (00:08:09), -/ (00:08:10), -&gt; (00:08:11), -&lt; (00:08:12), -div (00:08:13), -id (00:08:14), -= (00:08:15), -" (00:08:16), -marker (00:08:17), -" (00:08:18), -&gt; (00:08:19), -&lt; (00:08:20), -/ (00:08:21), -div (00:08:22), -&gt; (00:08:23), -&lt; (00:08:24), -/ (00:08:25), -div (00:08:26), -&gt; (00:08:27), +Inventory (00:00:00), +Inventory (00:00:00), +System (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +output (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +name (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +stock (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +price (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
+        <t>-Positioning (00:07:06) ~0.09, -Positioning (00:07:38) ~0.09, -&lt; (00:07:43), -div (00:07:44), -id (00:07:45), -= (00:07:46), -" (00:07:47), -mapContainer (00:07:48), -" (00:07:49), -&gt; (00:07:50), -&lt; (00:07:51), -img (00:07:52), -src (00:07:53), -= (00:07:54), -" (00:07:55), -map (00:07:56), -. (00:07:57), -png (00:07:58), -" (00:07:59), -id (00:08:00), -= (00:08:01), -" (00:08:02), -map (00:08:03), -" (00:08:04), -alt (00:08:05), -= (00:08:06), -" (00:08:07), -map (00:08:08), -" (00:08:09), -/ (00:08:10), -&gt; (00:08:11), -&lt; (00:08:12), -div (00:08:13), -id (00:08:14), -= (00:08:15), -" (00:08:16), -marker (00:08:17), -" (00:08:18), -&gt; (00:08:19), -&lt; (00:08:20), -/ (00:08:21), -div (00:08:22), -&gt; (00:08:23), -&lt; (00:08:24), -/ (00:08:25), -div (00:08:26), -&gt; (00:08:27), +Inventory (00:00:00), +Inventory (00:00:00), +System (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +output (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +name (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +stock (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +price (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="L73" authorId="0" shapeId="0">
@@ -1194,7 +1194,7 @@
     </comment>
     <comment ref="N73" authorId="0" shapeId="0">
       <text>
-        <t>-place (00:04:49), -showMarkerAt (00:04:58), -( (00:04:59), -place (00:05:00), -. (00:05:01), -top (00:05:02), -, (00:05:03), -place (00:05:04), -. (00:05:05), -left (00:05:06), -) (00:05:07), -; (00:05:08), -function (00:05:46), -showMarkerAt (00:05:47), -( (00:05:48), -top (00:05:49), -, (00:05:50), -left (00:05:51), -) (00:05:52), -{ (00:05:53), -marker (00:05:54), -. (00:05:55), -style (00:05:56), -. (00:05:57), -top (00:05:58), -= (00:05:59), -top (00:06:00), -; (00:06:01), -marker (00:06:02), -. (00:06:03), -style (00:06:04), -. (00:06:05), -left (00:06:06), -= (00:06:07), -left (00:06:08), -; (00:06:09), -} (00:06:10), +try (00:00:00), +{ (00:00:00), +item (00:00:00), +displayItem (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +catch (00:00:00), +( (00:00:00), +error (00:00:00), +) (00:00:00), +{ (00:00:00), +console (00:00:00), +. (00:00:00), +error (00:00:00), +( (00:00:00), +" (00:00:00), +Invalid (00:00:00), +QR (00:00:00), +data (00:00:00), +: (00:00:00), +" (00:00:00), +, (00:00:00), +error (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +function (00:00:00), +displayItem (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +nameEl (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +name (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +stockEl (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +stock (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +priceEl (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +price (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +nameEl (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +Name (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +name (00:00:00), +; (00:00:00), +stockEl (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +In (00:00:00), +store (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +( (00:00:00), +item (00:00:00), +. (00:00:00), +in (00:00:00), +_ (00:00:00), +store (00:00:00), +? (00:00:00), +" (00:00:00), +Yes (00:00:00), +" (00:00:00), +: (00:00:00), +" (00:00:00), +No (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +priceEl (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +Price (00:00:00), +: (00:00:00), +€ (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +price (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+        <t>-place (00:04:49) ~0.00, -showMarkerAt (00:04:58), -( (00:04:59), -place (00:05:00), -. (00:05:01), -top (00:05:02), -, (00:05:03), -place (00:05:04), -. (00:05:05), -left (00:05:06), -) (00:05:07), -; (00:05:08), -function (00:05:46), -showMarkerAt (00:05:47), -( (00:05:48), -top (00:05:49), -, (00:05:50), -left (00:05:51), -) (00:05:52), -{ (00:05:53), -marker (00:05:54), -. (00:05:55), -style (00:05:56), -. (00:05:57), -top (00:05:58), -= (00:05:59), -top (00:06:00), -; (00:06:01), -marker (00:06:02), -. (00:06:03), -style (00:06:04), -. (00:06:05), -left (00:06:06), -= (00:06:07), -left (00:06:08), -; (00:06:09), -} (00:06:10), +try (00:00:00), +{ (00:00:00), +item (00:00:00), +displayItem (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +catch (00:00:00), +( (00:00:00), +error (00:00:00), +) (00:00:00), +{ (00:00:00), +console (00:00:00), +. (00:00:00), +error (00:00:00), +( (00:00:00), +" (00:00:00), +Invalid (00:00:00), +QR (00:00:00), +data (00:00:00), +: (00:00:00), +" (00:00:00), +, (00:00:00), +error (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +function (00:00:00), +displayItem (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +nameEl (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +name (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +stockEl (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +stock (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +priceEl (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +price (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +nameEl (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +Name (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +name (00:00:00), +; (00:00:00), +stockEl (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +In (00:00:00), +store (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +( (00:00:00), +item (00:00:00), +. (00:00:00), +in (00:00:00), +_ (00:00:00), +store (00:00:00), +? (00:00:00), +" (00:00:00), +Yes (00:00:00), +" (00:00:00), +: (00:00:00), +" (00:00:00), +No (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +priceEl (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +Price (00:00:00), +: (00:00:00), +€ (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +price (00:00:00), +; (00:00:00), +} (00:00:00)</t>
       </text>
     </comment>
     <comment ref="P73" authorId="0" shapeId="0">
@@ -1354,7 +1354,7 @@
     </comment>
     <comment ref="L82" authorId="0" shapeId="0">
       <text>
-        <t>-3vw (00:01:28), +button (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +120px (00:00:00), +; (00:00:00), +height (00:00:00), +: (00:00:00), +50px (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +weight (00:00:00), +: (00:00:00), +bold (00:00:00), +; (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +10px (00:00:00), +; (00:00:00), +border (00:00:00), +: (00:00:00), +none (00:00:00), +; (00:00:00), +box (00:00:00), +- (00:00:00), +shadow (00:00:00), +: (00:00:00), +2px (00:00:00), +1px (00:00:00), +3px (00:00:00), +1px (00:00:00), +rgba (00:00:00), +( (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +. (00:00:00), +555 (00:00:00), +) (00:00:00), +; (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +crimson (00:00:00), +; (00:00:00), +letter (00:00:00), +- (00:00:00), +spacing (00:00:00), +: (00:00:00), +1px (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +22px (00:00:00), +; (00:00:00), +color (00:00:00), +: (00:00:00), +white (00:00:00), +; (00:00:00), +text (00:00:00), +- (00:00:00), +shadow (00:00:00), +: (00:00:00), +2px (00:00:00), +2px (00:00:00), +2px (00:00:00), +rgba (00:00:00), +( (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +. (00:00:00), +888 (00:00:00), +) (00:00:00), +; (00:00:00), +transition (00:00:00), +: (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +0 (00:00:00), +. (00:00:00), +5s (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +family (00:00:00), +: (00:00:00), +' (00:00:00), +Franklin (00:00:00), +Gothic (00:00:00), +Medium (00:00:00), +' (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +no (00:00:00), +{ (00:00:00), +margin (00:00:00), +- (00:00:00), +top (00:00:00), +: (00:00:00), +15px (00:00:00), +; (00:00:00), +width (00:00:00), +: (00:00:00), +200px (00:00:00), +; (00:00:00), +border (00:00:00), +: (00:00:00), +1px (00:00:00), +solid (00:00:00), +black (00:00:00), +; (00:00:00), +display (00:00:00), +: (00:00:00), +none (00:00:00), +; (00:00:00), +} (00:00:00), +p (00:00:00), +{ (00:00:00), +margin (00:00:00), +: (00:00:00), +0 (00:00:00), +; (00:00:00), +border (00:00:00), +: (00:00:00), +2px (00:00:00), +solid (00:00:00), +gray (00:00:00), +; (00:00:00), +justify (00:00:00), +- (00:00:00), +content (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +display (00:00:00), +: (00:00:00), +flex (00:00:00), +; (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +rgb (00:00:00), +( (00:00:00), +185 (00:00:00), +, (00:00:00), +185 (00:00:00), +, (00:00:00), +184 (00:00:00), +) (00:00:00), +; (00:00:00), +padding (00:00:00), +: (00:00:00), +15px (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +weight (00:00:00), +: (00:00:00), +bold (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +family (00:00:00), +: (00:00:00), +' (00:00:00), +Franklin (00:00:00), +Gothic (00:00:00), +Medium (00:00:00), +' (00:00:00), +; (00:00:00), +} (00:00:00), +button (00:00:00), +: (00:00:00), +hover (00:00:00), +{ (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +var (00:00:00), +( (00:00:00), +- (00:00:00), +- (00:00:00), +theme (00:00:00), +) (00:00:00), +; (00:00:00), +cursor (00:00:00), +: (00:00:00), +pointer (00:00:00), +; (00:00:00), +} (00:00:00), +3vh (00:00:00)</t>
+        <t>-3vw (00:01:28) ~0.67, +button (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +120px (00:00:00), +; (00:00:00), +height (00:00:00), +: (00:00:00), +50px (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +weight (00:00:00), +: (00:00:00), +bold (00:00:00), +; (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +10px (00:00:00), +; (00:00:00), +border (00:00:00), +: (00:00:00), +none (00:00:00), +; (00:00:00), +box (00:00:00), +- (00:00:00), +shadow (00:00:00), +: (00:00:00), +2px (00:00:00), +1px (00:00:00), +3px (00:00:00), +1px (00:00:00), +rgba (00:00:00), +( (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +. (00:00:00), +555 (00:00:00), +) (00:00:00), +; (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +crimson (00:00:00), +; (00:00:00), +letter (00:00:00), +- (00:00:00), +spacing (00:00:00), +: (00:00:00), +1px (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +22px (00:00:00), +; (00:00:00), +color (00:00:00), +: (00:00:00), +white (00:00:00), +; (00:00:00), +text (00:00:00), +- (00:00:00), +shadow (00:00:00), +: (00:00:00), +2px (00:00:00), +2px (00:00:00), +2px (00:00:00), +rgba (00:00:00), +( (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +. (00:00:00), +888 (00:00:00), +) (00:00:00), +; (00:00:00), +transition (00:00:00), +: (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +0 (00:00:00), +. (00:00:00), +5s (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +family (00:00:00), +: (00:00:00), +' (00:00:00), +Franklin (00:00:00), +Gothic (00:00:00), +Medium (00:00:00), +' (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +no (00:00:00), +{ (00:00:00), +margin (00:00:00), +- (00:00:00), +top (00:00:00), +: (00:00:00), +15px (00:00:00), +; (00:00:00), +width (00:00:00), +: (00:00:00), +200px (00:00:00), +; (00:00:00), +border (00:00:00), +: (00:00:00), +1px (00:00:00), +solid (00:00:00), +black (00:00:00), +; (00:00:00), +display (00:00:00), +: (00:00:00), +none (00:00:00), +; (00:00:00), +} (00:00:00), +p (00:00:00), +{ (00:00:00), +margin (00:00:00), +: (00:00:00), +0 (00:00:00), +; (00:00:00), +border (00:00:00), +: (00:00:00), +2px (00:00:00), +solid (00:00:00), +gray (00:00:00), +; (00:00:00), +justify (00:00:00), +- (00:00:00), +content (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +display (00:00:00), +: (00:00:00), +flex (00:00:00), +; (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +rgb (00:00:00), +( (00:00:00), +185 (00:00:00), +, (00:00:00), +185 (00:00:00), +, (00:00:00), +184 (00:00:00), +) (00:00:00), +; (00:00:00), +padding (00:00:00), +: (00:00:00), +15px (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +weight (00:00:00), +: (00:00:00), +bold (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +family (00:00:00), +: (00:00:00), +' (00:00:00), +Franklin (00:00:00), +Gothic (00:00:00), +Medium (00:00:00), +' (00:00:00), +; (00:00:00), +} (00:00:00), +button (00:00:00), +: (00:00:00), +hover (00:00:00), +{ (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +var (00:00:00), +( (00:00:00), +- (00:00:00), +- (00:00:00), +theme (00:00:00), +) (00:00:00), +; (00:00:00), +cursor (00:00:00), +: (00:00:00), +pointer (00:00:00), +; (00:00:00), +} (00:00:00), +3vh (00:00:00)</t>
       </text>
     </comment>
     <comment ref="N82" authorId="0" shapeId="0">
@@ -1379,7 +1379,7 @@
     </comment>
     <comment ref="J83" authorId="0" shapeId="0">
       <text>
-        <t>-map (00:08:08), +Map (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemInfo (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemName (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemLatitude (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemLongitude (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
+        <t>-map (00:08:08) ~0.67, +Map (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemInfo (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemName (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemLatitude (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemLongitude (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="L83" authorId="0" shapeId="0">
@@ -1414,7 +1414,7 @@
     </comment>
     <comment ref="J86" authorId="0" shapeId="0">
       <text>
-        <t>-Positioning (00:07:06), -Positioning (00:07:38), -&lt; (00:07:43), -div (00:07:44), -id (00:07:45), -= (00:07:46), -" (00:07:47), -mapContainer (00:07:48), -" (00:07:49), -&gt; (00:07:50), -&lt; (00:07:51), -img (00:07:52), -src (00:07:53), -= (00:07:54), -" (00:07:55), -map (00:07:56), -. (00:07:57), -png (00:07:58), -" (00:07:59), -id (00:08:00), -= (00:08:01), -" (00:08:02), -map (00:08:03), -" (00:08:04), -alt (00:08:05), -= (00:08:06), -" (00:08:07), -map (00:08:08), -" (00:08:09), -/ (00:08:10), -&gt; (00:08:11), -&lt; (00:08:12), -div (00:08:13), -id (00:08:14), -= (00:08:15), -" (00:08:16), -marker (00:08:17), -" (00:08:18), -&gt; (00:08:19), -&lt; (00:08:20), -/ (00:08:21), -div (00:08:22), -&gt; (00:08:23), -&lt; (00:08:24), -/ (00:08:25), -div (00:08:26), -&gt; (00:08:27), +Inventory (00:00:00), +System (00:00:00), +Inventory (00:00:00), +System (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +inventory (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemName (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Name (00:00:00), +: (00:00:00), +- (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemInStore (00:00:00), +" (00:00:00), +&gt; (00:00:00), +In (00:00:00), +store (00:00:00), +: (00:00:00), +- (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemPrice (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Price (00:00:00), +: (00:00:00), +- (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
+        <t>-Positioning (00:07:06) ~0.09, -Positioning (00:07:38) ~0.09, -&lt; (00:07:43), -div (00:07:44), -id (00:07:45), -= (00:07:46), -" (00:07:47), -mapContainer (00:07:48), -" (00:07:49), -&gt; (00:07:50), -&lt; (00:07:51), -img (00:07:52), -src (00:07:53), -= (00:07:54), -" (00:07:55), -map (00:07:56), -. (00:07:57), -png (00:07:58), -" (00:07:59), -id (00:08:00), -= (00:08:01), -" (00:08:02), -map (00:08:03), -" (00:08:04), -alt (00:08:05), -= (00:08:06), -" (00:08:07), -map (00:08:08), -" (00:08:09), -/ (00:08:10), -&gt; (00:08:11), -&lt; (00:08:12), -div (00:08:13), -id (00:08:14), -= (00:08:15), -" (00:08:16), -marker (00:08:17), -" (00:08:18), -&gt; (00:08:19), -&lt; (00:08:20), -/ (00:08:21), -div (00:08:22), -&gt; (00:08:23), -&lt; (00:08:24), -/ (00:08:25), -div (00:08:26), -&gt; (00:08:27), +Inventory (00:00:00), +System (00:00:00), +Inventory (00:00:00), +System (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +inventory (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemName (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Name (00:00:00), +: (00:00:00), +- (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemInStore (00:00:00), +" (00:00:00), +&gt; (00:00:00), +In (00:00:00), +store (00:00:00), +: (00:00:00), +- (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemPrice (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Price (00:00:00), +: (00:00:00), +- (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="L86" authorId="0" shapeId="0">
@@ -1424,7 +1424,7 @@
     </comment>
     <comment ref="N86" authorId="0" shapeId="0">
       <text>
-        <t>-mapContainer (00:03:46), -. (00:03:47), -style (00:03:48), -. (00:03:49), -display (00:03:50), -= (00:03:51), -" (00:03:52), -none (00:03:53), -" (00:03:54), -; (00:03:55), -mapContainer (00:04:11), -. (00:04:12), -style (00:04:13), -. (00:04:14), -display (00:04:15), -= (00:04:16), -" (00:04:17), -block (00:04:18), -" (00:04:19), -; (00:04:20), -place (00:04:49), -showMarkerAt (00:04:58), -( (00:04:59), -place (00:05:00), -. (00:05:01), -top (00:05:02), -, (00:05:03), -place (00:05:04), -. (00:05:05), -left (00:05:06), -) (00:05:07), -; (00:05:08), -function (00:05:46), -showMarkerAt (00:05:47), -( (00:05:48), -top (00:05:49), -, (00:05:50), -left (00:05:51), -) (00:05:52), -{ (00:05:53), -marker (00:05:54), -. (00:05:55), -style (00:05:56), -. (00:05:57), -top (00:05:58), -= (00:05:59), -top (00:06:00), -; (00:06:01), -marker (00:06:02), -. (00:06:03), -style (00:06:04), -. (00:06:05), -left (00:06:06), -= (00:06:07), -left (00:06:08), -; (00:06:09), -} (00:06:10), +item (00:00:00), +showInventoryItem (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +; (00:00:00), +. (00:00:00), +catch (00:00:00), +( (00:00:00), +function (00:00:00), +( (00:00:00), +err (00:00:00), +) (00:00:00), +{ (00:00:00), +console (00:00:00), +. (00:00:00), +error (00:00:00), +( (00:00:00), +err (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +) (00:00:00), +function (00:00:00), +showInventoryItem (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +{ (00:00:00), +itemName (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Name (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +name (00:00:00), +; (00:00:00), +if (00:00:00), +( (00:00:00), +item (00:00:00), +. (00:00:00), +in (00:00:00), +_ (00:00:00), +store (00:00:00), +) (00:00:00), +{ (00:00:00), +itemInStore (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +In (00:00:00), +store (00:00:00), +: (00:00:00), +Yes (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00), +else (00:00:00), +{ (00:00:00), +itemInStore (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +In (00:00:00), +store (00:00:00), +: (00:00:00), +No (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00), +itemPrice (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Price (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +price (00:00:00), ++ (00:00:00), +" (00:00:00), +€ (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+        <t>-mapContainer (00:03:46), -. (00:03:47), -style (00:03:48), -. (00:03:49), -display (00:03:50), -= (00:03:51), -" (00:03:52), -none (00:03:53), -" (00:03:54), -; (00:03:55), -mapContainer (00:04:11), -. (00:04:12), -style (00:04:13), -. (00:04:14), -display (00:04:15), -= (00:04:16), -" (00:04:17), -block (00:04:18), -" (00:04:19), -; (00:04:20), -place (00:04:49) ~0.00, -showMarkerAt (00:04:58), -( (00:04:59), -place (00:05:00), -. (00:05:01), -top (00:05:02), -, (00:05:03), -place (00:05:04), -. (00:05:05), -left (00:05:06), -) (00:05:07), -; (00:05:08), -function (00:05:46), -showMarkerAt (00:05:47), -( (00:05:48), -top (00:05:49), -, (00:05:50), -left (00:05:51), -) (00:05:52), -{ (00:05:53), -marker (00:05:54), -. (00:05:55), -style (00:05:56), -. (00:05:57), -top (00:05:58), -= (00:05:59), -top (00:06:00), -; (00:06:01), -marker (00:06:02), -. (00:06:03), -style (00:06:04), -. (00:06:05), -left (00:06:06), -= (00:06:07), -left (00:06:08), -; (00:06:09), -} (00:06:10), +item (00:00:00), +showInventoryItem (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +; (00:00:00), +. (00:00:00), +catch (00:00:00), +( (00:00:00), +function (00:00:00), +( (00:00:00), +err (00:00:00), +) (00:00:00), +{ (00:00:00), +console (00:00:00), +. (00:00:00), +error (00:00:00), +( (00:00:00), +err (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +) (00:00:00), +function (00:00:00), +showInventoryItem (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +{ (00:00:00), +itemName (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Name (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +name (00:00:00), +; (00:00:00), +if (00:00:00), +( (00:00:00), +item (00:00:00), +. (00:00:00), +in (00:00:00), +_ (00:00:00), +store (00:00:00), +) (00:00:00), +{ (00:00:00), +itemInStore (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +In (00:00:00), +store (00:00:00), +: (00:00:00), +Yes (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00), +else (00:00:00), +{ (00:00:00), +itemInStore (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +In (00:00:00), +store (00:00:00), +: (00:00:00), +No (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00), +itemPrice (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Price (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +price (00:00:00), ++ (00:00:00), +" (00:00:00), +€ (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00)</t>
       </text>
     </comment>
     <comment ref="P86" authorId="0" shapeId="0">
@@ -1449,17 +1449,17 @@
     </comment>
     <comment ref="J87" authorId="0" shapeId="0">
       <text>
-        <t>-QR (00:07:05), -Positioning (00:07:06), -QR (00:07:37), -Positioning (00:07:38), -&lt; (00:07:43), -div (00:07:44), -id (00:07:45), -= (00:07:46), -" (00:07:47), -mapContainer (00:07:48), -" (00:07:49), -&gt; (00:07:50), -&lt; (00:07:51), -img (00:07:52), -src (00:07:53), -= (00:07:54), -" (00:07:55), -map (00:07:56), -. (00:07:57), -png (00:07:58), -" (00:07:59), -id (00:08:00), -= (00:08:01), -" (00:08:02), -map (00:08:03), -" (00:08:04), -alt (00:08:05), -= (00:08:06), -" (00:08:07), -map (00:08:08), -" (00:08:09), -/ (00:08:10), -&gt; (00:08:11), -&lt; (00:08:12), -div (00:08:13), -id (00:08:14), -= (00:08:15), -" (00:08:16), -marker (00:08:17), -" (00:08:18), -&gt; (00:08:19), -&lt; (00:08:20), -/ (00:08:21), -div (00:08:22), -&gt; (00:08:23), -&lt; (00:08:24), -/ (00:08:25), -div (00:08:26), -&gt; (00:08:27), +Inventory (00:00:00), +Scanner (00:00:00), +Inventory (00:00:00), +Scanner (00:00:00), +&lt; (00:00:00), +section (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +inventoryCard (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemName (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Name (00:00:00), +: (00:00:00), +scan (00:00:00), +an (00:00:00), +item (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemStore (00:00:00), +" (00:00:00), +&gt; (00:00:00), +In (00:00:00), +store (00:00:00), +: (00:00:00), +- (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemPrice (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Price (00:00:00), +: (00:00:00), +- (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +section (00:00:00), +&gt; (00:00:00)</t>
+        <t>-QR (00:07:05) ~0.00, -Positioning (00:07:06) ~0.09, -QR (00:07:37) ~0.00, -Positioning (00:07:38) ~0.09, -&lt; (00:07:43), -div (00:07:44), -id (00:07:45), -= (00:07:46), -" (00:07:47), -mapContainer (00:07:48), -" (00:07:49), -&gt; (00:07:50), -&lt; (00:07:51), -img (00:07:52), -src (00:07:53), -= (00:07:54), -" (00:07:55), -map (00:07:56), -. (00:07:57), -png (00:07:58), -" (00:07:59), -id (00:08:00), -= (00:08:01), -" (00:08:02), -map (00:08:03), -" (00:08:04), -alt (00:08:05), -= (00:08:06), -" (00:08:07), -map (00:08:08), -" (00:08:09), -/ (00:08:10), -&gt; (00:08:11), -&lt; (00:08:12), -div (00:08:13), -id (00:08:14), -= (00:08:15), -" (00:08:16), -marker (00:08:17), -" (00:08:18), -&gt; (00:08:19), -&lt; (00:08:20), -/ (00:08:21), -div (00:08:22), -&gt; (00:08:23), -&lt; (00:08:24), -/ (00:08:25), -div (00:08:26), -&gt; (00:08:27), +Inventory (00:00:00), +Scanner (00:00:00), +Inventory (00:00:00), +Scanner (00:00:00), +&lt; (00:00:00), +section (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +inventoryCard (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemName (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Name (00:00:00), +: (00:00:00), +scan (00:00:00), +an (00:00:00), +item (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemStore (00:00:00), +" (00:00:00), +&gt; (00:00:00), +In (00:00:00), +store (00:00:00), +: (00:00:00), +- (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemPrice (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Price (00:00:00), +: (00:00:00), +- (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +section (00:00:00), +&gt; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="L87" authorId="0" shapeId="0">
       <text>
-        <t>-font (00:00:42), -- (00:00:43), -family (00:00:44), -: (00:00:45), -" (00:00:46), -Arial (00:00:47), -" (00:00:48), -; (00:00:49), -# (00:01:00), -map (00:01:01), -{ (00:01:02), -width (00:01:03), -: (00:01:04), -100 (00:01:05), -% (00:01:06), -; (00:01:07), -} (00:01:08), -# (00:01:09), -marker (00:01:10), -{ (00:01:11), -width (00:01:12), -: (00:01:13), -3vw (00:01:14), -; (00:01:15), -height (00:01:26), -: (00:01:27), -3vw (00:01:28), -; (00:01:29), -background (00:01:30), -- (00:01:31), -color (00:01:32), -: (00:01:33), -black (00:01:34), -; (00:01:35), -border (00:01:36), -- (00:01:37), -radius (00:01:38), -: (00:01:39), -50 (00:01:40), -% (00:01:41), -; (00:01:42), -outline (00:01:43), -: (00:01:44), -5px (00:01:45), -solid (00:01:46), -var (00:01:47), -( (00:01:48), -- (00:01:49), -- (00:01:50), -theme (00:01:51), -) (00:01:52), -; (00:01:53), -border (00:02:03), -: (00:02:04), -5px (00:02:05), -solid (00:02:06), -white (00:02:07), -; (00:02:08), -position (00:02:16), -: (00:02:17), -absolute (00:02:18), -; (00:02:19), -top (00:02:20), -: (00:02:21), -0 (00:02:22), -; (00:02:23), -left (00:02:24), -: (00:02:25), -0 (00:02:26), -; (00:02:27), -transform (00:02:28), -: (00:02:29), -translate (00:02:30), -( (00:02:31), -- (00:02:32), -50 (00:02:33), -% (00:02:34), -, (00:02:35), -- (00:02:36), -50 (00:02:37), -% (00:02:38), -) (00:02:39), -; (00:02:40), -} (00:02:41), -# (00:02:42), -mapContainer (00:02:43), -{ (00:02:44), -position (00:02:45), -: (00:02:46), -relative (00:02:47), -; (00:02:48), -display (00:02:49), -: (00:02:50), -none (00:02:51), -; (00:02:52), -} (00:02:53), -100 (00:02:59), +gap (00:00:00), +: (00:00:00), +20px (00:00:00), +; (00:00:00), +min (00:00:00), +- (00:00:00), +height (00:00:00), +: (00:00:00), +100vh (00:00:00), +; (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +f4f7f2 (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +family (00:00:00), +: (00:00:00), +Arial (00:00:00), +, (00:00:00), +sans (00:00:00), +- (00:00:00), +serif (00:00:00), +; (00:00:00), +} (00:00:00), +margin (00:00:00), +- (00:00:00), +top (00:00:00), +: (00:00:00), +40px (00:00:00), +; (00:00:00), +# (00:00:00), +inventoryCard (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +min (00:00:00), +( (00:00:00), +90 (00:00:00), +% (00:00:00), +, (00:00:00), +420px (00:00:00), +) (00:00:00), +; (00:00:00), +padding (00:00:00), +: (00:00:00), +24px (00:00:00), +; (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +white (00:00:00), +; (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +18px (00:00:00), +; (00:00:00), +box (00:00:00), +- (00:00:00), +shadow (00:00:00), +: (00:00:00), +0 (00:00:00), +10px (00:00:00), +25px (00:00:00), +rgba (00:00:00), +( (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +. (00:00:00), +12 (00:00:00), +) (00:00:00), +; (00:00:00), +border (00:00:00), +- (00:00:00), +top (00:00:00), +: (00:00:00), +6px (00:00:00), +solid (00:00:00), +var (00:00:00), +( (00:00:00), +- (00:00:00), +- (00:00:00), +theme (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +inventoryCard (00:00:00), +p (00:00:00), +{ (00:00:00), +margin (00:00:00), +: (00:00:00), +12px (00:00:00), +0 (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +1 (00:00:00), +. (00:00:00), +2rem (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +btn (00:00:00), +{ (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +var (00:00:00), +( (00:00:00), +- (00:00:00), +- (00:00:00), +theme (00:00:00), +) (00:00:00), +; (00:00:00), +color (00:00:00), +: (00:00:00), +white (00:00:00), +; (00:00:00), +padding (00:00:00), +: (00:00:00), +14px (00:00:00), +34px (00:00:00), +; (00:00:00), +border (00:00:00), +: (00:00:00), +none (00:00:00), +; (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +999px (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +1rem (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +weight (00:00:00), +: (00:00:00), +bold (00:00:00), +; (00:00:00), +letter (00:00:00), +- (00:00:00), +spacing (00:00:00), +: (00:00:00), +1px (00:00:00), +; (00:00:00), +box (00:00:00), +- (00:00:00), +shadow (00:00:00), +: (00:00:00), +0 (00:00:00), +8px (00:00:00), +18px (00:00:00), +rgba (00:00:00), +( (00:00:00), +34 (00:00:00), +, (00:00:00), +136 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +. (00:00:00), +3 (00:00:00), +) (00:00:00), +; (00:00:00), +transition (00:00:00), +: (00:00:00), +transform (00:00:00), +0 (00:00:00), +. (00:00:00), +2s (00:00:00), +ease (00:00:00), +, (00:00:00), +box (00:00:00), +- (00:00:00), +shadow (00:00:00), +0 (00:00:00), +. (00:00:00), +2s (00:00:00), +ease (00:00:00), +, (00:00:00), +filter (00:00:00), +0 (00:00:00), +. (00:00:00), +2s (00:00:00), +ease (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +btn (00:00:00), +: (00:00:00), +hover (00:00:00), +{ (00:00:00), +cursor (00:00:00), +: (00:00:00), +pointer (00:00:00), +; (00:00:00), +transform (00:00:00), +: (00:00:00), +translateY (00:00:00), +( (00:00:00), +- (00:00:00), +3px (00:00:00), +) (00:00:00), +; (00:00:00), +filter (00:00:00), +: (00:00:00), +brightness (00:00:00), +( (00:00:00), +1 (00:00:00), +. (00:00:00), +15 (00:00:00), +) (00:00:00), +; (00:00:00), +box (00:00:00), +- (00:00:00), +shadow (00:00:00), +: (00:00:00), +0 (00:00:00), +12px (00:00:00), +24px (00:00:00), +rgba (00:00:00), +( (00:00:00), +34 (00:00:00), +, (00:00:00), +136 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +. (00:00:00), +45 (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +min (00:00:00), +( (00:00:00), +90 (00:00:00), +, (00:00:00), +500px (00:00:00), +) (00:00:00)</t>
+        <t>-font (00:00:42), -- (00:00:43), -family (00:00:44), -: (00:00:45), -" (00:00:46), -Arial (00:00:47), -" (00:00:48), -; (00:00:49), -# (00:01:00), -map (00:01:01), -{ (00:01:02), -width (00:01:03), -: (00:01:04), -100 (00:01:05), -% (00:01:06), -; (00:01:07), -} (00:01:08), -# (00:01:09), -marker (00:01:10), -{ (00:01:11), -width (00:01:12), -: (00:01:13), -3vw (00:01:14), -; (00:01:15), -height (00:01:26), -: (00:01:27), -3vw (00:01:28), -; (00:01:29), -background (00:01:30), -- (00:01:31), -color (00:01:32), -: (00:01:33), -black (00:01:34), -; (00:01:35), -border (00:01:36), -- (00:01:37), -radius (00:01:38), -: (00:01:39), -50 (00:01:40), -% (00:01:41), -; (00:01:42), -outline (00:01:43), -: (00:01:44), -5px (00:01:45), -solid (00:01:46), -var (00:01:47), -( (00:01:48), -- (00:01:49), -- (00:01:50), -theme (00:01:51), -) (00:01:52), -; (00:01:53), -border (00:02:03), -: (00:02:04), -5px (00:02:05), -solid (00:02:06), -white (00:02:07), -; (00:02:08), -position (00:02:16), -: (00:02:17), -absolute (00:02:18), -; (00:02:19), -top (00:02:20), -: (00:02:21), -0 (00:02:22), -; (00:02:23), -left (00:02:24), -: (00:02:25), -0 (00:02:26), -; (00:02:27), -transform (00:02:28), -: (00:02:29), -translate (00:02:30), -( (00:02:31), -- (00:02:32), -50 (00:02:33), -% (00:02:34), -, (00:02:35), -- (00:02:36), -50 (00:02:37), -% (00:02:38), -) (00:02:39), -; (00:02:40), -} (00:02:41), -# (00:02:42), -mapContainer (00:02:43), -{ (00:02:44), -position (00:02:45), -: (00:02:46), -relative (00:02:47), -; (00:02:48), -display (00:02:49), -: (00:02:50), -none (00:02:51), -; (00:02:52), -} (00:02:53), -100 (00:02:59) ~0.33, +gap (00:00:00), +: (00:00:00), +20px (00:00:00), +; (00:00:00), +min (00:00:00), +- (00:00:00), +height (00:00:00), +: (00:00:00), +100vh (00:00:00), +; (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +f4f7f2 (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +family (00:00:00), +: (00:00:00), +Arial (00:00:00), +, (00:00:00), +sans (00:00:00), +- (00:00:00), +serif (00:00:00), +; (00:00:00), +} (00:00:00), +margin (00:00:00), +- (00:00:00), +top (00:00:00), +: (00:00:00), +40px (00:00:00), +; (00:00:00), +# (00:00:00), +inventoryCard (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +min (00:00:00), +( (00:00:00), +90 (00:00:00), +% (00:00:00), +, (00:00:00), +420px (00:00:00), +) (00:00:00), +; (00:00:00), +padding (00:00:00), +: (00:00:00), +24px (00:00:00), +; (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +white (00:00:00), +; (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +18px (00:00:00), +; (00:00:00), +box (00:00:00), +- (00:00:00), +shadow (00:00:00), +: (00:00:00), +0 (00:00:00), +10px (00:00:00), +25px (00:00:00), +rgba (00:00:00), +( (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +. (00:00:00), +12 (00:00:00), +) (00:00:00), +; (00:00:00), +border (00:00:00), +- (00:00:00), +top (00:00:00), +: (00:00:00), +6px (00:00:00), +solid (00:00:00), +var (00:00:00), +( (00:00:00), +- (00:00:00), +- (00:00:00), +theme (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +inventoryCard (00:00:00), +p (00:00:00), +{ (00:00:00), +margin (00:00:00), +: (00:00:00), +12px (00:00:00), +0 (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +1 (00:00:00), +. (00:00:00), +2rem (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +btn (00:00:00), +{ (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +var (00:00:00), +( (00:00:00), +- (00:00:00), +- (00:00:00), +theme (00:00:00), +) (00:00:00), +; (00:00:00), +color (00:00:00), +: (00:00:00), +white (00:00:00), +; (00:00:00), +padding (00:00:00), +: (00:00:00), +14px (00:00:00), +34px (00:00:00), +; (00:00:00), +border (00:00:00), +: (00:00:00), +none (00:00:00), +; (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +999px (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +1rem (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +weight (00:00:00), +: (00:00:00), +bold (00:00:00), +; (00:00:00), +letter (00:00:00), +- (00:00:00), +spacing (00:00:00), +: (00:00:00), +1px (00:00:00), +; (00:00:00), +box (00:00:00), +- (00:00:00), +shadow (00:00:00), +: (00:00:00), +0 (00:00:00), +8px (00:00:00), +18px (00:00:00), +rgba (00:00:00), +( (00:00:00), +34 (00:00:00), +, (00:00:00), +136 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +. (00:00:00), +3 (00:00:00), +) (00:00:00), +; (00:00:00), +transition (00:00:00), +: (00:00:00), +transform (00:00:00), +0 (00:00:00), +. (00:00:00), +2s (00:00:00), +ease (00:00:00), +, (00:00:00), +box (00:00:00), +- (00:00:00), +shadow (00:00:00), +0 (00:00:00), +. (00:00:00), +2s (00:00:00), +ease (00:00:00), +, (00:00:00), +filter (00:00:00), +0 (00:00:00), +. (00:00:00), +2s (00:00:00), +ease (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +btn (00:00:00), +: (00:00:00), +hover (00:00:00), +{ (00:00:00), +cursor (00:00:00), +: (00:00:00), +pointer (00:00:00), +; (00:00:00), +transform (00:00:00), +: (00:00:00), +translateY (00:00:00), +( (00:00:00), +- (00:00:00), +3px (00:00:00), +) (00:00:00), +; (00:00:00), +filter (00:00:00), +: (00:00:00), +brightness (00:00:00), +( (00:00:00), +1 (00:00:00), +. (00:00:00), +15 (00:00:00), +) (00:00:00), +; (00:00:00), +box (00:00:00), +- (00:00:00), +shadow (00:00:00), +: (00:00:00), +0 (00:00:00), +12px (00:00:00), +24px (00:00:00), +rgba (00:00:00), +( (00:00:00), +34 (00:00:00), +, (00:00:00), +136 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +. (00:00:00), +45 (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +min (00:00:00), +( (00:00:00), +90 (00:00:00), +, (00:00:00), +500px (00:00:00), +) (00:00:00)</t>
       </text>
     </comment>
     <comment ref="N87" authorId="0" shapeId="0">
       <text>
-        <t>-mapContainer (00:03:46), -. (00:03:47), -style (00:03:48), -. (00:03:49), -display (00:03:50), -= (00:03:51), -" (00:03:52), -none (00:03:53), -" (00:03:54), -; (00:03:55), -mapContainer (00:04:11), -. (00:04:12), -style (00:04:13), -. (00:04:14), -display (00:04:15), -= (00:04:16), -" (00:04:17), -block (00:04:18), -" (00:04:19), -; (00:04:20), -place (00:04:49), -showMarkerAt (00:04:58), -( (00:04:59), -place (00:05:00), -. (00:05:01), -top (00:05:02), -, (00:05:03), -place (00:05:04), -. (00:05:05), -left (00:05:06), -) (00:05:07), -; (00:05:08), -function (00:05:46), -showMarkerAt (00:05:47), -( (00:05:48), -top (00:05:49), -, (00:05:50), -left (00:05:51), -) (00:05:52), -{ (00:05:53), -marker (00:05:54), -. (00:05:55), -style (00:05:56), -. (00:05:57), -top (00:05:58), -= (00:05:59), -top (00:06:00), -; (00:06:01), -marker (00:06:02), -. (00:06:03), -style (00:06:04), -. (00:06:05), -left (00:06:06), -= (00:06:07), -left (00:06:08), -; (00:06:09), -} (00:06:10), +item (00:00:00), +showInventoryItem (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +; (00:00:00), +. (00:00:00), +catch (00:00:00), +( (00:00:00), +function (00:00:00), +( (00:00:00), +err (00:00:00), +) (00:00:00), +{ (00:00:00), +console (00:00:00), +. (00:00:00), +error (00:00:00), +( (00:00:00), +err (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +) (00:00:00), +function (00:00:00), +showInventoryItem (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +{ (00:00:00), +itemName (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Name (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +name (00:00:00), +; (00:00:00), +if (00:00:00), +( (00:00:00), +item (00:00:00), +. (00:00:00), +in (00:00:00), +_ (00:00:00), +store (00:00:00), +) (00:00:00), +{ (00:00:00), +itemStore (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +In (00:00:00), +store (00:00:00), +: (00:00:00), +yes (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00), +else (00:00:00), +{ (00:00:00), +itemStore (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +In (00:00:00), +store (00:00:00), +: (00:00:00), +no (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00), +itemPrice (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Price (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +price (00:00:00), ++ (00:00:00), +" (00:00:00), +€ (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+        <t>-mapContainer (00:03:46), -. (00:03:47), -style (00:03:48), -. (00:03:49), -display (00:03:50), -= (00:03:51), -" (00:03:52), -none (00:03:53), -" (00:03:54), -; (00:03:55), -mapContainer (00:04:11), -. (00:04:12), -style (00:04:13), -. (00:04:14), -display (00:04:15), -= (00:04:16), -" (00:04:17), -block (00:04:18), -" (00:04:19), -; (00:04:20), -place (00:04:49) ~0.00, -showMarkerAt (00:04:58), -( (00:04:59), -place (00:05:00), -. (00:05:01), -top (00:05:02), -, (00:05:03), -place (00:05:04), -. (00:05:05), -left (00:05:06), -) (00:05:07), -; (00:05:08), -function (00:05:46), -showMarkerAt (00:05:47), -( (00:05:48), -top (00:05:49), -, (00:05:50), -left (00:05:51), -) (00:05:52), -{ (00:05:53), -marker (00:05:54), -. (00:05:55), -style (00:05:56), -. (00:05:57), -top (00:05:58), -= (00:05:59), -top (00:06:00), -; (00:06:01), -marker (00:06:02), -. (00:06:03), -style (00:06:04), -. (00:06:05), -left (00:06:06), -= (00:06:07), -left (00:06:08), -; (00:06:09), -} (00:06:10), +item (00:00:00), +showInventoryItem (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +; (00:00:00), +. (00:00:00), +catch (00:00:00), +( (00:00:00), +function (00:00:00), +( (00:00:00), +err (00:00:00), +) (00:00:00), +{ (00:00:00), +console (00:00:00), +. (00:00:00), +error (00:00:00), +( (00:00:00), +err (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +) (00:00:00), +function (00:00:00), +showInventoryItem (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +{ (00:00:00), +itemName (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Name (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +name (00:00:00), +; (00:00:00), +if (00:00:00), +( (00:00:00), +item (00:00:00), +. (00:00:00), +in (00:00:00), +_ (00:00:00), +store (00:00:00), +) (00:00:00), +{ (00:00:00), +itemStore (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +In (00:00:00), +store (00:00:00), +: (00:00:00), +yes (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00), +else (00:00:00), +{ (00:00:00), +itemStore (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +In (00:00:00), +store (00:00:00), +: (00:00:00), +no (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00), +itemPrice (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Price (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +price (00:00:00), ++ (00:00:00), +" (00:00:00), +€ (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00)</t>
       </text>
     </comment>
     <comment ref="P87" authorId="0" shapeId="0">
@@ -1519,7 +1519,7 @@
     </comment>
     <comment ref="J89" authorId="0" shapeId="0">
       <text>
-        <t>-QR (00:07:05), -Positioning (00:07:06), -QR (00:07:37), -Positioning (00:07:38), -&lt; (00:07:43), -div (00:07:44), -id (00:07:45), -= (00:07:46), -" (00:07:47), -mapContainer (00:07:48), -" (00:07:49), -&gt; (00:07:50), -&lt; (00:07:51), -img (00:07:52), -src (00:07:53), -= (00:07:54), -" (00:07:55), -map (00:07:56), -. (00:07:57), -png (00:07:58), -" (00:07:59), -id (00:08:00), -= (00:08:01), -" (00:08:02), -map (00:08:03), -" (00:08:04), -alt (00:08:05), -= (00:08:06), -" (00:08:07), -map (00:08:08), -" (00:08:09), -/ (00:08:10), -&gt; (00:08:11), -&lt; (00:08:12), -div (00:08:13), -id (00:08:14), -= (00:08:15), -" (00:08:16), -marker (00:08:17), -" (00:08:18), -&gt; (00:08:19), -&lt; (00:08:20), -/ (00:08:21), -div (00:08:22), -&gt; (00:08:23), -&lt; (00:08:24), -/ (00:08:25), -div (00:08:26), -&gt; (00:08:27), +Inventory (00:00:00), +System (00:00:00), +Inventory (00:00:00), +System (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +inventory (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +name (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +stock (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +price (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
+        <t>-QR (00:07:05) ~0.00, -Positioning (00:07:06) ~0.18, -QR (00:07:37) ~0.00, -Positioning (00:07:38) ~0.18, -&lt; (00:07:43), -div (00:07:44), -id (00:07:45), -= (00:07:46), -" (00:07:47), -mapContainer (00:07:48), -" (00:07:49), -&gt; (00:07:50), -&lt; (00:07:51), -img (00:07:52), -src (00:07:53), -= (00:07:54), -" (00:07:55), -map (00:07:56), -. (00:07:57), -png (00:07:58), -" (00:07:59), -id (00:08:00), -= (00:08:01), -" (00:08:02), -map (00:08:03), -" (00:08:04), -alt (00:08:05), -= (00:08:06), -" (00:08:07), -map (00:08:08), -" (00:08:09), -/ (00:08:10), -&gt; (00:08:11), -&lt; (00:08:12), -div (00:08:13), -id (00:08:14), -= (00:08:15), -" (00:08:16), -marker (00:08:17), -" (00:08:18), -&gt; (00:08:19), -&lt; (00:08:20), -/ (00:08:21), -div (00:08:22), -&gt; (00:08:23), -&lt; (00:08:24), -/ (00:08:25), -div (00:08:26), -&gt; (00:08:27), +Inventory (00:00:00), +System (00:00:00), +Inventory (00:00:00), +System (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +inventory (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +name (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +stock (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +price (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="L89" authorId="0" shapeId="0">
@@ -1529,7 +1529,7 @@
     </comment>
     <comment ref="N89" authorId="0" shapeId="0">
       <text>
-        <t>-mapContainer (00:03:46), -mapContainer (00:04:11), -place (00:04:49), -showMarkerAt (00:04:58), -( (00:04:59), -place (00:05:00), -. (00:05:01), -top (00:05:02), -, (00:05:03), -place (00:05:04), -. (00:05:05), -left (00:05:06), -) (00:05:07), -; (00:05:08), -function (00:05:46), -showMarkerAt (00:05:47), -( (00:05:48), -top (00:05:49), -, (00:05:50), -left (00:05:51), -) (00:05:52), -{ (00:05:53), -marker (00:05:54), -. (00:05:55), -style (00:05:56), -. (00:05:57), -top (00:05:58), -= (00:05:59), -top (00:06:00), -; (00:06:01), -marker (00:06:02), -. (00:06:03), -style (00:06:04), -. (00:06:05), -left (00:06:06), -= (00:06:07), -left (00:06:08), -; (00:06:09), -} (00:06:10), +inventory (00:00:00), +inventory (00:00:00), +item (00:00:00), +showItem (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +; (00:00:00), +function (00:00:00), +showItem (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +{ (00:00:00), +name (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Name (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +name (00:00:00), +; (00:00:00), +stock (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +item (00:00:00), +. (00:00:00), +in (00:00:00), +_ (00:00:00), +store (00:00:00), +? (00:00:00), +" (00:00:00), +In (00:00:00), +store (00:00:00), +: (00:00:00), +yes (00:00:00), +" (00:00:00), +: (00:00:00), +" (00:00:00), +In (00:00:00), +store (00:00:00), +: (00:00:00), +no (00:00:00), +" (00:00:00), +; (00:00:00), +price (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Price (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +price (00:00:00), ++ (00:00:00), +" (00:00:00), +€ (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+        <t>-mapContainer (00:03:46) ~0.17, -mapContainer (00:04:11) ~0.17, -place (00:04:49) ~0.00, -showMarkerAt (00:04:58), -( (00:04:59), -place (00:05:00), -. (00:05:01), -top (00:05:02), -, (00:05:03), -place (00:05:04), -. (00:05:05), -left (00:05:06), -) (00:05:07), -; (00:05:08), -function (00:05:46), -showMarkerAt (00:05:47), -( (00:05:48), -top (00:05:49), -, (00:05:50), -left (00:05:51), -) (00:05:52), -{ (00:05:53), -marker (00:05:54), -. (00:05:55), -style (00:05:56), -. (00:05:57), -top (00:05:58), -= (00:05:59), -top (00:06:00), -; (00:06:01), -marker (00:06:02), -. (00:06:03), -style (00:06:04), -. (00:06:05), -left (00:06:06), -= (00:06:07), -left (00:06:08), -; (00:06:09), -} (00:06:10), +inventory (00:00:00), +inventory (00:00:00), +item (00:00:00), +showItem (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +; (00:00:00), +function (00:00:00), +showItem (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +{ (00:00:00), +name (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Name (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +name (00:00:00), +; (00:00:00), +stock (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +item (00:00:00), +. (00:00:00), +in (00:00:00), +_ (00:00:00), +store (00:00:00), +? (00:00:00), +" (00:00:00), +In (00:00:00), +store (00:00:00), +: (00:00:00), +yes (00:00:00), +" (00:00:00), +: (00:00:00), +" (00:00:00), +In (00:00:00), +store (00:00:00), +: (00:00:00), +no (00:00:00), +" (00:00:00), +; (00:00:00), +price (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Price (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +price (00:00:00), ++ (00:00:00), +" (00:00:00), +€ (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00)</t>
       </text>
     </comment>
     <comment ref="P89" authorId="0" shapeId="0">
@@ -1574,7 +1574,7 @@
     </comment>
     <comment ref="D91" authorId="0" shapeId="0">
       <text>
-        <t>Student number not found, Short name part(s) not auto-redacted (verify manually): v3, DOCX: cleared author metadata (answer.docx), Unexpected file type: map.png</t>
+        <t>Student number not found, Short name part(s) not auto-redacted, DOCX: cleared author metadata (answer.docx), Unexpected file type: map.png</t>
       </text>
     </comment>
     <comment ref="E91" authorId="0" shapeId="0">
@@ -1589,7 +1589,7 @@
     </comment>
     <comment ref="J91" authorId="0" shapeId="0">
       <text>
-        <t>-Positioning (00:07:06), -Positioning (00:07:38), -onclick (00:08:35), -= (00:08:36), -" (00:08:37), -toggleScanner (00:08:38), -( (00:08:39), -) (00:08:40), -" (00:08:41), +, (00:00:00), +user (00:00:00), +- (00:00:00), +scalable (00:00:00), += (00:00:00), +yes (00:00:00), +Inventory (00:00:00), +System (00:00:00), +📦 (00:00:00), +Inventory (00:00:00), +System (00:00:00), +store (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +inventoryPanel (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +inventoryHeader (00:00:00), +" (00:00:00), +&gt; (00:00:00), +📋 (00:00:00), +PRODUCT (00:00:00), +DETAILS (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +inventoryInfo (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +info (00:00:00), +- (00:00:00), +placeholder (00:00:00), +" (00:00:00), +&gt; (00:00:00), +🔍 (00:00:00), +Scan (00:00:00), +a (00:00:00), +QR (00:00:00), +code (00:00:00), +to (00:00:00), +see (00:00:00), +inventory (00:00:00), +data (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +scan (00:00:00), +- (00:00:00), +button (00:00:00), +" (00:00:00), +📷 (00:00:00), +QR (00:00:00), +@ (00:00:00), +2 (00:00:00), +. (00:00:00), +3 (00:00:00), +. (00:00:00), +8 (00:00:00), +/ (00:00:00), +html5 (00:00:00), +- (00:00:00), +qrcode (00:00:00), +. (00:00:00), +min (00:00:00), +. (00:00:00), +js (00:00:00)</t>
+        <t>-Positioning (00:07:06) ~0.09, -Positioning (00:07:38) ~0.09, -onclick (00:08:35), -= (00:08:36), -" (00:08:37), -toggleScanner (00:08:38), -( (00:08:39), -) (00:08:40), -" (00:08:41), +, (00:00:00), +user (00:00:00), +- (00:00:00), +scalable (00:00:00), += (00:00:00), +yes (00:00:00), +Inventory (00:00:00), +System (00:00:00), +📦 (00:00:00), +Inventory (00:00:00), +System (00:00:00), +store (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +inventoryPanel (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +inventoryHeader (00:00:00), +" (00:00:00), +&gt; (00:00:00), +📋 (00:00:00), +PRODUCT (00:00:00), +DETAILS (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +inventoryInfo (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +info (00:00:00), +- (00:00:00), +placeholder (00:00:00), +" (00:00:00), +&gt; (00:00:00), +🔍 (00:00:00), +Scan (00:00:00), +a (00:00:00), +QR (00:00:00), +code (00:00:00), +to (00:00:00), +see (00:00:00), +inventory (00:00:00), +data (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +scan (00:00:00), +- (00:00:00), +button (00:00:00), +" (00:00:00), +📷 (00:00:00), +QR (00:00:00), +@ (00:00:00), +2 (00:00:00), +. (00:00:00), +3 (00:00:00), +. (00:00:00), +8 (00:00:00), +/ (00:00:00), +html5 (00:00:00), +- (00:00:00), +qrcode (00:00:00), +. (00:00:00), +min (00:00:00), +. (00:00:00), +js (00:00:00)</t>
       </text>
     </comment>
     <comment ref="L91" authorId="0" shapeId="0">
@@ -1659,7 +1659,7 @@
     </comment>
     <comment ref="J93" authorId="0" shapeId="0">
       <text>
-        <t>-QR (00:07:05), -Positioning (00:07:06), -QR (00:07:37), -Positioning (00:07:38), -&lt; (00:07:43), -div (00:07:44), -id (00:07:45), -= (00:07:46), -" (00:07:47), -mapContainer (00:07:48), -" (00:07:49), -&gt; (00:07:50), -&lt; (00:07:51), -img (00:07:52), -src (00:07:53), -= (00:07:54), -" (00:07:55), -map (00:07:56), -. (00:07:57), -png (00:07:58), -" (00:07:59), -id (00:08:00), -= (00:08:01), -" (00:08:02), -map (00:08:03), -" (00:08:04), -alt (00:08:05), -= (00:08:06), -" (00:08:07), -map (00:08:08), -" (00:08:09), -/ (00:08:10), -&gt; (00:08:11), -&lt; (00:08:12), -div (00:08:13), -id (00:08:14), -= (00:08:15), -" (00:08:16), -marker (00:08:17), -" (00:08:18), -&gt; (00:08:19), -&lt; (00:08:20), -/ (00:08:21), -div (00:08:22), -&gt; (00:08:23), -&lt; (00:08:24), -/ (00:08:25), -div (00:08:26), -&gt; (00:08:27), +Inventory (00:00:00), +Scanner (00:00:00), +Inventory (00:00:00), +Scanner (00:00:00), +ITEM (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +inventory (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemName (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Name (00:00:00), +: (00:00:00), +- (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemStore (00:00:00), +" (00:00:00), +&gt; (00:00:00), +In (00:00:00), +store (00:00:00), +: (00:00:00), +- (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemPrice (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Price (00:00:00), +: (00:00:00), +- (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
+        <t>-QR (00:07:05) ~0.00, -Positioning (00:07:06) ~0.09, -QR (00:07:37) ~0.00, -Positioning (00:07:38) ~0.09, -&lt; (00:07:43), -div (00:07:44), -id (00:07:45), -= (00:07:46), -" (00:07:47), -mapContainer (00:07:48), -" (00:07:49), -&gt; (00:07:50), -&lt; (00:07:51), -img (00:07:52), -src (00:07:53), -= (00:07:54), -" (00:07:55), -map (00:07:56), -. (00:07:57), -png (00:07:58), -" (00:07:59), -id (00:08:00), -= (00:08:01), -" (00:08:02), -map (00:08:03), -" (00:08:04), -alt (00:08:05), -= (00:08:06), -" (00:08:07), -map (00:08:08), -" (00:08:09), -/ (00:08:10), -&gt; (00:08:11), -&lt; (00:08:12), -div (00:08:13), -id (00:08:14), -= (00:08:15), -" (00:08:16), -marker (00:08:17), -" (00:08:18), -&gt; (00:08:19), -&lt; (00:08:20), -/ (00:08:21), -div (00:08:22), -&gt; (00:08:23), -&lt; (00:08:24), -/ (00:08:25), -div (00:08:26), -&gt; (00:08:27), +Inventory (00:00:00), +Scanner (00:00:00), +Inventory (00:00:00), +Scanner (00:00:00), +ITEM (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +inventory (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemName (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Name (00:00:00), +: (00:00:00), +- (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemStore (00:00:00), +" (00:00:00), +&gt; (00:00:00), +In (00:00:00), +store (00:00:00), +: (00:00:00), +- (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemPrice (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Price (00:00:00), +: (00:00:00), +- (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="L93" authorId="0" shapeId="0">
@@ -1669,7 +1669,7 @@
     </comment>
     <comment ref="N93" authorId="0" shapeId="0">
       <text>
-        <t>-mapContainer (00:03:46), -. (00:03:47), -style (00:03:48), -. (00:03:49), -display (00:03:50), -= (00:03:51), -" (00:03:52), -none (00:03:53), -" (00:03:54), -; (00:03:55), -mapContainer (00:04:11), -. (00:04:12), -style (00:04:13), -. (00:04:14), -display (00:04:15), -= (00:04:16), -" (00:04:17), -block (00:04:18), -" (00:04:19), -; (00:04:20), -place (00:04:49), -showMarkerAt (00:04:58), -( (00:04:59), -place (00:05:00), -. (00:05:01), -top (00:05:02), -, (00:05:03), -place (00:05:04), -. (00:05:05), -left (00:05:06), -) (00:05:07), -; (00:05:08), -function (00:05:46), -showMarkerAt (00:05:47), -( (00:05:48), -top (00:05:49), -, (00:05:50), -left (00:05:51), -) (00:05:52), -{ (00:05:53), -marker (00:05:54), -. (00:05:55), -style (00:05:56), -. (00:05:57), -top (00:05:58), -= (00:05:59), -top (00:06:00), -; (00:06:01), -marker (00:06:02), -. (00:06:03), -style (00:06:04), -. (00:06:05), -left (00:06:06), -= (00:06:07), -left (00:06:08), -; (00:06:09), -} (00:06:10), +ITEM (00:00:00), +item (00:00:00), +showInventoryItem (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +; (00:00:00), +function (00:00:00), +showInventoryItem (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +{ (00:00:00), +itemName (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Name (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +name (00:00:00), +; (00:00:00), +itemStore (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +In (00:00:00), +store (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +( (00:00:00), +item (00:00:00), +. (00:00:00), +inStock (00:00:00), +? (00:00:00), +" (00:00:00), +yes (00:00:00), +" (00:00:00), +: (00:00:00), +" (00:00:00), +no (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +itemPrice (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Price (00:00:00), +: (00:00:00), +€ (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +price (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+        <t>-mapContainer (00:03:46), -. (00:03:47), -style (00:03:48), -. (00:03:49), -display (00:03:50), -= (00:03:51), -" (00:03:52), -none (00:03:53), -" (00:03:54), -; (00:03:55), -mapContainer (00:04:11), -. (00:04:12), -style (00:04:13), -. (00:04:14), -display (00:04:15), -= (00:04:16), -" (00:04:17), -block (00:04:18), -" (00:04:19), -; (00:04:20), -place (00:04:49) ~0.00, -showMarkerAt (00:04:58), -( (00:04:59), -place (00:05:00), -. (00:05:01), -top (00:05:02), -, (00:05:03), -place (00:05:04), -. (00:05:05), -left (00:05:06), -) (00:05:07), -; (00:05:08), -function (00:05:46), -showMarkerAt (00:05:47), -( (00:05:48), -top (00:05:49), -, (00:05:50), -left (00:05:51), -) (00:05:52), -{ (00:05:53), -marker (00:05:54), -. (00:05:55), -style (00:05:56), -. (00:05:57), -top (00:05:58), -= (00:05:59), -top (00:06:00), -; (00:06:01), -marker (00:06:02), -. (00:06:03), -style (00:06:04), -. (00:06:05), -left (00:06:06), -= (00:06:07), -left (00:06:08), -; (00:06:09), -} (00:06:10), +ITEM (00:00:00), +item (00:00:00), +showInventoryItem (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +; (00:00:00), +function (00:00:00), +showInventoryItem (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +{ (00:00:00), +itemName (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Name (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +name (00:00:00), +; (00:00:00), +itemStore (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +In (00:00:00), +store (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +( (00:00:00), +item (00:00:00), +. (00:00:00), +inStock (00:00:00), +? (00:00:00), +" (00:00:00), +yes (00:00:00), +" (00:00:00), +: (00:00:00), +" (00:00:00), +no (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +itemPrice (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Price (00:00:00), +: (00:00:00), +€ (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +price (00:00:00), +; (00:00:00), +} (00:00:00)</t>
       </text>
     </comment>
     <comment ref="D94" authorId="0" shapeId="0">
@@ -1689,7 +1689,7 @@
     </comment>
     <comment ref="J94" authorId="0" shapeId="0">
       <text>
-        <t>-QR (00:07:05), -Positioning (00:07:06), -QR (00:07:37), -Positioning (00:07:38), -&lt; (00:07:43), -div (00:07:44), -id (00:07:45), -= (00:07:46), -" (00:07:47), -mapContainer (00:07:48), -" (00:07:49), -&gt; (00:07:50), -&lt; (00:07:51), -img (00:07:52), -src (00:07:53), -= (00:07:54), -" (00:07:55), -map (00:07:56), -. (00:07:57), -png (00:07:58), -" (00:07:59), -id (00:08:00), -= (00:08:01), -" (00:08:02), -map (00:08:03), -" (00:08:04), -alt (00:08:05), -= (00:08:06), -" (00:08:07), -map (00:08:08), -" (00:08:09), -/ (00:08:10), -&gt; (00:08:11), -&lt; (00:08:12), -div (00:08:13), -id (00:08:14), -= (00:08:15), -" (00:08:16), -marker (00:08:17), -" (00:08:18), -&gt; (00:08:19), -&lt; (00:08:20), -/ (00:08:21), -div (00:08:22), -&gt; (00:08:23), -&lt; (00:08:24), -/ (00:08:25), -div (00:08:26), -&gt; (00:08:27), +Inventory (00:00:00), +System (00:00:00), +Inventory (00:00:00), +System (00:00:00), +&lt; (00:00:00), +section (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +inventoryCard (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemName (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Name (00:00:00), +: (00:00:00), +scan (00:00:00), +an (00:00:00), +item (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemStore (00:00:00), +" (00:00:00), +&gt; (00:00:00), +In (00:00:00), +store (00:00:00), +: (00:00:00), +- (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemPrice (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Price (00:00:00), +: (00:00:00), +- (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +section (00:00:00), +&gt; (00:00:00), +ITEM (00:00:00)</t>
+        <t>-QR (00:07:05) ~0.00, -Positioning (00:07:06) ~0.18, -QR (00:07:37) ~0.00, -Positioning (00:07:38) ~0.18, -&lt; (00:07:43), -div (00:07:44), -id (00:07:45), -= (00:07:46), -" (00:07:47), -mapContainer (00:07:48), -" (00:07:49), -&gt; (00:07:50), -&lt; (00:07:51), -img (00:07:52), -src (00:07:53), -= (00:07:54), -" (00:07:55), -map (00:07:56), -. (00:07:57), -png (00:07:58), -" (00:07:59), -id (00:08:00), -= (00:08:01), -" (00:08:02), -map (00:08:03), -" (00:08:04), -alt (00:08:05), -= (00:08:06), -" (00:08:07), -map (00:08:08), -" (00:08:09), -/ (00:08:10), -&gt; (00:08:11), -&lt; (00:08:12), -div (00:08:13), -id (00:08:14), -= (00:08:15), -" (00:08:16), -marker (00:08:17), -" (00:08:18), -&gt; (00:08:19), -&lt; (00:08:20), -/ (00:08:21), -div (00:08:22), -&gt; (00:08:23), -&lt; (00:08:24), -/ (00:08:25), -div (00:08:26), -&gt; (00:08:27), +Inventory (00:00:00), +System (00:00:00), +Inventory (00:00:00), +System (00:00:00), +&lt; (00:00:00), +section (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +inventoryCard (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemName (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Name (00:00:00), +: (00:00:00), +scan (00:00:00), +an (00:00:00), +item (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemStore (00:00:00), +" (00:00:00), +&gt; (00:00:00), +In (00:00:00), +store (00:00:00), +: (00:00:00), +- (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemPrice (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Price (00:00:00), +: (00:00:00), +- (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +section (00:00:00), +&gt; (00:00:00), +ITEM (00:00:00)</t>
       </text>
     </comment>
     <comment ref="L94" authorId="0" shapeId="0">
@@ -1699,7 +1699,7 @@
     </comment>
     <comment ref="N94" authorId="0" shapeId="0">
       <text>
-        <t>-mapContainer (00:03:46), -. (00:03:47), -style (00:03:48), -. (00:03:49), -display (00:03:50), -= (00:03:51), -" (00:03:52), -none (00:03:53), -" (00:03:54), -; (00:03:55), -mapContainer (00:04:11), -. (00:04:12), -style (00:04:13), -. (00:04:14), -display (00:04:15), -= (00:04:16), -" (00:04:17), -block (00:04:18), -" (00:04:19), -; (00:04:20), -place (00:04:49), -showMarkerAt (00:04:58), -( (00:04:59), -place (00:05:00), -. (00:05:01), -top (00:05:02), -, (00:05:03), -place (00:05:04), -. (00:05:05), -left (00:05:06), -) (00:05:07), -; (00:05:08), -function (00:05:46), -showMarkerAt (00:05:47), -( (00:05:48), -top (00:05:49), -, (00:05:50), -left (00:05:51), -) (00:05:52), -{ (00:05:53), -marker (00:05:54), -. (00:05:55), -style (00:05:56), -. (00:05:57), -top (00:05:58), -= (00:05:59), -top (00:06:00), -; (00:06:01), -marker (00:06:02), -. (00:06:03), -style (00:06:04), -. (00:06:05), -left (00:06:06), -= (00:06:07), -left (00:06:08), -; (00:06:09), -} (00:06:10), +ITEM (00:00:00), +item (00:00:00), +showInventoryItem (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +; (00:00:00), +. (00:00:00), +catch (00:00:00), +( (00:00:00), +function (00:00:00), +( (00:00:00), +err (00:00:00), +) (00:00:00), +{ (00:00:00), +console (00:00:00), +. (00:00:00), +error (00:00:00), +( (00:00:00), +err (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +) (00:00:00), +function (00:00:00), +showInventoryItem (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +{ (00:00:00), +itemName (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Name (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +name (00:00:00), +; (00:00:00), +itemStore (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +In (00:00:00), +store (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +( (00:00:00), +item (00:00:00), +. (00:00:00), +inStock (00:00:00), +? (00:00:00), +" (00:00:00), +yes (00:00:00), +" (00:00:00), +: (00:00:00), +" (00:00:00), +no (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +itemPrice (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Price (00:00:00), +: (00:00:00), +€ (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +price (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+        <t>-mapContainer (00:03:46), -. (00:03:47), -style (00:03:48), -. (00:03:49), -display (00:03:50), -= (00:03:51), -" (00:03:52), -none (00:03:53), -" (00:03:54), -; (00:03:55), -mapContainer (00:04:11), -. (00:04:12), -style (00:04:13), -. (00:04:14), -display (00:04:15), -= (00:04:16), -" (00:04:17), -block (00:04:18), -" (00:04:19), -; (00:04:20), -place (00:04:49) ~0.00, -showMarkerAt (00:04:58), -( (00:04:59), -place (00:05:00), -. (00:05:01), -top (00:05:02), -, (00:05:03), -place (00:05:04), -. (00:05:05), -left (00:05:06), -) (00:05:07), -; (00:05:08), -function (00:05:46), -showMarkerAt (00:05:47), -( (00:05:48), -top (00:05:49), -, (00:05:50), -left (00:05:51), -) (00:05:52), -{ (00:05:53), -marker (00:05:54), -. (00:05:55), -style (00:05:56), -. (00:05:57), -top (00:05:58), -= (00:05:59), -top (00:06:00), -; (00:06:01), -marker (00:06:02), -. (00:06:03), -style (00:06:04), -. (00:06:05), -left (00:06:06), -= (00:06:07), -left (00:06:08), -; (00:06:09), -} (00:06:10), +ITEM (00:00:00), +item (00:00:00), +showInventoryItem (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +; (00:00:00), +. (00:00:00), +catch (00:00:00), +( (00:00:00), +function (00:00:00), +( (00:00:00), +err (00:00:00), +) (00:00:00), +{ (00:00:00), +console (00:00:00), +. (00:00:00), +error (00:00:00), +( (00:00:00), +err (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +) (00:00:00), +function (00:00:00), +showInventoryItem (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +{ (00:00:00), +itemName (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Name (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +name (00:00:00), +; (00:00:00), +itemStore (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +In (00:00:00), +store (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +( (00:00:00), +item (00:00:00), +. (00:00:00), +inStock (00:00:00), +? (00:00:00), +" (00:00:00), +yes (00:00:00), +" (00:00:00), +: (00:00:00), +" (00:00:00), +no (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +itemPrice (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Price (00:00:00), +: (00:00:00), +€ (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +price (00:00:00), +; (00:00:00), +} (00:00:00)</t>
       </text>
     </comment>
     <comment ref="D95" authorId="0" shapeId="0">
@@ -1784,7 +1784,7 @@
     </comment>
     <comment ref="N97" authorId="0" shapeId="0">
       <text>
-        <t>-place (00:04:49), -showMarkerAt (00:04:58), -( (00:04:59), -place (00:05:00), -. (00:05:01), -top (00:05:02), -, (00:05:03), -place (00:05:04), -. (00:05:05), -left (00:05:06), -) (00:05:07), -; (00:05:08), +const (00:00:00), +mapContainer (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +mapContainer (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +btn (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +btn (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +itemName (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +itemName (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +itemAvailability (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +itemAvailability (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +itemPrice (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +itemPrice (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +try (00:00:00), +{ (00:00:00), +data (00:00:00), +displayInventory (00:00:00), +( (00:00:00), +data (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +catch (00:00:00), +( (00:00:00), +e (00:00:00), +) (00:00:00), +{ (00:00:00), +console (00:00:00), +. (00:00:00), +error (00:00:00), +( (00:00:00), +" (00:00:00), +Scanned (00:00:00), +data (00:00:00), +is (00:00:00), +not (00:00:00), +valid (00:00:00), +JSON (00:00:00), +: (00:00:00), +" (00:00:00), +, (00:00:00), +e (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +function (00:00:00), +displayInventory (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +{ (00:00:00), +itemName (00:00:00), +. (00:00:00), +innerHTML (00:00:00), += (00:00:00), +` (00:00:00), +&lt; (00:00:00), +strong (00:00:00), +&gt; (00:00:00), +Product (00:00:00), +Name (00:00:00), +: (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +strong (00:00:00), +&gt; (00:00:00), +$ (00:00:00), +{ (00:00:00), +item (00:00:00), +. (00:00:00), +name (00:00:00), +| (00:00:00), +| (00:00:00), +" (00:00:00), +N (00:00:00), +/ (00:00:00), +A (00:00:00), +" (00:00:00), +} (00:00:00), +` (00:00:00), +; (00:00:00), +if (00:00:00), +( (00:00:00), +item (00:00:00), +. (00:00:00), +in (00:00:00), +_ (00:00:00), +store (00:00:00), += (00:00:00), += (00:00:00), += (00:00:00), +true (00:00:00), +| (00:00:00), +| (00:00:00), +item (00:00:00), +. (00:00:00), +in (00:00:00), +_ (00:00:00), +store (00:00:00), += (00:00:00), += (00:00:00), += (00:00:00), +" (00:00:00), +true (00:00:00), +" (00:00:00), +) (00:00:00), +{ (00:00:00), +itemAvailability (00:00:00), +. (00:00:00), +innerHTML (00:00:00), += (00:00:00), +` (00:00:00), +&lt; (00:00:00), +strong (00:00:00), +&gt; (00:00:00), +Availability (00:00:00), +: (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +strong (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +span (00:00:00), +style (00:00:00), += (00:00:00), +" (00:00:00), +color (00:00:00), +: (00:00:00), +green (00:00:00), +; (00:00:00), +" (00:00:00), +&gt; (00:00:00), +In (00:00:00), +Stock (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +span (00:00:00), +&gt; (00:00:00), +` (00:00:00), +; (00:00:00), +} (00:00:00), +else (00:00:00), +{ (00:00:00), +itemAvailability (00:00:00), +. (00:00:00), +innerHTML (00:00:00), += (00:00:00), +` (00:00:00), +&lt; (00:00:00), +strong (00:00:00), +&gt; (00:00:00), +Availability (00:00:00), +: (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +strong (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +span (00:00:00), +style (00:00:00), += (00:00:00), +" (00:00:00), +color (00:00:00), +: (00:00:00), +red (00:00:00), +; (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Out (00:00:00), +of (00:00:00), +Stock (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +span (00:00:00), +&gt; (00:00:00), +` (00:00:00), +; (00:00:00), +} (00:00:00), +if (00:00:00), +( (00:00:00), +item (00:00:00), +. (00:00:00), +price (00:00:00), +! (00:00:00), += (00:00:00), += (00:00:00), +undefined (00:00:00), +) (00:00:00), +{ (00:00:00), +itemAvailability (00:00:00), +. (00:00:00), +innerHTML (00:00:00), ++ (00:00:00), += (00:00:00), +` (00:00:00), +( (00:00:00), +$ (00:00:00), +{ (00:00:00), +item (00:00:00), +. (00:00:00), +in (00:00:00), +_ (00:00:00), +store (00:00:00), +? (00:00:00), +' (00:00:00), +Available (00:00:00), +' (00:00:00), +: (00:00:00), +' (00:00:00), +Unavailable (00:00:00), +' (00:00:00), +} (00:00:00), +) (00:00:00), +` (00:00:00), +; (00:00:00), +itemPrice (00:00:00), +. (00:00:00), +innerHTML (00:00:00), += (00:00:00), +` (00:00:00), +&lt; (00:00:00), +strong (00:00:00), +&gt; (00:00:00), +Price (00:00:00), +: (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +strong (00:00:00), +&gt; (00:00:00), +€ (00:00:00), +$ (00:00:00), +{ (00:00:00), +parseFloat (00:00:00), +( (00:00:00), +item (00:00:00), +. (00:00:00), +price (00:00:00), +) (00:00:00), +. (00:00:00), +toFixed (00:00:00), +( (00:00:00), +2 (00:00:00), +) (00:00:00), +} (00:00:00), +` (00:00:00), +; (00:00:00), +} (00:00:00), +else (00:00:00), +{ (00:00:00), +itemPrice (00:00:00), +. (00:00:00), +innerHTML (00:00:00), += (00:00:00), +` (00:00:00), +&lt; (00:00:00), +strong (00:00:00), +&gt; (00:00:00), +Price (00:00:00), +: (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +strong (00:00:00), +&gt; (00:00:00), +N (00:00:00), +/ (00:00:00), +A (00:00:00), +` (00:00:00), +; (00:00:00), +} (00:00:00), +} (00:00:00), +const (00:00:00), +marker (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +marker (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +if (00:00:00), +( (00:00:00), +marker (00:00:00), +) (00:00:00), +{ (00:00:00), +} (00:00:00)</t>
+        <t>-place (00:04:49) ~0.20, -showMarkerAt (00:04:58), -( (00:04:59), -place (00:05:00), -. (00:05:01), -top (00:05:02), -, (00:05:03), -place (00:05:04), -. (00:05:05), -left (00:05:06), -) (00:05:07), -; (00:05:08), +const (00:00:00), +mapContainer (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +mapContainer (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +btn (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +btn (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +itemName (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +itemName (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +itemAvailability (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +itemAvailability (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +itemPrice (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +itemPrice (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +try (00:00:00), +{ (00:00:00), +data (00:00:00), +displayInventory (00:00:00), +( (00:00:00), +data (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +catch (00:00:00), +( (00:00:00), +e (00:00:00), +) (00:00:00), +{ (00:00:00), +console (00:00:00), +. (00:00:00), +error (00:00:00), +( (00:00:00), +" (00:00:00), +Scanned (00:00:00), +data (00:00:00), +is (00:00:00), +not (00:00:00), +valid (00:00:00), +JSON (00:00:00), +: (00:00:00), +" (00:00:00), +, (00:00:00), +e (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +function (00:00:00), +displayInventory (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +{ (00:00:00), +itemName (00:00:00), +. (00:00:00), +innerHTML (00:00:00), += (00:00:00), +` (00:00:00), +&lt; (00:00:00), +strong (00:00:00), +&gt; (00:00:00), +Product (00:00:00), +Name (00:00:00), +: (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +strong (00:00:00), +&gt; (00:00:00), +$ (00:00:00), +{ (00:00:00), +item (00:00:00), +. (00:00:00), +name (00:00:00), +| (00:00:00), +| (00:00:00), +" (00:00:00), +N (00:00:00), +/ (00:00:00), +A (00:00:00), +" (00:00:00), +} (00:00:00), +` (00:00:00), +; (00:00:00), +if (00:00:00), +( (00:00:00), +item (00:00:00), +. (00:00:00), +in (00:00:00), +_ (00:00:00), +store (00:00:00), += (00:00:00), += (00:00:00), += (00:00:00), +true (00:00:00), +| (00:00:00), +| (00:00:00), +item (00:00:00), +. (00:00:00), +in (00:00:00), +_ (00:00:00), +store (00:00:00), += (00:00:00), += (00:00:00), += (00:00:00), +" (00:00:00), +true (00:00:00), +" (00:00:00), +) (00:00:00), +{ (00:00:00), +itemAvailability (00:00:00), +. (00:00:00), +innerHTML (00:00:00), += (00:00:00), +` (00:00:00), +&lt; (00:00:00), +strong (00:00:00), +&gt; (00:00:00), +Availability (00:00:00), +: (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +strong (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +span (00:00:00), +style (00:00:00), += (00:00:00), +" (00:00:00), +color (00:00:00), +: (00:00:00), +green (00:00:00), +; (00:00:00), +" (00:00:00), +&gt; (00:00:00), +In (00:00:00), +Stock (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +span (00:00:00), +&gt; (00:00:00), +` (00:00:00), +; (00:00:00), +} (00:00:00), +else (00:00:00), +{ (00:00:00), +itemAvailability (00:00:00), +. (00:00:00), +innerHTML (00:00:00), += (00:00:00), +` (00:00:00), +&lt; (00:00:00), +strong (00:00:00), +&gt; (00:00:00), +Availability (00:00:00), +: (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +strong (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +span (00:00:00), +style (00:00:00), += (00:00:00), +" (00:00:00), +color (00:00:00), +: (00:00:00), +red (00:00:00), +; (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Out (00:00:00), +of (00:00:00), +Stock (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +span (00:00:00), +&gt; (00:00:00), +` (00:00:00), +; (00:00:00), +} (00:00:00), +if (00:00:00), +( (00:00:00), +item (00:00:00), +. (00:00:00), +price (00:00:00), +! (00:00:00), += (00:00:00), += (00:00:00), +undefined (00:00:00), +) (00:00:00), +{ (00:00:00), +itemAvailability (00:00:00), +. (00:00:00), +innerHTML (00:00:00), ++ (00:00:00), += (00:00:00), +` (00:00:00), +( (00:00:00), +$ (00:00:00), +{ (00:00:00), +item (00:00:00), +. (00:00:00), +in (00:00:00), +_ (00:00:00), +store (00:00:00), +? (00:00:00), +' (00:00:00), +Available (00:00:00), +' (00:00:00), +: (00:00:00), +' (00:00:00), +Unavailable (00:00:00), +' (00:00:00), +} (00:00:00), +) (00:00:00), +` (00:00:00), +; (00:00:00), +itemPrice (00:00:00), +. (00:00:00), +innerHTML (00:00:00), += (00:00:00), +` (00:00:00), +&lt; (00:00:00), +strong (00:00:00), +&gt; (00:00:00), +Price (00:00:00), +: (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +strong (00:00:00), +&gt; (00:00:00), +€ (00:00:00), +$ (00:00:00), +{ (00:00:00), +parseFloat (00:00:00), +( (00:00:00), +item (00:00:00), +. (00:00:00), +price (00:00:00), +) (00:00:00), +. (00:00:00), +toFixed (00:00:00), +( (00:00:00), +2 (00:00:00), +) (00:00:00), +} (00:00:00), +` (00:00:00), +; (00:00:00), +} (00:00:00), +else (00:00:00), +{ (00:00:00), +itemPrice (00:00:00), +. (00:00:00), +innerHTML (00:00:00), += (00:00:00), +` (00:00:00), +&lt; (00:00:00), +strong (00:00:00), +&gt; (00:00:00), +Price (00:00:00), +: (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +strong (00:00:00), +&gt; (00:00:00), +N (00:00:00), +/ (00:00:00), +A (00:00:00), +` (00:00:00), +; (00:00:00), +} (00:00:00), +} (00:00:00), +const (00:00:00), +marker (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +marker (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +if (00:00:00), +( (00:00:00), +marker (00:00:00), +) (00:00:00), +{ (00:00:00), +} (00:00:00)</t>
       </text>
     </comment>
     <comment ref="P97" authorId="0" shapeId="0">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>-place (00:04:49), -place (00:05:00), -place (00:05:04), +const (00:00:00), +mapContainer (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +mapContainer (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +btn (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +btn (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +marker (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +marker (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +data (00:00:00), +if (00:00:00), +( (00:00:00), +data (00:00:00), +. (00:00:00), +top (00:00:00), +&amp; (00:00:00), +&amp; (00:00:00), +data (00:00:00), +. (00:00:00), +left (00:00:00), +) (00:00:00), +{ (00:00:00), +data (00:00:00), +data (00:00:00), +} (00:00:00), +if (00:00:00), +( (00:00:00), +data (00:00:00), +. (00:00:00), +name (00:00:00), +) (00:00:00), +{ (00:00:00), +showProduct (00:00:00), +( (00:00:00), +text (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +function (00:00:00), +showProduct (00:00:00), +( (00:00:00), +data (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +obj (00:00:00), += (00:00:00), +JSON (00:00:00), +. (00:00:00), +parse (00:00:00), +( (00:00:00), +data (00:00:00), +) (00:00:00), +; (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +name (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +Name (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +( (00:00:00), +obj (00:00:00), +. (00:00:00), +name (00:00:00), +| (00:00:00), +| (00:00:00), +" (00:00:00), +Yes (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +stock (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +In (00:00:00), +store (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +( (00:00:00), +obj (00:00:00), +. (00:00:00), +in (00:00:00), +_ (00:00:00), +store (00:00:00), +! (00:00:00), += (00:00:00), += (00:00:00), +undefined (00:00:00), +? (00:00:00), +obj (00:00:00), +. (00:00:00), +in (00:00:00), +_ (00:00:00), +store (00:00:00), +: (00:00:00), +" (00:00:00), +No (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +price (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +Price (00:00:00), +: (00:00:00), +€ (00:00:00), +" (00:00:00), ++ (00:00:00), +( (00:00:00), +obj (00:00:00), +. (00:00:00), +price (00:00:00), +! (00:00:00), += (00:00:00), += (00:00:00), +undefined (00:00:00), +? (00:00:00), +obj (00:00:00), +. (00:00:00), +price (00:00:00), +: (00:00:00), +" (00:00:00), +No (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+          <t>-place (00:04:49) ~0.20, -place (00:05:00) ~0.20, -place (00:05:04) ~0.20, +const (00:00:00), +mapContainer (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +mapContainer (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +btn (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +btn (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +marker (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +marker (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +data (00:00:00), +if (00:00:00), +( (00:00:00), +data (00:00:00), +. (00:00:00), +top (00:00:00), +&amp; (00:00:00), +&amp; (00:00:00), +data (00:00:00), +. (00:00:00), +left (00:00:00), +) (00:00:00), +{ (00:00:00), +data (00:00:00), +data (00:00:00), +} (00:00:00), +if (00:00:00), +( (00:00:00), +data (00:00:00), +. (00:00:00), +name (00:00:00), +) (00:00:00), +{ (00:00:00), +showProduct (00:00:00), +( (00:00:00), +text (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +function (00:00:00), +showProduct (00:00:00), +( (00:00:00), +data (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +obj (00:00:00), += (00:00:00), +JSON (00:00:00), +. (00:00:00), +parse (00:00:00), +( (00:00:00), +data (00:00:00), +) (00:00:00), +; (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +name (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +Name (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +( (00:00:00), +obj (00:00:00), +. (00:00:00), +name (00:00:00), +| (00:00:00), +| (00:00:00), +" (00:00:00), +Yes (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +stock (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +In (00:00:00), +store (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +( (00:00:00), +obj (00:00:00), +. (00:00:00), +in (00:00:00), +_ (00:00:00), +store (00:00:00), +! (00:00:00), += (00:00:00), += (00:00:00), +undefined (00:00:00), +? (00:00:00), +obj (00:00:00), +. (00:00:00), +in (00:00:00), +_ (00:00:00), +store (00:00:00), +: (00:00:00), +" (00:00:00), +No (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +price (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +Price (00:00:00), +: (00:00:00), +€ (00:00:00), +" (00:00:00), ++ (00:00:00), +( (00:00:00), +obj (00:00:00), +. (00:00:00), +price (00:00:00), +! (00:00:00), += (00:00:00), += (00:00:00), +undefined (00:00:00), +? (00:00:00), +obj (00:00:00), +. (00:00:00), +price (00:00:00), +: (00:00:00), +" (00:00:00), +No (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00)</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>-place (00:04:49), -showMarkerAt (00:04:58), -( (00:04:59), -place (00:05:00), -. (00:05:01), -top (00:05:02), -, (00:05:03), -place (00:05:04), -. (00:05:05), -left (00:05:06), -) (00:05:07), -; (00:05:08), +item (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +itemName (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Name (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +name (00:00:00), +; (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +itemStatus (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +In (00:00:00), +store (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +( (00:00:00), +item (00:00:00), +. (00:00:00), +in (00:00:00), +_ (00:00:00), +store (00:00:00), +? (00:00:00), +" (00:00:00), +Yes (00:00:00), +" (00:00:00), +: (00:00:00), +" (00:00:00), +No (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +itemPrice (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Price (00:00:00), +: (00:00:00), +€ (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +price (00:00:00), +; (00:00:00)</t>
+          <t>-place (00:04:49) ~0.00, -showMarkerAt (00:04:58), -( (00:04:59), -place (00:05:00), -. (00:05:01), -top (00:05:02), -, (00:05:03), -place (00:05:04), -. (00:05:05), -left (00:05:06), -) (00:05:07), -; (00:05:08), +item (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +itemName (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Name (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +name (00:00:00), +; (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +itemStatus (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +In (00:00:00), +store (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +( (00:00:00), +item (00:00:00), +. (00:00:00), +in (00:00:00), +_ (00:00:00), +store (00:00:00), +? (00:00:00), +" (00:00:00), +Yes (00:00:00), +" (00:00:00), +: (00:00:00), +" (00:00:00), +No (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +itemPrice (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Price (00:00:00), +: (00:00:00), +€ (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +price (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
@@ -2993,7 +2993,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>-SCAN (00:08:43), +Scan (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +inventory (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +style (00:00:00), += (00:00:00), +" (00:00:00), +margin (00:00:00), +- (00:00:00), +bottom (00:00:00), +: (00:00:00), +3px (00:00:00), +; (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Stock (00:00:00), +Information (00:00:00), +: (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +name (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +price (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +inStock (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
+          <t>-SCAN (00:08:43) ~0.25, +Scan (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +inventory (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +style (00:00:00), += (00:00:00), +" (00:00:00), +margin (00:00:00), +- (00:00:00), +bottom (00:00:00), +: (00:00:00), +3px (00:00:00), +; (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Stock (00:00:00), +Information (00:00:00), +: (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +name (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +price (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +inStock (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
         </is>
       </c>
       <c r="L21" t="n">
@@ -3009,7 +3009,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>-CANCEL (00:03:43), -SCAN (00:04:08), +const (00:00:00), +inventory (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +inventory (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +mapContainer (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +mapContainer (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +btn (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +btn (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +marker (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +marker (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +inventory (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +display (00:00:00), += (00:00:00), +" (00:00:00), +none (00:00:00), +" (00:00:00), +; (00:00:00), +Cancel (00:00:00), +inventory (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +display (00:00:00), += (00:00:00), +" (00:00:00), +flex (00:00:00), +" (00:00:00), +; (00:00:00), +Scan (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +text (00:00:00), +) (00:00:00), +; (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +name (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +' (00:00:00), +Item (00:00:00), +name (00:00:00), +: (00:00:00), +' (00:00:00), ++ (00:00:00), +place (00:00:00), +. (00:00:00), +name (00:00:00), +; (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +price (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +innerHTML (00:00:00), += (00:00:00), +' (00:00:00), +Price (00:00:00), +( (00:00:00), +&amp; (00:00:00), +# (00:00:00), +x20AC (00:00:00), +) (00:00:00), +: (00:00:00), +' (00:00:00), ++ (00:00:00), +place (00:00:00), +. (00:00:00), +price (00:00:00), +; (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +inStock (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +' (00:00:00), +In (00:00:00), +Stock (00:00:00), +: (00:00:00), +' (00:00:00), ++ (00:00:00), +Number (00:00:00), +( (00:00:00), +place (00:00:00), +. (00:00:00), +inStock (00:00:00), +) (00:00:00), +; (00:00:00)</t>
+          <t>-CANCEL (00:03:43) ~0.17, -SCAN (00:04:08) ~0.25, +const (00:00:00), +inventory (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +inventory (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +mapContainer (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +mapContainer (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +btn (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +btn (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +marker (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +marker (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +inventory (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +display (00:00:00), += (00:00:00), +" (00:00:00), +none (00:00:00), +" (00:00:00), +; (00:00:00), +Cancel (00:00:00), +inventory (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +display (00:00:00), += (00:00:00), +" (00:00:00), +flex (00:00:00), +" (00:00:00), +; (00:00:00), +Scan (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +text (00:00:00), +) (00:00:00), +; (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +name (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +' (00:00:00), +Item (00:00:00), +name (00:00:00), +: (00:00:00), +' (00:00:00), ++ (00:00:00), +place (00:00:00), +. (00:00:00), +name (00:00:00), +; (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +price (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +innerHTML (00:00:00), += (00:00:00), +' (00:00:00), +Price (00:00:00), +( (00:00:00), +&amp; (00:00:00), +# (00:00:00), +x20AC (00:00:00), +) (00:00:00), +: (00:00:00), +' (00:00:00), ++ (00:00:00), +place (00:00:00), +. (00:00:00), +price (00:00:00), +; (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +inStock (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +' (00:00:00), +In (00:00:00), +Stock (00:00:00), +: (00:00:00), +' (00:00:00), ++ (00:00:00), +Number (00:00:00), +( (00:00:00), +place (00:00:00), +. (00:00:00), +inStock (00:00:00), +) (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>-onclick (00:08:35), +onClick (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +paragraphContainer (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
+          <t>-onclick (00:08:35) ~0.86, +onClick (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +paragraphContainer (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
         </is>
       </c>
       <c r="L24" t="n">
@@ -3197,7 +3197,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>-place (00:04:49), -place (00:05:00), -place (00:05:04), +data (00:00:00), +if (00:00:00), +( (00:00:00), +data (00:00:00), +. (00:00:00), +top (00:00:00), +&amp; (00:00:00), +&amp; (00:00:00), +data (00:00:00), +. (00:00:00), +left (00:00:00), +) (00:00:00), +{ (00:00:00), +data (00:00:00), +data (00:00:00), +} (00:00:00), +if (00:00:00), +( (00:00:00), +data (00:00:00), +. (00:00:00), +name (00:00:00), +) (00:00:00), +{ (00:00:00), +showInventory (00:00:00), +( (00:00:00), +data (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +function (00:00:00), +showInventory (00:00:00), +( (00:00:00), +data (00:00:00), +) (00:00:00), +{ (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +itemName (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Name (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +data (00:00:00), +. (00:00:00), +name (00:00:00), +; (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +itemStore (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +In (00:00:00), +store (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +( (00:00:00), +data (00:00:00), +. (00:00:00), +in (00:00:00), +_ (00:00:00), +store (00:00:00), +? (00:00:00), +" (00:00:00), +Yes (00:00:00), +" (00:00:00), +: (00:00:00), +" (00:00:00), +No (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +itemPrice (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Price (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +data (00:00:00), +. (00:00:00), +price (00:00:00), ++ (00:00:00), +" (00:00:00), +€ (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+          <t>-place (00:04:49) ~0.20, -place (00:05:00) ~0.20, -place (00:05:04) ~0.20, +data (00:00:00), +if (00:00:00), +( (00:00:00), +data (00:00:00), +. (00:00:00), +top (00:00:00), +&amp; (00:00:00), +&amp; (00:00:00), +data (00:00:00), +. (00:00:00), +left (00:00:00), +) (00:00:00), +{ (00:00:00), +data (00:00:00), +data (00:00:00), +} (00:00:00), +if (00:00:00), +( (00:00:00), +data (00:00:00), +. (00:00:00), +name (00:00:00), +) (00:00:00), +{ (00:00:00), +showInventory (00:00:00), +( (00:00:00), +data (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +function (00:00:00), +showInventory (00:00:00), +( (00:00:00), +data (00:00:00), +) (00:00:00), +{ (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +itemName (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Name (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +data (00:00:00), +. (00:00:00), +name (00:00:00), +; (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +itemStore (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +In (00:00:00), +store (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +( (00:00:00), +data (00:00:00), +. (00:00:00), +in (00:00:00), +_ (00:00:00), +store (00:00:00), +? (00:00:00), +" (00:00:00), +Yes (00:00:00), +" (00:00:00), +: (00:00:00), +" (00:00:00), +No (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +itemPrice (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Price (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +data (00:00:00), +. (00:00:00), +price (00:00:00), ++ (00:00:00), +" (00:00:00), +€ (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00)</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3301,7 +3301,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>-Positioning (00:07:06), -Positioning (00:07:38), -&lt; (00:07:43), -div (00:07:44), -id (00:07:45), -= (00:07:46), -" (00:07:47), -mapContainer (00:07:48), -" (00:07:49), -&gt; (00:07:50), -&lt; (00:07:51), -img (00:07:52), -src (00:07:53), -= (00:07:54), -" (00:07:55), -map (00:07:56), -. (00:07:57), -png (00:07:58), -" (00:07:59), -id (00:08:00), -= (00:08:01), -" (00:08:02), -map (00:08:03), -" (00:08:04), -alt (00:08:05), -= (00:08:06), -" (00:08:07), -map (00:08:08), -" (00:08:09), -/ (00:08:10), -&gt; (00:08:11), -&lt; (00:08:12), -div (00:08:13), -id (00:08:14), -= (00:08:15), -" (00:08:16), -marker (00:08:17), -" (00:08:18), -&gt; (00:08:19), -&lt; (00:08:20), -/ (00:08:21), -div (00:08:22), -&gt; (00:08:23), -&lt; (00:08:24), -/ (00:08:25), -div (00:08:26), -&gt; (00:08:27), -btn (00:08:33), -onclick (00:08:35), -= (00:08:36), -" (00:08:37), -toggleScanner (00:08:38), -( (00:08:39), -) (00:08:40), -" (00:08:41), -SCAN (00:08:43), -&lt; (00:08:48), -div (00:08:49), -id (00:08:50), -= (00:08:51), -" (00:08:52), -camera (00:08:53), -" (00:08:54), -&gt; (00:08:55), -&lt; (00:08:56), -/ (00:08:57), -div (00:08:58), -&gt; (00:08:59), -type (00:09:17), -= (00:09:18), -" (00:09:19), -text (00:09:20), -/ (00:09:21), -javascript (00:09:22), -" (00:09:23), +Inventory (00:00:00), +Scanner (00:00:00), +Inventory (00:00:00), +Scanner (00:00:00), +scanBtn (00:00:00), +Scan (00:00:00), +QR (00:00:00), +Code (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +reader (00:00:00), +" (00:00:00), +style (00:00:00), += (00:00:00), +" (00:00:00), +width (00:00:00), +: (00:00:00), +300px (00:00:00), +; (00:00:00), +margin (00:00:00), +- (00:00:00), +top (00:00:00), +: (00:00:00), +20px (00:00:00), +; (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +h2 (00:00:00), +&gt; (00:00:00), +Item (00:00:00), +Information (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +h2 (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +name (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +store (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +price (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00)</t>
+          <t>-Positioning (00:07:06) ~0.09, -Positioning (00:07:38) ~0.09, -&lt; (00:07:43), -div (00:07:44), -id (00:07:45), -= (00:07:46), -" (00:07:47), -mapContainer (00:07:48), -" (00:07:49), -&gt; (00:07:50), -&lt; (00:07:51), -img (00:07:52), -src (00:07:53), -= (00:07:54), -" (00:07:55), -map (00:07:56), -. (00:07:57), -png (00:07:58), -" (00:07:59), -id (00:08:00), -= (00:08:01), -" (00:08:02), -map (00:08:03), -" (00:08:04), -alt (00:08:05), -= (00:08:06), -" (00:08:07), -map (00:08:08), -" (00:08:09), -/ (00:08:10), -&gt; (00:08:11), -&lt; (00:08:12), -div (00:08:13), -id (00:08:14), -= (00:08:15), -" (00:08:16), -marker (00:08:17), -" (00:08:18), -&gt; (00:08:19), -&lt; (00:08:20), -/ (00:08:21), -div (00:08:22), -&gt; (00:08:23), -&lt; (00:08:24), -/ (00:08:25), -div (00:08:26), -&gt; (00:08:27), -btn (00:08:33) ~0.29, -onclick (00:08:35), -= (00:08:36), -" (00:08:37), -toggleScanner (00:08:38), -( (00:08:39), -) (00:08:40), -" (00:08:41), -SCAN (00:08:43) ~0.25, -&lt; (00:08:48), -div (00:08:49), -id (00:08:50), -= (00:08:51), -" (00:08:52), -camera (00:08:53), -" (00:08:54), -&gt; (00:08:55), -&lt; (00:08:56), -/ (00:08:57), -div (00:08:58), -&gt; (00:08:59), -type (00:09:17), -= (00:09:18), -" (00:09:19), -text (00:09:20), -/ (00:09:21), -javascript (00:09:22), -" (00:09:23), +Inventory (00:00:00), +Scanner (00:00:00), +Inventory (00:00:00), +Scanner (00:00:00), +scanBtn (00:00:00), +Scan (00:00:00), +QR (00:00:00), +Code (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +reader (00:00:00), +" (00:00:00), +style (00:00:00), += (00:00:00), +" (00:00:00), +width (00:00:00), +: (00:00:00), +300px (00:00:00), +; (00:00:00), +margin (00:00:00), +- (00:00:00), +top (00:00:00), +: (00:00:00), +20px (00:00:00), +; (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +h2 (00:00:00), +&gt; (00:00:00), +Item (00:00:00), +Information (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +h2 (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +name (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +store (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +price (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00)</t>
         </is>
       </c>
       <c r="L28" t="n">
@@ -3473,7 +3473,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>-QR (00:07:05), -Positioning (00:07:38), +Qr (00:00:00), +Positionining (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +inventoryBox (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +h2 (00:00:00), +&gt; (00:00:00), +Inventory (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +h2 (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemName (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemStock (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemPrice (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
+          <t>-QR (00:07:05) ~0.50, -Positioning (00:07:38) ~0.85, +Qr (00:00:00), +Positionining (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +inventoryBox (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +h2 (00:00:00), +&gt; (00:00:00), +Inventory (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +h2 (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemName (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemStock (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemPrice (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
         </is>
       </c>
       <c r="L31" t="n">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>-Positioning (00:07:06), -Positioning (00:07:38), +Inventory (00:00:00), +System (00:00:00), +Inventory (00:00:00), +System (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +inventoryInfo (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemName (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +inStore (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +price (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
+          <t>-Positioning (00:07:06) ~0.09, -Positioning (00:07:38) ~0.09, +Inventory (00:00:00), +System (00:00:00), +Inventory (00:00:00), +System (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +inventoryInfo (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemName (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +inStore (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +price (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
         </is>
       </c>
       <c r="L36" t="n">
@@ -3638,7 +3638,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>-# (00:00:07), -280 (00:00:08), +red (00:00:00), +margin (00:00:00), +: (00:00:00), +10px (00:00:00), +0 (00:00:00), +; (00:00:00), +# (00:00:00), +btn (00:00:00), +{ (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +var (00:00:00), +( (00:00:00), +- (00:00:00), +- (00:00:00), +theme (00:00:00), +) (00:00:00), +; (00:00:00), +color (00:00:00), +: (00:00:00), +white (00:00:00), +; (00:00:00), +border (00:00:00), +: (00:00:00), +none (00:00:00), +; (00:00:00), +padding (00:00:00), +: (00:00:00), +12px (00:00:00), +24px (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +16px (00:00:00), +; (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +8px (00:00:00), +; (00:00:00), +cursor (00:00:00), +: (00:00:00), +pointer (00:00:00), +; (00:00:00), +transition (00:00:00), +: (00:00:00), +all (00:00:00), +0 (00:00:00), +. (00:00:00), +3s (00:00:00), +ease (00:00:00), +; (00:00:00), +box (00:00:00), +- (00:00:00), +shadow (00:00:00), +: (00:00:00), +0 (00:00:00), +4px (00:00:00), +6px (00:00:00), +rgba (00:00:00), +( (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +. (00:00:00), +2 (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +btn (00:00:00), +: (00:00:00), +hover (00:00:00), +{ (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +white (00:00:00), +; (00:00:00), +color (00:00:00), +: (00:00:00), +var (00:00:00), +( (00:00:00), +- (00:00:00), +- (00:00:00), +theme (00:00:00), +) (00:00:00), +; (00:00:00), +box (00:00:00), +- (00:00:00), +shadow (00:00:00), +: (00:00:00), +0 (00:00:00), +6px (00:00:00), +10px (00:00:00), +rgba (00:00:00), +( (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +. (00:00:00), +3 (00:00:00), +) (00:00:00), +; (00:00:00), +transform (00:00:00), +: (00:00:00), +scale (00:00:00), +( (00:00:00), +1 (00:00:00), +. (00:00:00), +05 (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +inventoryInfo (00:00:00), +{ (00:00:00), +margin (00:00:00), +- (00:00:00), +top (00:00:00), +: (00:00:00), +20px (00:00:00), +; (00:00:00), +text (00:00:00), +- (00:00:00), +align (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +inventoryInfo (00:00:00), +p (00:00:00), +{ (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +18px (00:00:00), +; (00:00:00), +margin (00:00:00), +: (00:00:00), +5px (00:00:00), +0 (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+          <t>-# (00:00:07), -280 (00:00:08) ~0.00, +red (00:00:00), +margin (00:00:00), +: (00:00:00), +10px (00:00:00), +0 (00:00:00), +; (00:00:00), +# (00:00:00), +btn (00:00:00), +{ (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +var (00:00:00), +( (00:00:00), +- (00:00:00), +- (00:00:00), +theme (00:00:00), +) (00:00:00), +; (00:00:00), +color (00:00:00), +: (00:00:00), +white (00:00:00), +; (00:00:00), +border (00:00:00), +: (00:00:00), +none (00:00:00), +; (00:00:00), +padding (00:00:00), +: (00:00:00), +12px (00:00:00), +24px (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +16px (00:00:00), +; (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +8px (00:00:00), +; (00:00:00), +cursor (00:00:00), +: (00:00:00), +pointer (00:00:00), +; (00:00:00), +transition (00:00:00), +: (00:00:00), +all (00:00:00), +0 (00:00:00), +. (00:00:00), +3s (00:00:00), +ease (00:00:00), +; (00:00:00), +box (00:00:00), +- (00:00:00), +shadow (00:00:00), +: (00:00:00), +0 (00:00:00), +4px (00:00:00), +6px (00:00:00), +rgba (00:00:00), +( (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +. (00:00:00), +2 (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +btn (00:00:00), +: (00:00:00), +hover (00:00:00), +{ (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +white (00:00:00), +; (00:00:00), +color (00:00:00), +: (00:00:00), +var (00:00:00), +( (00:00:00), +- (00:00:00), +- (00:00:00), +theme (00:00:00), +) (00:00:00), +; (00:00:00), +box (00:00:00), +- (00:00:00), +shadow (00:00:00), +: (00:00:00), +0 (00:00:00), +6px (00:00:00), +10px (00:00:00), +rgba (00:00:00), +( (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +. (00:00:00), +3 (00:00:00), +) (00:00:00), +; (00:00:00), +transform (00:00:00), +: (00:00:00), +scale (00:00:00), +( (00:00:00), +1 (00:00:00), +. (00:00:00), +05 (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +inventoryInfo (00:00:00), +{ (00:00:00), +margin (00:00:00), +- (00:00:00), +top (00:00:00), +: (00:00:00), +20px (00:00:00), +; (00:00:00), +text (00:00:00), +- (00:00:00), +align (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +inventoryInfo (00:00:00), +p (00:00:00), +{ (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +18px (00:00:00), +; (00:00:00), +margin (00:00:00), +: (00:00:00), +5px (00:00:00), +0 (00:00:00), +; (00:00:00), +} (00:00:00)</t>
         </is>
       </c>
       <c r="N36" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>-place (00:04:49), -showMarkerAt (00:04:58), -( (00:04:59), -place (00:05:00), -. (00:05:01), -top (00:05:02), -, (00:05:03), -place (00:05:04), -. (00:05:05), -left (00:05:06), -) (00:05:07), -; (00:05:08), +const (00:00:00), +mapContainer (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +mapContainer (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +btn (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +btn (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +try (00:00:00), +{ (00:00:00), +item (00:00:00), +showInventory (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +catch (00:00:00), +( (00:00:00), +err (00:00:00), +) (00:00:00), +{ (00:00:00), +console (00:00:00), +. (00:00:00), +error (00:00:00), +( (00:00:00), +" (00:00:00), +Invalid (00:00:00), +QR (00:00:00), +code (00:00:00), +data (00:00:00), +" (00:00:00), +, (00:00:00), +err (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +function (00:00:00), +showInventory (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +{ (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +itemName (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Name (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +( (00:00:00), +item (00:00:00), +. (00:00:00), +name (00:00:00), +| (00:00:00), +| (00:00:00), +" (00:00:00), +Unknown (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +inStore (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +In (00:00:00), +Store (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +( (00:00:00), +item (00:00:00), +. (00:00:00), +in (00:00:00), +_ (00:00:00), +store (00:00:00), +? (00:00:00), +" (00:00:00), +Yes (00:00:00), +" (00:00:00), +: (00:00:00), +" (00:00:00), +No (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +price (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Price (00:00:00), +: (00:00:00), +€ (00:00:00), +" (00:00:00), ++ (00:00:00), +( (00:00:00), +item (00:00:00), +. (00:00:00), +price (00:00:00), +| (00:00:00), +| (00:00:00), +" (00:00:00), +0 (00:00:00), +. (00:00:00), +00 (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +function (00:00:00), +showMarkerAt (00:00:00), +( (00:00:00), +top (00:00:00), +, (00:00:00), +left (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +marker (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +marker (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +marker (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +top (00:00:00), += (00:00:00), +top (00:00:00), +; (00:00:00), +marker (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +left (00:00:00), += (00:00:00), +left (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+          <t>-place (00:04:49) ~0.00, -showMarkerAt (00:04:58), -( (00:04:59), -place (00:05:00), -. (00:05:01), -top (00:05:02), -, (00:05:03), -place (00:05:04), -. (00:05:05), -left (00:05:06), -) (00:05:07), -; (00:05:08), +const (00:00:00), +mapContainer (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +mapContainer (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +btn (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +btn (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +try (00:00:00), +{ (00:00:00), +item (00:00:00), +showInventory (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +catch (00:00:00), +( (00:00:00), +err (00:00:00), +) (00:00:00), +{ (00:00:00), +console (00:00:00), +. (00:00:00), +error (00:00:00), +( (00:00:00), +" (00:00:00), +Invalid (00:00:00), +QR (00:00:00), +code (00:00:00), +data (00:00:00), +" (00:00:00), +, (00:00:00), +err (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +function (00:00:00), +showInventory (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +{ (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +itemName (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Name (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +( (00:00:00), +item (00:00:00), +. (00:00:00), +name (00:00:00), +| (00:00:00), +| (00:00:00), +" (00:00:00), +Unknown (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +inStore (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +In (00:00:00), +Store (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +( (00:00:00), +item (00:00:00), +. (00:00:00), +in (00:00:00), +_ (00:00:00), +store (00:00:00), +? (00:00:00), +" (00:00:00), +Yes (00:00:00), +" (00:00:00), +: (00:00:00), +" (00:00:00), +No (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +price (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Price (00:00:00), +: (00:00:00), +€ (00:00:00), +" (00:00:00), ++ (00:00:00), +( (00:00:00), +item (00:00:00), +. (00:00:00), +price (00:00:00), +| (00:00:00), +| (00:00:00), +" (00:00:00), +0 (00:00:00), +. (00:00:00), +00 (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +function (00:00:00), +showMarkerAt (00:00:00), +( (00:00:00), +top (00:00:00), +, (00:00:00), +left (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +marker (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +marker (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +marker (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +top (00:00:00), += (00:00:00), +top (00:00:00), +; (00:00:00), +marker (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +left (00:00:00), += (00:00:00), +left (00:00:00), +; (00:00:00), +} (00:00:00)</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>-280 (00:00:08), -body (00:00:17), -{ (00:00:18), -display (00:00:19), -: (00:00:20), -flex (00:00:21), -; (00:00:22), -flex (00:00:23), -- (00:00:24), -direction (00:00:25), -: (00:00:26), -column (00:00:27), -; (00:00:28), -align (00:00:29), -- (00:00:30), -items (00:00:31), -: (00:00:32), -center (00:00:33), -; (00:00:34), -margin (00:00:35), -: (00:00:36), -0 (00:00:37), -; (00:00:38), -} (00:00:39), -h1 (00:00:40), -{ (00:00:41), -font (00:00:42), -- (00:00:43), -family (00:00:44), -: (00:00:45), -" (00:00:46), -Arial (00:00:47), -" (00:00:48), -; (00:00:49), -color (00:00:50), -: (00:00:51), -var (00:00:52), -( (00:00:53), -- (00:00:54), -- (00:00:55), -theme (00:00:56), -) (00:00:57), -; (00:00:58), -} (00:00:59), -# (00:01:00), -map (00:01:01), -{ (00:01:02), -width (00:01:03), -: (00:01:04), -100 (00:01:05), -% (00:01:06), -; (00:01:07), -} (00:01:08), -# (00:01:09), -marker (00:01:10), -{ (00:01:11), -width (00:01:12), -: (00:01:13), -3vw (00:01:14), -; (00:01:15), -height (00:01:26), -: (00:01:27), -3vw (00:01:28), -; (00:01:29), -background (00:01:30), -- (00:01:31), -color (00:01:32), -: (00:01:33), -black (00:01:34), -; (00:01:35), -border (00:01:36), -- (00:01:37), -radius (00:01:38), -: (00:01:39), -50 (00:01:40), -% (00:01:41), -; (00:01:42), -outline (00:01:43), -: (00:01:44), -5px (00:01:45), -solid (00:01:46), -var (00:01:47), -( (00:01:48), -- (00:01:49), -- (00:01:50), -theme (00:01:51), -) (00:01:52), -; (00:01:53), -border (00:02:03), -: (00:02:04), -5px (00:02:05), -solid (00:02:06), -white (00:02:07), -; (00:02:08), -position (00:02:16), -: (00:02:17), -absolute (00:02:18), -; (00:02:19), -top (00:02:20), -: (00:02:21), -0 (00:02:22), -; (00:02:23), -left (00:02:24), -: (00:02:25), -0 (00:02:26), -; (00:02:27), -transform (00:02:28), -: (00:02:29), -translate (00:02:30), -( (00:02:31), -- (00:02:32), -50 (00:02:33), -% (00:02:34), -, (00:02:35), -- (00:02:36), -50 (00:02:37), -% (00:02:38), -) (00:02:39), -; (00:02:40), -} (00:02:41), -# (00:02:42), -mapContainer (00:02:43), -{ (00:02:44), -position (00:02:45), -: (00:02:46), -relative (00:02:47), -; (00:02:48), -display (00:02:49), -: (00:02:50), -none (00:02:51), -; (00:02:52), -} (00:02:53), -# (00:02:54), -camera (00:02:55), -{ (00:02:56), -width (00:02:57), -: (00:02:58), -100 (00:02:59), -% (00:03:00), -; (00:03:01), -} (00:03:02), +000000 (00:00:00), +# (00:00:00), +btn (00:00:00), +{ (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +var (00:00:00), +( (00:00:00), +- (00:00:00), +- (00:00:00), +theme (00:00:00), +) (00:00:00), +; (00:00:00), +color (00:00:00), +: (00:00:00), +white (00:00:00), +; (00:00:00), +border (00:00:00), +: (00:00:00), +none (00:00:00), +; (00:00:00), +padding (00:00:00), +: (00:00:00), +12px (00:00:00), +30px (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +18px (00:00:00), +; (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +8px (00:00:00), +; (00:00:00), +transition (00:00:00), +: (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +0 (00:00:00), +. (00:00:00), +3s (00:00:00), +ease (00:00:00), +, (00:00:00), +transform (00:00:00), +0 (00:00:00), +. (00:00:00), +2s (00:00:00), +ease (00:00:00), +, (00:00:00), +box (00:00:00), +- (00:00:00), +shadow (00:00:00), +0 (00:00:00), +. (00:00:00), +3s (00:00:00), +ease (00:00:00), +; (00:00:00), +box (00:00:00), +- (00:00:00), +shadow (00:00:00), +: (00:00:00), +0 (00:00:00), +4px (00:00:00), +8px (00:00:00), +rgba (00:00:00), +( (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +. (00:00:00), +1 (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +btn (00:00:00), +: (00:00:00), +hover (00:00:00), +{ (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +333333 (00:00:00), +; (00:00:00), +transform (00:00:00), +: (00:00:00), +scale (00:00:00), +( (00:00:00), +1 (00:00:00), +. (00:00:00), +1 (00:00:00), +) (00:00:00), +; (00:00:00), +cursor (00:00:00), +: (00:00:00), +pointer (00:00:00), +; (00:00:00), +box (00:00:00), +- (00:00:00), +shadow (00:00:00), +: (00:00:00), +0 (00:00:00), +6px (00:00:00), +15px (00:00:00), +rgba (00:00:00), +( (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +. (00:00:00), +2 (00:00:00), +) (00:00:00), +; (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +fff (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +btn (00:00:00), +: (00:00:00), +active (00:00:00), +{ (00:00:00), +transform (00:00:00), +: (00:00:00), +scale (00:00:00), +( (00:00:00), +1 (00:00:00), +) (00:00:00), +; (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +var (00:00:00), +( (00:00:00), +- (00:00:00), +- (00:00:00), +theme (00:00:00), +) (00:00:00), +; (00:00:00), +box (00:00:00), +- (00:00:00), +shadow (00:00:00), +: (00:00:00), +0 (00:00:00), +4px (00:00:00), +8px (00:00:00), +rgba (00:00:00), +( (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +. (00:00:00), +1 (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+          <t>-280 (00:00:08) ~0.17, -body (00:00:17), -{ (00:00:18), -display (00:00:19), -: (00:00:20), -flex (00:00:21), -; (00:00:22), -flex (00:00:23), -- (00:00:24), -direction (00:00:25), -: (00:00:26), -column (00:00:27), -; (00:00:28), -align (00:00:29), -- (00:00:30), -items (00:00:31), -: (00:00:32), -center (00:00:33), -; (00:00:34), -margin (00:00:35), -: (00:00:36), -0 (00:00:37), -; (00:00:38), -} (00:00:39), -h1 (00:00:40), -{ (00:00:41), -font (00:00:42), -- (00:00:43), -family (00:00:44), -: (00:00:45), -" (00:00:46), -Arial (00:00:47), -" (00:00:48), -; (00:00:49), -color (00:00:50), -: (00:00:51), -var (00:00:52), -( (00:00:53), -- (00:00:54), -- (00:00:55), -theme (00:00:56), -) (00:00:57), -; (00:00:58), -} (00:00:59), -# (00:01:00), -map (00:01:01), -{ (00:01:02), -width (00:01:03), -: (00:01:04), -100 (00:01:05), -% (00:01:06), -; (00:01:07), -} (00:01:08), -# (00:01:09), -marker (00:01:10), -{ (00:01:11), -width (00:01:12), -: (00:01:13), -3vw (00:01:14), -; (00:01:15), -height (00:01:26), -: (00:01:27), -3vw (00:01:28), -; (00:01:29), -background (00:01:30), -- (00:01:31), -color (00:01:32), -: (00:01:33), -black (00:01:34), -; (00:01:35), -border (00:01:36), -- (00:01:37), -radius (00:01:38), -: (00:01:39), -50 (00:01:40), -% (00:01:41), -; (00:01:42), -outline (00:01:43), -: (00:01:44), -5px (00:01:45), -solid (00:01:46), -var (00:01:47), -( (00:01:48), -- (00:01:49), -- (00:01:50), -theme (00:01:51), -) (00:01:52), -; (00:01:53), -border (00:02:03), -: (00:02:04), -5px (00:02:05), -solid (00:02:06), -white (00:02:07), -; (00:02:08), -position (00:02:16), -: (00:02:17), -absolute (00:02:18), -; (00:02:19), -top (00:02:20), -: (00:02:21), -0 (00:02:22), -; (00:02:23), -left (00:02:24), -: (00:02:25), -0 (00:02:26), -; (00:02:27), -transform (00:02:28), -: (00:02:29), -translate (00:02:30), -( (00:02:31), -- (00:02:32), -50 (00:02:33), -% (00:02:34), -, (00:02:35), -- (00:02:36), -50 (00:02:37), -% (00:02:38), -) (00:02:39), -; (00:02:40), -} (00:02:41), -# (00:02:42), -mapContainer (00:02:43), -{ (00:02:44), -position (00:02:45), -: (00:02:46), -relative (00:02:47), -; (00:02:48), -display (00:02:49), -: (00:02:50), -none (00:02:51), -; (00:02:52), -} (00:02:53), -# (00:02:54), -camera (00:02:55), -{ (00:02:56), -width (00:02:57), -: (00:02:58), -100 (00:02:59), -% (00:03:00), -; (00:03:01), -} (00:03:02), +000000 (00:00:00), +# (00:00:00), +btn (00:00:00), +{ (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +var (00:00:00), +( (00:00:00), +- (00:00:00), +- (00:00:00), +theme (00:00:00), +) (00:00:00), +; (00:00:00), +color (00:00:00), +: (00:00:00), +white (00:00:00), +; (00:00:00), +border (00:00:00), +: (00:00:00), +none (00:00:00), +; (00:00:00), +padding (00:00:00), +: (00:00:00), +12px (00:00:00), +30px (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +18px (00:00:00), +; (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +8px (00:00:00), +; (00:00:00), +transition (00:00:00), +: (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +0 (00:00:00), +. (00:00:00), +3s (00:00:00), +ease (00:00:00), +, (00:00:00), +transform (00:00:00), +0 (00:00:00), +. (00:00:00), +2s (00:00:00), +ease (00:00:00), +, (00:00:00), +box (00:00:00), +- (00:00:00), +shadow (00:00:00), +0 (00:00:00), +. (00:00:00), +3s (00:00:00), +ease (00:00:00), +; (00:00:00), +box (00:00:00), +- (00:00:00), +shadow (00:00:00), +: (00:00:00), +0 (00:00:00), +4px (00:00:00), +8px (00:00:00), +rgba (00:00:00), +( (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +. (00:00:00), +1 (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +btn (00:00:00), +: (00:00:00), +hover (00:00:00), +{ (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +333333 (00:00:00), +; (00:00:00), +transform (00:00:00), +: (00:00:00), +scale (00:00:00), +( (00:00:00), +1 (00:00:00), +. (00:00:00), +1 (00:00:00), +) (00:00:00), +; (00:00:00), +cursor (00:00:00), +: (00:00:00), +pointer (00:00:00), +; (00:00:00), +box (00:00:00), +- (00:00:00), +shadow (00:00:00), +: (00:00:00), +0 (00:00:00), +6px (00:00:00), +15px (00:00:00), +rgba (00:00:00), +( (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +. (00:00:00), +2 (00:00:00), +) (00:00:00), +; (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +fff (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +btn (00:00:00), +: (00:00:00), +active (00:00:00), +{ (00:00:00), +transform (00:00:00), +: (00:00:00), +scale (00:00:00), +( (00:00:00), +1 (00:00:00), +) (00:00:00), +; (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +var (00:00:00), +( (00:00:00), +- (00:00:00), +- (00:00:00), +theme (00:00:00), +) (00:00:00), +; (00:00:00), +box (00:00:00), +- (00:00:00), +shadow (00:00:00), +: (00:00:00), +0 (00:00:00), +4px (00:00:00), +8px (00:00:00), +rgba (00:00:00), +( (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +. (00:00:00), +1 (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00)</t>
         </is>
       </c>
       <c r="N42" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>-const (00:03:03), -new (00:03:06), -Html5Qrcode (00:03:07), -( (00:03:08), -" (00:03:09), -camera (00:03:10), -" (00:03:11), -) (00:03:12), -; (00:03:13), -reader (00:04:28), -. (00:04:29), -start (00:04:30), -( (00:04:31), -{ (00:04:32), -facingMode (00:04:33), -: (00:04:34), -" (00:04:35), -environment (00:04:36), -" (00:04:37), -} (00:04:38), -, (00:04:39), -{ (00:04:40), -} (00:04:41), -, (00:04:42), -function (00:04:43), -( (00:04:44), -text (00:04:45), -) (00:04:46), -{ (00:04:47), -const (00:04:48), -place (00:04:49), -= (00:04:50), -JSON (00:04:51), -. (00:04:52), -parse (00:04:53), -( (00:04:54), -text (00:04:55), -) (00:04:56), -; (00:04:57), -showMarkerAt (00:04:58), -( (00:04:59), -place (00:05:00), -. (00:05:01), -top (00:05:02), -, (00:05:03), -place (00:05:04), -. (00:05:05), -left (00:05:06), -) (00:05:07), -; (00:05:08), -toggleScanner (00:05:09), -( (00:05:10), -) (00:05:11), -; (00:05:12), -} (00:05:13), -) (00:05:14), -. (00:05:15), -catch (00:05:16), -( (00:05:17), -function (00:05:18), -( (00:05:19), -err (00:05:20), -) (00:05:21), -{ (00:05:22), -console (00:05:23), -. (00:05:24), -error (00:05:25), -( (00:05:26), -err (00:05:27), -) (00:05:28), -; (00:05:29), -} (00:05:30), -) (00:05:31), -; (00:05:32), -stop (00:05:41), -function (00:05:46), -showMarkerAt (00:05:47), -( (00:05:48), -top (00:05:49), -, (00:05:50), -left (00:05:51), -) (00:05:52), -{ (00:05:53), -marker (00:05:54), -. (00:05:55), -style (00:05:56), -. (00:05:57), -top (00:05:58), -= (00:05:59), -top (00:06:00), -; (00:06:01), -marker (00:06:02), -. (00:06:03), -style (00:06:04), -. (00:06:05), -left (00:06:06), -= (00:06:07), -left (00:06:08), -; (00:06:09), -} (00:06:10), +let (00:00:00), +null (00:00:00), +reader (00:00:00), += (00:00:00), +new (00:00:00), +Html5QrcodeScanner (00:00:00), +( (00:00:00), +" (00:00:00), +qr (00:00:00), +- (00:00:00), +reader (00:00:00), +" (00:00:00), +, (00:00:00), +{ (00:00:00), +fps (00:00:00), +: (00:00:00), +10 (00:00:00), +, (00:00:00), +qrbox (00:00:00), +: (00:00:00), +250 (00:00:00), +} (00:00:00), +) (00:00:00), +; (00:00:00), +reader (00:00:00), +. (00:00:00), +render (00:00:00), +( (00:00:00), +onScanSuccess (00:00:00), +, (00:00:00), +onScanError (00:00:00), +) (00:00:00), +; (00:00:00), +function (00:00:00), +onScanSuccess (00:00:00), +( (00:00:00), +decodedText (00:00:00), +, (00:00:00), +decodedResult (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +item (00:00:00), += (00:00:00), +JSON (00:00:00), +. (00:00:00), +parse (00:00:00), +( (00:00:00), +decodedText (00:00:00), +) (00:00:00), +; (00:00:00), +displayItemDetails (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +; (00:00:00), +toggleScanner (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +function (00:00:00), +onScanError (00:00:00), +( (00:00:00), +errorMessage (00:00:00), +) (00:00:00), +{ (00:00:00), +console (00:00:00), +. (00:00:00), +error (00:00:00), +( (00:00:00), +" (00:00:00), +Error (00:00:00), +scanning (00:00:00), +QR (00:00:00), +code (00:00:00), +: (00:00:00), +" (00:00:00), +, (00:00:00), +errorMessage (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +clear (00:00:00), +function (00:00:00), +displayItemDetails (00:00:00), +( (00:00:00), +data (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +nameParagraph (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +item (00:00:00), +- (00:00:00), +name (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +inStockParagraph (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +in (00:00:00), +- (00:00:00), +stock (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +priceParagraph (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +price (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +nameParagraph (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +Name (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +data (00:00:00), +. (00:00:00), +name (00:00:00), +; (00:00:00), +inStockParagraph (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +In (00:00:00), +Stock (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +( (00:00:00), +data (00:00:00), +. (00:00:00), +inStock (00:00:00), +? (00:00:00), +" (00:00:00), +Yes (00:00:00), +" (00:00:00), +: (00:00:00), +" (00:00:00), +No (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +priceParagraph (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +Price (00:00:00), +: (00:00:00), +€ (00:00:00), +" (00:00:00), ++ (00:00:00), +data (00:00:00), +. (00:00:00), +price (00:00:00), +. (00:00:00), +toFixed (00:00:00), +( (00:00:00), +2 (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+          <t>-const (00:03:03) ~0.20, -new (00:03:06), -Html5Qrcode (00:03:07), -( (00:03:08), -" (00:03:09), -camera (00:03:10), -" (00:03:11), -) (00:03:12), -; (00:03:13), -reader (00:04:28), -. (00:04:29), -start (00:04:30), -( (00:04:31), -{ (00:04:32), -facingMode (00:04:33), -: (00:04:34), -" (00:04:35), -environment (00:04:36), -" (00:04:37), -} (00:04:38), -, (00:04:39), -{ (00:04:40), -} (00:04:41), -, (00:04:42), -function (00:04:43), -( (00:04:44), -text (00:04:45), -) (00:04:46), -{ (00:04:47), -const (00:04:48), -place (00:04:49), -= (00:04:50), -JSON (00:04:51), -. (00:04:52), -parse (00:04:53), -( (00:04:54), -text (00:04:55), -) (00:04:56), -; (00:04:57), -showMarkerAt (00:04:58), -( (00:04:59), -place (00:05:00), -. (00:05:01), -top (00:05:02), -, (00:05:03), -place (00:05:04), -. (00:05:05), -left (00:05:06), -) (00:05:07), -; (00:05:08), -toggleScanner (00:05:09), -( (00:05:10), -) (00:05:11), -; (00:05:12), -} (00:05:13), -) (00:05:14), -. (00:05:15), -catch (00:05:16), -( (00:05:17), -function (00:05:18), -( (00:05:19), -err (00:05:20), -) (00:05:21), -{ (00:05:22), -console (00:05:23), -. (00:05:24), -error (00:05:25), -( (00:05:26), -err (00:05:27), -) (00:05:28), -; (00:05:29), -} (00:05:30), -) (00:05:31), -; (00:05:32), -stop (00:05:41) ~0.00, -function (00:05:46), -showMarkerAt (00:05:47), -( (00:05:48), -top (00:05:49), -, (00:05:50), -left (00:05:51), -) (00:05:52), -{ (00:05:53), -marker (00:05:54), -. (00:05:55), -style (00:05:56), -. (00:05:57), -top (00:05:58), -= (00:05:59), -top (00:06:00), -; (00:06:01), -marker (00:06:02), -. (00:06:03), -style (00:06:04), -. (00:06:05), -left (00:06:06), -= (00:06:07), -left (00:06:08), -; (00:06:09), -} (00:06:10), +let (00:00:00), +null (00:00:00), +reader (00:00:00), += (00:00:00), +new (00:00:00), +Html5QrcodeScanner (00:00:00), +( (00:00:00), +" (00:00:00), +qr (00:00:00), +- (00:00:00), +reader (00:00:00), +" (00:00:00), +, (00:00:00), +{ (00:00:00), +fps (00:00:00), +: (00:00:00), +10 (00:00:00), +, (00:00:00), +qrbox (00:00:00), +: (00:00:00), +250 (00:00:00), +} (00:00:00), +) (00:00:00), +; (00:00:00), +reader (00:00:00), +. (00:00:00), +render (00:00:00), +( (00:00:00), +onScanSuccess (00:00:00), +, (00:00:00), +onScanError (00:00:00), +) (00:00:00), +; (00:00:00), +function (00:00:00), +onScanSuccess (00:00:00), +( (00:00:00), +decodedText (00:00:00), +, (00:00:00), +decodedResult (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +item (00:00:00), += (00:00:00), +JSON (00:00:00), +. (00:00:00), +parse (00:00:00), +( (00:00:00), +decodedText (00:00:00), +) (00:00:00), +; (00:00:00), +displayItemDetails (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +; (00:00:00), +toggleScanner (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +function (00:00:00), +onScanError (00:00:00), +( (00:00:00), +errorMessage (00:00:00), +) (00:00:00), +{ (00:00:00), +console (00:00:00), +. (00:00:00), +error (00:00:00), +( (00:00:00), +" (00:00:00), +Error (00:00:00), +scanning (00:00:00), +QR (00:00:00), +code (00:00:00), +: (00:00:00), +" (00:00:00), +, (00:00:00), +errorMessage (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +clear (00:00:00), +function (00:00:00), +displayItemDetails (00:00:00), +( (00:00:00), +data (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +nameParagraph (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +item (00:00:00), +- (00:00:00), +name (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +inStockParagraph (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +in (00:00:00), +- (00:00:00), +stock (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +priceParagraph (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +price (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +nameParagraph (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +Name (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +data (00:00:00), +. (00:00:00), +name (00:00:00), +; (00:00:00), +inStockParagraph (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +In (00:00:00), +Stock (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +( (00:00:00), +data (00:00:00), +. (00:00:00), +inStock (00:00:00), +? (00:00:00), +" (00:00:00), +Yes (00:00:00), +" (00:00:00), +: (00:00:00), +" (00:00:00), +No (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +priceParagraph (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +Price (00:00:00), +: (00:00:00), +€ (00:00:00), +" (00:00:00), ++ (00:00:00), +data (00:00:00), +. (00:00:00), +price (00:00:00), +. (00:00:00), +toFixed (00:00:00), +( (00:00:00), +2 (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00)</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>-place (00:04:49), -place (00:05:00), -place (00:05:04), +item (00:00:00), +item (00:00:00), +item (00:00:00), +showInventory (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +; (00:00:00), +function (00:00:00), +showInventory (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +{ (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +name (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Name (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +name (00:00:00), +; (00:00:00), +if (00:00:00), +( (00:00:00), +item (00:00:00), +. (00:00:00), +inStock (00:00:00), +) (00:00:00), +{ (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +stock (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +in (00:00:00), +stock (00:00:00), +: (00:00:00), +Yes (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00), +else (00:00:00), +{ (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +stock (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +in (00:00:00), +stock (00:00:00), +: (00:00:00), +No (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +price (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Price (00:00:00), +: (00:00:00), +€ (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +price (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+          <t>-place (00:04:49) ~0.00, -place (00:05:00) ~0.00, -place (00:05:04) ~0.00, +item (00:00:00), +item (00:00:00), +item (00:00:00), +showInventory (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +; (00:00:00), +function (00:00:00), +showInventory (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +{ (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +name (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Name (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +name (00:00:00), +; (00:00:00), +if (00:00:00), +( (00:00:00), +item (00:00:00), +. (00:00:00), +inStock (00:00:00), +) (00:00:00), +{ (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +stock (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +in (00:00:00), +stock (00:00:00), +: (00:00:00), +Yes (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00), +else (00:00:00), +{ (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +stock (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +in (00:00:00), +stock (00:00:00), +: (00:00:00), +No (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +price (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Price (00:00:00), +: (00:00:00), +€ (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +price (00:00:00), +; (00:00:00), +} (00:00:00)</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -4053,7 +4053,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>-Positioning (00:07:06), -Positioning (00:07:38), +Inventory (00:00:00), +System (00:00:00), +Inventory (00:00:00), +System (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +inventory (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemName (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemStock (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemPrice (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
+          <t>-Positioning (00:07:06) ~0.09, -Positioning (00:07:38) ~0.09, +Inventory (00:00:00), +System (00:00:00), +Inventory (00:00:00), +System (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +inventory (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemName (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemStock (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemPrice (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
         </is>
       </c>
       <c r="L46" t="n">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>-Positioning (00:07:06), -Positioning (00:07:38), +Inventory (00:00:00), +System (00:00:00), +Inventory (00:00:00), +System (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +name (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +store (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +price (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00)</t>
+          <t>-Positioning (00:07:06) ~0.09, -Positioning (00:07:38) ~0.09, +Inventory (00:00:00), +System (00:00:00), +Inventory (00:00:00), +System (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +name (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +store (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +price (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00)</t>
         </is>
       </c>
       <c r="L48" t="n">
@@ -4220,7 +4220,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>-place (00:04:49), -place (00:05:00), -place (00:05:04), +item (00:00:00), +item (00:00:00), +item (00:00:00), +showItemInfo (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +; (00:00:00), +function (00:00:00), +showItemInfo (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +{ (00:00:00), +name (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Name (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +name (00:00:00), +; (00:00:00), +store (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +In (00:00:00), +store (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +( (00:00:00), +item (00:00:00), +. (00:00:00), +in (00:00:00), +_ (00:00:00), +store (00:00:00), +? (00:00:00), +" (00:00:00), +Yes (00:00:00), +" (00:00:00), +: (00:00:00), +" (00:00:00), +No (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +price (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Price (00:00:00), +: (00:00:00), +€ (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +price (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+          <t>-place (00:04:49) ~0.00, -place (00:05:00) ~0.00, -place (00:05:04) ~0.00, +item (00:00:00), +item (00:00:00), +item (00:00:00), +showItemInfo (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +; (00:00:00), +function (00:00:00), +showItemInfo (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +{ (00:00:00), +name (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Name (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +name (00:00:00), +; (00:00:00), +store (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +In (00:00:00), +store (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +( (00:00:00), +item (00:00:00), +. (00:00:00), +in (00:00:00), +_ (00:00:00), +store (00:00:00), +? (00:00:00), +" (00:00:00), +Yes (00:00:00), +" (00:00:00), +: (00:00:00), +" (00:00:00), +No (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +price (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Price (00:00:00), +: (00:00:00), +€ (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +price (00:00:00), +; (00:00:00), +} (00:00:00)</t>
         </is>
       </c>
       <c r="P48" s="3" t="inlineStr">
@@ -4303,7 +4303,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>-viewport (00:06:42), +viewpoint (00:00:00), +&lt; (00:00:00), +style (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +style (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +inventory (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +script (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +script (00:00:00), +&gt; (00:00:00)</t>
+          <t>-viewport (00:06:42) ~0.78, +viewpoint (00:00:00), +&lt; (00:00:00), +style (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +style (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +inventory (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +script (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +script (00:00:00), +&gt; (00:00:00)</t>
         </is>
       </c>
       <c r="L50" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>-onclick (00:08:35), +onClick (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +inventory (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +name (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +stock (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +price (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
+          <t>-onclick (00:08:35) ~0.86, +onClick (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +inventory (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +name (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +stock (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +price (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
         </is>
       </c>
       <c r="L51" t="n">
@@ -4397,7 +4397,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>-place (00:04:49), -place (00:05:00), -place (00:05:04), +item (00:00:00), +item (00:00:00), +item (00:00:00), +displayInventory (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +; (00:00:00), +function (00:00:00), +displayInventory (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +name (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +name (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +stock (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +stock (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +price (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +price (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +name (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +Name (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +name (00:00:00), +; (00:00:00), +stock (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +In (00:00:00), +stock (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +( (00:00:00), +item (00:00:00), +. (00:00:00), +inStock (00:00:00), +? (00:00:00), +" (00:00:00), +yes (00:00:00), +" (00:00:00), +: (00:00:00), +" (00:00:00), +no (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +price (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +Price (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +price (00:00:00), ++ (00:00:00), +" (00:00:00), +€ (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+          <t>-place (00:04:49) ~0.00, -place (00:05:00) ~0.00, -place (00:05:04) ~0.00, +item (00:00:00), +item (00:00:00), +item (00:00:00), +displayInventory (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +; (00:00:00), +function (00:00:00), +displayInventory (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +name (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +name (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +stock (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +stock (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +price (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +price (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +name (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +Name (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +name (00:00:00), +; (00:00:00), +stock (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +In (00:00:00), +stock (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +( (00:00:00), +item (00:00:00), +. (00:00:00), +inStock (00:00:00), +? (00:00:00), +" (00:00:00), +yes (00:00:00), +" (00:00:00), +: (00:00:00), +" (00:00:00), +no (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +price (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +Price (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +price (00:00:00), ++ (00:00:00), +" (00:00:00), +€ (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00)</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>-SCAN (00:08:43), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +name (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +stock (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +price (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +style (00:00:00), += (00:00:00), +" (00:00:00), +- (00:00:00), +- (00:00:00), +theme (00:00:00), +: (00:00:00), +# (00:00:00), +ffc0cb (00:00:00), +" (00:00:00), +Scan (00:00:00)</t>
+          <t>-SCAN (00:08:43) ~0.25, +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +name (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +stock (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +price (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +style (00:00:00), += (00:00:00), +" (00:00:00), +- (00:00:00), +- (00:00:00), +theme (00:00:00), +: (00:00:00), +# (00:00:00), +ffc0cb (00:00:00), +" (00:00:00), +Scan (00:00:00)</t>
         </is>
       </c>
       <c r="L56" t="n">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>-place (00:04:49), -place (00:05:00), -place (00:05:04), +item (00:00:00), +item (00:00:00), +item (00:00:00), +displayItemInfo (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +; (00:00:00), +function (00:00:00), +displayItemInfo (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +{ (00:00:00), +name (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Name (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +name (00:00:00), +; (00:00:00), +inStore (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +In (00:00:00), +store (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +( (00:00:00), +item (00:00:00), +. (00:00:00), +in (00:00:00), +_ (00:00:00), +store (00:00:00), +? (00:00:00), +" (00:00:00), +Yes (00:00:00), +" (00:00:00), +: (00:00:00), +" (00:00:00), +No (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +price (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Price (00:00:00), +: (00:00:00), +€ (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +price (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+          <t>-place (00:04:49) ~0.00, -place (00:05:00) ~0.00, -place (00:05:04) ~0.00, +item (00:00:00), +item (00:00:00), +item (00:00:00), +displayItemInfo (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +; (00:00:00), +function (00:00:00), +displayItemInfo (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +{ (00:00:00), +name (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Name (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +name (00:00:00), +; (00:00:00), +inStore (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +In (00:00:00), +store (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +( (00:00:00), +item (00:00:00), +. (00:00:00), +in (00:00:00), +_ (00:00:00), +store (00:00:00), +? (00:00:00), +" (00:00:00), +Yes (00:00:00), +" (00:00:00), +: (00:00:00), +" (00:00:00), +No (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +price (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Price (00:00:00), +: (00:00:00), +€ (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +price (00:00:00), +; (00:00:00), +} (00:00:00)</t>
         </is>
       </c>
       <c r="P61" s="3" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>-DOCTYPE (00:06:13), +doctype (00:00:00), +/ (00:00:00), +/ (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +inventory (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemName (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Item (00:00:00), +Name (00:00:00), +: (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemStock (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Available (00:00:00), +in (00:00:00), +Store (00:00:00), +: (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemPrice (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Item (00:00:00), +Price (00:00:00), +: (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
+          <t>-DOCTYPE (00:06:13) ~0.00, +doctype (00:00:00), +/ (00:00:00), +/ (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +inventory (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemName (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Item (00:00:00), +Name (00:00:00), +: (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemStock (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Available (00:00:00), +in (00:00:00), +Store (00:00:00), +: (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemPrice (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Item (00:00:00), +Price (00:00:00), +: (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
         </is>
       </c>
       <c r="L62" t="n">
@@ -4982,7 +4982,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>-place (00:04:49), -place (00:05:00), -place (00:05:04), +const (00:00:00), +inventory (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +inventory (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +data (00:00:00), +data (00:00:00), +data (00:00:00), +const (00:00:00), +itemDiv (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +createElement (00:00:00), +( (00:00:00), +" (00:00:00), +div (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +name (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +createElement (00:00:00), +( (00:00:00), +" (00:00:00), +p (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +name (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +Name (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +data (00:00:00), +. (00:00:00), +name (00:00:00), +; (00:00:00), +const (00:00:00), +stock (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +createElement (00:00:00), +( (00:00:00), +" (00:00:00), +p (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +stock (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +In (00:00:00), +Store (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +( (00:00:00), +data (00:00:00), +. (00:00:00), +in (00:00:00), +_ (00:00:00), +store (00:00:00), +? (00:00:00), +" (00:00:00), +Yes (00:00:00), +" (00:00:00), +: (00:00:00), +" (00:00:00), +No (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +price (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +createElement (00:00:00), +( (00:00:00), +" (00:00:00), +p (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +price (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +Price (00:00:00), +: (00:00:00), +€ (00:00:00), +" (00:00:00), ++ (00:00:00), +data (00:00:00), +. (00:00:00), +price (00:00:00), +; (00:00:00), +itemDiv (00:00:00), +. (00:00:00), +appendChild (00:00:00), +( (00:00:00), +name (00:00:00), +) (00:00:00), +; (00:00:00), +itemDiv (00:00:00), +. (00:00:00), +appendChild (00:00:00), +( (00:00:00), +stock (00:00:00), +) (00:00:00), +; (00:00:00), +itemDiv (00:00:00), +. (00:00:00), +appendChild (00:00:00), +( (00:00:00), +price (00:00:00), +) (00:00:00), +; (00:00:00), +inventory (00:00:00), +. (00:00:00), +appendChild (00:00:00), +( (00:00:00), +itemDiv (00:00:00), +) (00:00:00), +; (00:00:00)</t>
+          <t>-place (00:04:49) ~0.20, -place (00:05:00) ~0.20, -place (00:05:04) ~0.20, +const (00:00:00), +inventory (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +inventory (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +data (00:00:00), +data (00:00:00), +data (00:00:00), +const (00:00:00), +itemDiv (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +createElement (00:00:00), +( (00:00:00), +" (00:00:00), +div (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +name (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +createElement (00:00:00), +( (00:00:00), +" (00:00:00), +p (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +name (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +Name (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +data (00:00:00), +. (00:00:00), +name (00:00:00), +; (00:00:00), +const (00:00:00), +stock (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +createElement (00:00:00), +( (00:00:00), +" (00:00:00), +p (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +stock (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +In (00:00:00), +Store (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +( (00:00:00), +data (00:00:00), +. (00:00:00), +in (00:00:00), +_ (00:00:00), +store (00:00:00), +? (00:00:00), +" (00:00:00), +Yes (00:00:00), +" (00:00:00), +: (00:00:00), +" (00:00:00), +No (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +price (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +createElement (00:00:00), +( (00:00:00), +" (00:00:00), +p (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +price (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +Price (00:00:00), +: (00:00:00), +€ (00:00:00), +" (00:00:00), ++ (00:00:00), +data (00:00:00), +. (00:00:00), +price (00:00:00), +; (00:00:00), +itemDiv (00:00:00), +. (00:00:00), +appendChild (00:00:00), +( (00:00:00), +name (00:00:00), +) (00:00:00), +; (00:00:00), +itemDiv (00:00:00), +. (00:00:00), +appendChild (00:00:00), +( (00:00:00), +stock (00:00:00), +) (00:00:00), +; (00:00:00), +itemDiv (00:00:00), +. (00:00:00), +appendChild (00:00:00), +( (00:00:00), +price (00:00:00), +) (00:00:00), +; (00:00:00), +inventory (00:00:00), +. (00:00:00), +appendChild (00:00:00), +( (00:00:00), +itemDiv (00:00:00), +) (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
       <c r="P66" s="3" t="inlineStr">
@@ -5065,7 +5065,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>-Positioning (00:07:06), -Positioning (00:07:38), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +HEAD (00:00:00), +&lt; (00:00:00), +! (00:00:00), +DOCTYPE (00:00:00), +html (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +html (00:00:00), +lang (00:00:00), += (00:00:00), +" (00:00:00), +en (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +head (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +meta (00:00:00), +charset (00:00:00), += (00:00:00), +" (00:00:00), +UTF (00:00:00), +- (00:00:00), +8 (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +meta (00:00:00), +name (00:00:00), += (00:00:00), +" (00:00:00), +viewport (00:00:00), +" (00:00:00), +content (00:00:00), += (00:00:00), +" (00:00:00), +width (00:00:00), += (00:00:00), +device (00:00:00), +- (00:00:00), +width (00:00:00), +, (00:00:00), +initial (00:00:00), +- (00:00:00), +scale (00:00:00), += (00:00:00), +1 (00:00:00), +. (00:00:00), +0 (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +title (00:00:00), +&gt; (00:00:00), +QR (00:00:00), +Inventory (00:00:00), +System (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +title (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +link (00:00:00), +rel (00:00:00), += (00:00:00), +" (00:00:00), +stylesheet (00:00:00), +" (00:00:00), +href (00:00:00), += (00:00:00), +" (00:00:00), +123456 (00:00:00), +- (00:00:00), +p (00:00:00), +. (00:00:00), +css (00:00:00), +" (00:00:00), +/ (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +head (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +body (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +h1 (00:00:00), +&gt; (00:00:00), +QR (00:00:00), +Inventory (00:00:00), +System (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +h1 (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +mapContainer (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +img (00:00:00), +src (00:00:00), += (00:00:00), +" (00:00:00), +map (00:00:00), +. (00:00:00), +png (00:00:00), +" (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +map (00:00:00), +" (00:00:00), +alt (00:00:00), += (00:00:00), +" (00:00:00), +map (00:00:00), +" (00:00:00), +/ (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +marker (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +button (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +btn (00:00:00), +" (00:00:00), +onclick (00:00:00), += (00:00:00), +" (00:00:00), +toggleScanner (00:00:00), +( (00:00:00), +) (00:00:00), +" (00:00:00), +&gt; (00:00:00), +SCAN (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +button (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +inventory (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +camera (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +script (00:00:00), +src (00:00:00), += (00:00:00), +" (00:00:00), +https (00:00:00), +: (00:00:00), +/ (00:00:00), +/ (00:00:00), +unpkg (00:00:00), +. (00:00:00), +com (00:00:00), +/ (00:00:00), +html5 (00:00:00), +- (00:00:00), +qrcode (00:00:00), +" (00:00:00), +type (00:00:00), += (00:00:00), +" (00:00:00), +text (00:00:00), +/ (00:00:00), +javascript (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +script (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +script (00:00:00), +src (00:00:00), += (00:00:00), +" (00:00:00), +123456 (00:00:00), +- (00:00:00), +p (00:00:00), +. (00:00:00), +js (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +script (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +body (00:00:00), +&gt; (00:00:00), += (00:00:00), += (00:00:00), += (00:00:00), += (00:00:00), += (00:00:00), += (00:00:00), += (00:00:00), +Inventory (00:00:00), +System (00:00:00), +Inventory (00:00:00), +System (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +inventory (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +4503462fa4f894817eb35001cb59a566f24c4879 (00:00:00)</t>
+          <t>-Positioning (00:07:06) ~0.09, -Positioning (00:07:38) ~0.09, +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +HEAD (00:00:00), +&lt; (00:00:00), +! (00:00:00), +DOCTYPE (00:00:00), +html (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +html (00:00:00), +lang (00:00:00), += (00:00:00), +" (00:00:00), +en (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +head (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +meta (00:00:00), +charset (00:00:00), += (00:00:00), +" (00:00:00), +UTF (00:00:00), +- (00:00:00), +8 (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +meta (00:00:00), +name (00:00:00), += (00:00:00), +" (00:00:00), +viewport (00:00:00), +" (00:00:00), +content (00:00:00), += (00:00:00), +" (00:00:00), +width (00:00:00), += (00:00:00), +device (00:00:00), +- (00:00:00), +width (00:00:00), +, (00:00:00), +initial (00:00:00), +- (00:00:00), +scale (00:00:00), += (00:00:00), +1 (00:00:00), +. (00:00:00), +0 (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +title (00:00:00), +&gt; (00:00:00), +QR (00:00:00), +Inventory (00:00:00), +System (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +title (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +link (00:00:00), +rel (00:00:00), += (00:00:00), +" (00:00:00), +stylesheet (00:00:00), +" (00:00:00), +href (00:00:00), += (00:00:00), +" (00:00:00), +123456 (00:00:00), +- (00:00:00), +p (00:00:00), +. (00:00:00), +css (00:00:00), +" (00:00:00), +/ (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +head (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +body (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +h1 (00:00:00), +&gt; (00:00:00), +QR (00:00:00), +Inventory (00:00:00), +System (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +h1 (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +mapContainer (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +img (00:00:00), +src (00:00:00), += (00:00:00), +" (00:00:00), +map (00:00:00), +. (00:00:00), +png (00:00:00), +" (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +map (00:00:00), +" (00:00:00), +alt (00:00:00), += (00:00:00), +" (00:00:00), +map (00:00:00), +" (00:00:00), +/ (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +marker (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +button (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +btn (00:00:00), +" (00:00:00), +onclick (00:00:00), += (00:00:00), +" (00:00:00), +toggleScanner (00:00:00), +( (00:00:00), +) (00:00:00), +" (00:00:00), +&gt; (00:00:00), +SCAN (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +button (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +inventory (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +camera (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +script (00:00:00), +src (00:00:00), += (00:00:00), +" (00:00:00), +https (00:00:00), +: (00:00:00), +/ (00:00:00), +/ (00:00:00), +unpkg (00:00:00), +. (00:00:00), +com (00:00:00), +/ (00:00:00), +html5 (00:00:00), +- (00:00:00), +qrcode (00:00:00), +" (00:00:00), +type (00:00:00), += (00:00:00), +" (00:00:00), +text (00:00:00), +/ (00:00:00), +javascript (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +script (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +script (00:00:00), +src (00:00:00), += (00:00:00), +" (00:00:00), +123456 (00:00:00), +- (00:00:00), +p (00:00:00), +. (00:00:00), +js (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +script (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +body (00:00:00), +&gt; (00:00:00), += (00:00:00), += (00:00:00), += (00:00:00), += (00:00:00), += (00:00:00), += (00:00:00), += (00:00:00), +Inventory (00:00:00), +System (00:00:00), +Inventory (00:00:00), +System (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +inventory (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +4503462fa4f894817eb35001cb59a566f24c4879 (00:00:00)</t>
         </is>
       </c>
       <c r="L68" t="n">
@@ -5073,7 +5073,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>-black (00:01:34), -white (00:02:07), +yellow (00:00:00), +red (00:00:00), +button (00:00:00), +{ (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +var (00:00:00), +( (00:00:00), +- (00:00:00), +- (00:00:00), +theme (00:00:00), +) (00:00:00), +; (00:00:00), +color (00:00:00), +: (00:00:00), +white (00:00:00), +; (00:00:00), +cursor (00:00:00), +: (00:00:00), +pointer (00:00:00), +; (00:00:00), +transition (00:00:00), +: (00:00:00), +all (00:00:00), +2s (00:00:00), +ease (00:00:00), +; (00:00:00), +} (00:00:00), +button (00:00:00), +: (00:00:00), +hover (00:00:00), +{ (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +blue (00:00:00), +; (00:00:00), +transform (00:00:00), +: (00:00:00), +scale (00:00:00), +( (00:00:00), +2 (00:00:00), +. (00:00:00), +2 (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +inventory (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +80 (00:00:00), +% (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +family (00:00:00), +: (00:00:00), +' (00:00:00), +Times (00:00:00), +New (00:00:00), +Roman (00:00:00), +' (00:00:00), +, (00:00:00), +Times (00:00:00), +, (00:00:00), +serif (00:00:00), +, (00:00:00), +sans (00:00:00), +- (00:00:00), +serif (00:00:00), +; (00:00:00), +border (00:00:00), +: (00:00:00), +1px (00:00:00), +solid (00:00:00), +var (00:00:00), +( (00:00:00), +- (00:00:00), +- (00:00:00), +theme (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +inventory (00:00:00), +p (00:00:00), +{ (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +red (00:00:00), +; (00:00:00), +text (00:00:00), +- (00:00:00), +align (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +} (00:00:00), +: (00:00:00), +root (00:00:00), +{ (00:00:00), +- (00:00:00), +- (00:00:00), +theme (00:00:00), +: (00:00:00), +# (00:00:00), +280 (00:00:00), +; (00:00:00), +} (00:00:00), +body (00:00:00), +{ (00:00:00), +display (00:00:00), +: (00:00:00), +flex (00:00:00), +; (00:00:00), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +margin (00:00:00), +: (00:00:00), +0 (00:00:00), +; (00:00:00), +} (00:00:00), +h1 (00:00:00), +{ (00:00:00), +font (00:00:00), +- (00:00:00), +family (00:00:00), +: (00:00:00), +" (00:00:00), +Arial (00:00:00), +" (00:00:00), +; (00:00:00), +color (00:00:00), +: (00:00:00), +var (00:00:00), +( (00:00:00), +- (00:00:00), +- (00:00:00), +theme (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +map (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +100 (00:00:00), +% (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +marker (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +3vw (00:00:00), +; (00:00:00), +height (00:00:00), +: (00:00:00), +3vw (00:00:00), +; (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +yellow (00:00:00), +; (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +50 (00:00:00), +% (00:00:00), +; (00:00:00), +outline (00:00:00), +: (00:00:00), +5px (00:00:00), +solid (00:00:00), +var (00:00:00), +( (00:00:00), +- (00:00:00), +- (00:00:00), +theme (00:00:00), +) (00:00:00), +; (00:00:00), +border (00:00:00), +: (00:00:00), +5px (00:00:00), +solid (00:00:00), +red (00:00:00), +; (00:00:00), +position (00:00:00), +: (00:00:00), +absolute (00:00:00), +; (00:00:00), +top (00:00:00), +: (00:00:00), +0 (00:00:00), +; (00:00:00), +left (00:00:00), +: (00:00:00), +0 (00:00:00), +; (00:00:00), +transform (00:00:00), +: (00:00:00), +translate (00:00:00), +( (00:00:00), +- (00:00:00), +50 (00:00:00), +% (00:00:00), +, (00:00:00), +- (00:00:00), +50 (00:00:00), +% (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +mapContainer (00:00:00), +{ (00:00:00), +position (00:00:00), +: (00:00:00), +relative (00:00:00), +; (00:00:00), +display (00:00:00), +: (00:00:00), +none (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +camera (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +100 (00:00:00), +% (00:00:00), +; (00:00:00), +} (00:00:00), +button (00:00:00), +{ (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +var (00:00:00), +( (00:00:00), +- (00:00:00), +- (00:00:00), +theme (00:00:00), +) (00:00:00), +; (00:00:00), +color (00:00:00), +: (00:00:00), +white (00:00:00), +; (00:00:00), +cursor (00:00:00), +: (00:00:00), +pointer (00:00:00), +; (00:00:00), +transition (00:00:00), +: (00:00:00), +all (00:00:00), +2s (00:00:00), +ease (00:00:00), +; (00:00:00), +} (00:00:00), +button (00:00:00), +: (00:00:00), +hover (00:00:00), +{ (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +blue (00:00:00), +; (00:00:00), +transform (00:00:00), +: (00:00:00), +scale (00:00:00), +( (00:00:00), +2 (00:00:00), +. (00:00:00), +2 (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +inventory (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +80 (00:00:00), +% (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +family (00:00:00), +: (00:00:00), +' (00:00:00), +Times (00:00:00), +New (00:00:00), +Roman (00:00:00), +' (00:00:00), +, (00:00:00), +Times (00:00:00), +, (00:00:00), +serif (00:00:00), +, (00:00:00), +sans (00:00:00), +- (00:00:00), +serif (00:00:00), +; (00:00:00), +border (00:00:00), +: (00:00:00), +1px (00:00:00), +solid (00:00:00), +var (00:00:00), +( (00:00:00), +- (00:00:00), +- (00:00:00), +theme (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +inventory (00:00:00), +p (00:00:00), +{ (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +red (00:00:00), +; (00:00:00), +text (00:00:00), +- (00:00:00), +align (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +} (00:00:00), +: (00:00:00), +root (00:00:00), +{ (00:00:00), +- (00:00:00), +- (00:00:00), +theme (00:00:00), +: (00:00:00), +# (00:00:00), +280 (00:00:00), +; (00:00:00), +} (00:00:00), +body (00:00:00), +{ (00:00:00), +display (00:00:00), +: (00:00:00), +flex (00:00:00), +; (00:00:00), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +margin (00:00:00), +: (00:00:00), +0 (00:00:00), +; (00:00:00), +} (00:00:00), +h1 (00:00:00), +{ (00:00:00), +font (00:00:00), +- (00:00:00), +family (00:00:00), +: (00:00:00), +" (00:00:00), +Arial (00:00:00), +" (00:00:00), +; (00:00:00), +color (00:00:00), +: (00:00:00), +var (00:00:00), +( (00:00:00), +- (00:00:00), +- (00:00:00), +theme (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +map (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +100 (00:00:00), +% (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +marker (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +3vw (00:00:00), +; (00:00:00), +height (00:00:00), +: (00:00:00), +3vw (00:00:00), +; (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +black (00:00:00), +; (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +50 (00:00:00), +% (00:00:00), +; (00:00:00), +outline (00:00:00), +: (00:00:00), +5px (00:00:00), +solid (00:00:00), +var (00:00:00), +( (00:00:00), +- (00:00:00), +- (00:00:00), +theme (00:00:00), +) (00:00:00), +; (00:00:00), +border (00:00:00), +: (00:00:00), +5px (00:00:00), +solid (00:00:00), +white (00:00:00), +; (00:00:00), +position (00:00:00), +: (00:00:00), +absolute (00:00:00), +; (00:00:00), +top (00:00:00), +: (00:00:00), +0 (00:00:00), +; (00:00:00), +left (00:00:00), +: (00:00:00), +0 (00:00:00), +; (00:00:00), +transform (00:00:00), +: (00:00:00), +translate (00:00:00), +( (00:00:00), +- (00:00:00), +50 (00:00:00), +% (00:00:00), +, (00:00:00), +- (00:00:00), +50 (00:00:00), +% (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +mapContainer (00:00:00), +{ (00:00:00), +position (00:00:00), +: (00:00:00), +relative (00:00:00), +; (00:00:00), +display (00:00:00), +: (00:00:00), +none (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +camera (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +100 (00:00:00), +% (00:00:00), +; (00:00:00), +} (00:00:00), +button (00:00:00), +{ (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +var (00:00:00), +( (00:00:00), +- (00:00:00), +- (00:00:00), +theme (00:00:00), +) (00:00:00), +; (00:00:00), +color (00:00:00), +: (00:00:00), +white (00:00:00), +; (00:00:00), +cursor (00:00:00), +: (00:00:00), +pointer (00:00:00), +; (00:00:00), +transition (00:00:00), +: (00:00:00), +all (00:00:00), +2s (00:00:00), +ease (00:00:00), +; (00:00:00), +} (00:00:00), +button (00:00:00), +: (00:00:00), +hover (00:00:00), +{ (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +blue (00:00:00), +; (00:00:00), +transform (00:00:00), +: (00:00:00), +scale (00:00:00), +( (00:00:00), +2 (00:00:00), +. (00:00:00), +2 (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+          <t>-black (00:01:34) ~0.17, -white (00:02:07) ~0.00, +yellow (00:00:00), +red (00:00:00), +button (00:00:00), +{ (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +var (00:00:00), +( (00:00:00), +- (00:00:00), +- (00:00:00), +theme (00:00:00), +) (00:00:00), +; (00:00:00), +color (00:00:00), +: (00:00:00), +white (00:00:00), +; (00:00:00), +cursor (00:00:00), +: (00:00:00), +pointer (00:00:00), +; (00:00:00), +transition (00:00:00), +: (00:00:00), +all (00:00:00), +2s (00:00:00), +ease (00:00:00), +; (00:00:00), +} (00:00:00), +button (00:00:00), +: (00:00:00), +hover (00:00:00), +{ (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +blue (00:00:00), +; (00:00:00), +transform (00:00:00), +: (00:00:00), +scale (00:00:00), +( (00:00:00), +2 (00:00:00), +. (00:00:00), +2 (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +inventory (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +80 (00:00:00), +% (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +family (00:00:00), +: (00:00:00), +' (00:00:00), +Times (00:00:00), +New (00:00:00), +Roman (00:00:00), +' (00:00:00), +, (00:00:00), +Times (00:00:00), +, (00:00:00), +serif (00:00:00), +, (00:00:00), +sans (00:00:00), +- (00:00:00), +serif (00:00:00), +; (00:00:00), +border (00:00:00), +: (00:00:00), +1px (00:00:00), +solid (00:00:00), +var (00:00:00), +( (00:00:00), +- (00:00:00), +- (00:00:00), +theme (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +inventory (00:00:00), +p (00:00:00), +{ (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +red (00:00:00), +; (00:00:00), +text (00:00:00), +- (00:00:00), +align (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +} (00:00:00), +: (00:00:00), +root (00:00:00), +{ (00:00:00), +- (00:00:00), +- (00:00:00), +theme (00:00:00), +: (00:00:00), +# (00:00:00), +280 (00:00:00), +; (00:00:00), +} (00:00:00), +body (00:00:00), +{ (00:00:00), +display (00:00:00), +: (00:00:00), +flex (00:00:00), +; (00:00:00), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +margin (00:00:00), +: (00:00:00), +0 (00:00:00), +; (00:00:00), +} (00:00:00), +h1 (00:00:00), +{ (00:00:00), +font (00:00:00), +- (00:00:00), +family (00:00:00), +: (00:00:00), +" (00:00:00), +Arial (00:00:00), +" (00:00:00), +; (00:00:00), +color (00:00:00), +: (00:00:00), +var (00:00:00), +( (00:00:00), +- (00:00:00), +- (00:00:00), +theme (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +map (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +100 (00:00:00), +% (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +marker (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +3vw (00:00:00), +; (00:00:00), +height (00:00:00), +: (00:00:00), +3vw (00:00:00), +; (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +yellow (00:00:00), +; (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +50 (00:00:00), +% (00:00:00), +; (00:00:00), +outline (00:00:00), +: (00:00:00), +5px (00:00:00), +solid (00:00:00), +var (00:00:00), +( (00:00:00), +- (00:00:00), +- (00:00:00), +theme (00:00:00), +) (00:00:00), +; (00:00:00), +border (00:00:00), +: (00:00:00), +5px (00:00:00), +solid (00:00:00), +red (00:00:00), +; (00:00:00), +position (00:00:00), +: (00:00:00), +absolute (00:00:00), +; (00:00:00), +top (00:00:00), +: (00:00:00), +0 (00:00:00), +; (00:00:00), +left (00:00:00), +: (00:00:00), +0 (00:00:00), +; (00:00:00), +transform (00:00:00), +: (00:00:00), +translate (00:00:00), +( (00:00:00), +- (00:00:00), +50 (00:00:00), +% (00:00:00), +, (00:00:00), +- (00:00:00), +50 (00:00:00), +% (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +mapContainer (00:00:00), +{ (00:00:00), +position (00:00:00), +: (00:00:00), +relative (00:00:00), +; (00:00:00), +display (00:00:00), +: (00:00:00), +none (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +camera (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +100 (00:00:00), +% (00:00:00), +; (00:00:00), +} (00:00:00), +button (00:00:00), +{ (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +var (00:00:00), +( (00:00:00), +- (00:00:00), +- (00:00:00), +theme (00:00:00), +) (00:00:00), +; (00:00:00), +color (00:00:00), +: (00:00:00), +white (00:00:00), +; (00:00:00), +cursor (00:00:00), +: (00:00:00), +pointer (00:00:00), +; (00:00:00), +transition (00:00:00), +: (00:00:00), +all (00:00:00), +2s (00:00:00), +ease (00:00:00), +; (00:00:00), +} (00:00:00), +button (00:00:00), +: (00:00:00), +hover (00:00:00), +{ (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +blue (00:00:00), +; (00:00:00), +transform (00:00:00), +: (00:00:00), +scale (00:00:00), +( (00:00:00), +2 (00:00:00), +. (00:00:00), +2 (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +inventory (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +80 (00:00:00), +% (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +family (00:00:00), +: (00:00:00), +' (00:00:00), +Times (00:00:00), +New (00:00:00), +Roman (00:00:00), +' (00:00:00), +, (00:00:00), +Times (00:00:00), +, (00:00:00), +serif (00:00:00), +, (00:00:00), +sans (00:00:00), +- (00:00:00), +serif (00:00:00), +; (00:00:00), +border (00:00:00), +: (00:00:00), +1px (00:00:00), +solid (00:00:00), +var (00:00:00), +( (00:00:00), +- (00:00:00), +- (00:00:00), +theme (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +inventory (00:00:00), +p (00:00:00), +{ (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +red (00:00:00), +; (00:00:00), +text (00:00:00), +- (00:00:00), +align (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +} (00:00:00), +: (00:00:00), +root (00:00:00), +{ (00:00:00), +- (00:00:00), +- (00:00:00), +theme (00:00:00), +: (00:00:00), +# (00:00:00), +280 (00:00:00), +; (00:00:00), +} (00:00:00), +body (00:00:00), +{ (00:00:00), +display (00:00:00), +: (00:00:00), +flex (00:00:00), +; (00:00:00), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +margin (00:00:00), +: (00:00:00), +0 (00:00:00), +; (00:00:00), +} (00:00:00), +h1 (00:00:00), +{ (00:00:00), +font (00:00:00), +- (00:00:00), +family (00:00:00), +: (00:00:00), +" (00:00:00), +Arial (00:00:00), +" (00:00:00), +; (00:00:00), +color (00:00:00), +: (00:00:00), +var (00:00:00), +( (00:00:00), +- (00:00:00), +- (00:00:00), +theme (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +map (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +100 (00:00:00), +% (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +marker (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +3vw (00:00:00), +; (00:00:00), +height (00:00:00), +: (00:00:00), +3vw (00:00:00), +; (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +black (00:00:00), +; (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +50 (00:00:00), +% (00:00:00), +; (00:00:00), +outline (00:00:00), +: (00:00:00), +5px (00:00:00), +solid (00:00:00), +var (00:00:00), +( (00:00:00), +- (00:00:00), +- (00:00:00), +theme (00:00:00), +) (00:00:00), +; (00:00:00), +border (00:00:00), +: (00:00:00), +5px (00:00:00), +solid (00:00:00), +white (00:00:00), +; (00:00:00), +position (00:00:00), +: (00:00:00), +absolute (00:00:00), +; (00:00:00), +top (00:00:00), +: (00:00:00), +0 (00:00:00), +; (00:00:00), +left (00:00:00), +: (00:00:00), +0 (00:00:00), +; (00:00:00), +transform (00:00:00), +: (00:00:00), +translate (00:00:00), +( (00:00:00), +- (00:00:00), +50 (00:00:00), +% (00:00:00), +, (00:00:00), +- (00:00:00), +50 (00:00:00), +% (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +mapContainer (00:00:00), +{ (00:00:00), +position (00:00:00), +: (00:00:00), +relative (00:00:00), +; (00:00:00), +display (00:00:00), +: (00:00:00), +none (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +camera (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +100 (00:00:00), +% (00:00:00), +; (00:00:00), +} (00:00:00), +button (00:00:00), +{ (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +var (00:00:00), +( (00:00:00), +- (00:00:00), +- (00:00:00), +theme (00:00:00), +) (00:00:00), +; (00:00:00), +color (00:00:00), +: (00:00:00), +white (00:00:00), +; (00:00:00), +cursor (00:00:00), +: (00:00:00), +pointer (00:00:00), +; (00:00:00), +transition (00:00:00), +: (00:00:00), +all (00:00:00), +2s (00:00:00), +ease (00:00:00), +; (00:00:00), +} (00:00:00), +button (00:00:00), +: (00:00:00), +hover (00:00:00), +{ (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +blue (00:00:00), +; (00:00:00), +transform (00:00:00), +: (00:00:00), +scale (00:00:00), +( (00:00:00), +2 (00:00:00), +. (00:00:00), +2 (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00)</t>
         </is>
       </c>
       <c r="N68" t="n">
@@ -5180,7 +5180,7 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>-place (00:04:49), -place (00:05:00), -place (00:05:04), +data (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +item (00:00:00), +- (00:00:00), +name (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +Name (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +data (00:00:00), +. (00:00:00), +name (00:00:00), +; (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +item (00:00:00), +- (00:00:00), +stock (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +In (00:00:00), +store (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +( (00:00:00), +data (00:00:00), +. (00:00:00), +in (00:00:00), +_ (00:00:00), +store (00:00:00), +? (00:00:00), +" (00:00:00), +Yes (00:00:00), +" (00:00:00), +: (00:00:00), +" (00:00:00), +No (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +item (00:00:00), +- (00:00:00), +price (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +Price (00:00:00), +: (00:00:00), +€ (00:00:00), +" (00:00:00), ++ (00:00:00), +data (00:00:00), +. (00:00:00), +price (00:00:00), +; (00:00:00), +data (00:00:00), +data (00:00:00)</t>
+          <t>-place (00:04:49) ~0.20, -place (00:05:00) ~0.20, -place (00:05:04) ~0.20, +data (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +item (00:00:00), +- (00:00:00), +name (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +Name (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +data (00:00:00), +. (00:00:00), +name (00:00:00), +; (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +item (00:00:00), +- (00:00:00), +stock (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +In (00:00:00), +store (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +( (00:00:00), +data (00:00:00), +. (00:00:00), +in (00:00:00), +_ (00:00:00), +store (00:00:00), +? (00:00:00), +" (00:00:00), +Yes (00:00:00), +" (00:00:00), +: (00:00:00), +" (00:00:00), +No (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +item (00:00:00), +- (00:00:00), +price (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +Price (00:00:00), +: (00:00:00), +€ (00:00:00), +" (00:00:00), ++ (00:00:00), +data (00:00:00), +. (00:00:00), +price (00:00:00), +; (00:00:00), +data (00:00:00), +data (00:00:00)</t>
         </is>
       </c>
       <c r="P70" s="3" t="inlineStr">
@@ -5320,7 +5320,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>-Positioning (00:07:06), -Positioning (00:07:38), +Inventory (00:00:00), +System (00:00:00), +Inventory (00:00:00), +System (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +name (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +store (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +price (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00)</t>
+          <t>-Positioning (00:07:06) ~0.09, -Positioning (00:07:38) ~0.09, +Inventory (00:00:00), +System (00:00:00), +Inventory (00:00:00), +System (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +name (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +store (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +price (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00)</t>
         </is>
       </c>
       <c r="L72" t="n">
@@ -5336,7 +5336,7 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>-place (00:04:49), -place (00:05:00), -place (00:05:04), +item (00:00:00), +item (00:00:00), +item (00:00:00), +showItemInfo (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +; (00:00:00), +function (00:00:00), +showItemInfo (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +{ (00:00:00), +name (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Name (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +name (00:00:00), +; (00:00:00), +store (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +In (00:00:00), +store (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +( (00:00:00), +item (00:00:00), +. (00:00:00), +in (00:00:00), +_ (00:00:00), +store (00:00:00), +? (00:00:00), +" (00:00:00), +Yes (00:00:00), +" (00:00:00), +: (00:00:00), +" (00:00:00), +No (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +price (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Price (00:00:00), +: (00:00:00), +€ (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +price (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+          <t>-place (00:04:49) ~0.00, -place (00:05:00) ~0.00, -place (00:05:04) ~0.00, +item (00:00:00), +item (00:00:00), +item (00:00:00), +showItemInfo (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +; (00:00:00), +function (00:00:00), +showItemInfo (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +{ (00:00:00), +name (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Name (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +name (00:00:00), +; (00:00:00), +store (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +In (00:00:00), +store (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +( (00:00:00), +item (00:00:00), +. (00:00:00), +in (00:00:00), +_ (00:00:00), +store (00:00:00), +? (00:00:00), +" (00:00:00), +Yes (00:00:00), +" (00:00:00), +: (00:00:00), +" (00:00:00), +No (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +price (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Price (00:00:00), +: (00:00:00), +€ (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +price (00:00:00), +; (00:00:00), +} (00:00:00)</t>
         </is>
       </c>
       <c r="P72" s="3" t="inlineStr">
@@ -5398,7 +5398,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>-Positioning (00:07:06), -Positioning (00:07:38), -&lt; (00:07:43), -div (00:07:44), -id (00:07:45), -= (00:07:46), -" (00:07:47), -mapContainer (00:07:48), -" (00:07:49), -&gt; (00:07:50), -&lt; (00:07:51), -img (00:07:52), -src (00:07:53), -= (00:07:54), -" (00:07:55), -map (00:07:56), -. (00:07:57), -png (00:07:58), -" (00:07:59), -id (00:08:00), -= (00:08:01), -" (00:08:02), -map (00:08:03), -" (00:08:04), -alt (00:08:05), -= (00:08:06), -" (00:08:07), -map (00:08:08), -" (00:08:09), -/ (00:08:10), -&gt; (00:08:11), -&lt; (00:08:12), -div (00:08:13), -id (00:08:14), -= (00:08:15), -" (00:08:16), -marker (00:08:17), -" (00:08:18), -&gt; (00:08:19), -&lt; (00:08:20), -/ (00:08:21), -div (00:08:22), -&gt; (00:08:23), -&lt; (00:08:24), -/ (00:08:25), -div (00:08:26), -&gt; (00:08:27), +Inventory (00:00:00), +Inventory (00:00:00), +System (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +output (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +name (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +stock (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +price (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
+          <t>-Positioning (00:07:06) ~0.09, -Positioning (00:07:38) ~0.09, -&lt; (00:07:43), -div (00:07:44), -id (00:07:45), -= (00:07:46), -" (00:07:47), -mapContainer (00:07:48), -" (00:07:49), -&gt; (00:07:50), -&lt; (00:07:51), -img (00:07:52), -src (00:07:53), -= (00:07:54), -" (00:07:55), -map (00:07:56), -. (00:07:57), -png (00:07:58), -" (00:07:59), -id (00:08:00), -= (00:08:01), -" (00:08:02), -map (00:08:03), -" (00:08:04), -alt (00:08:05), -= (00:08:06), -" (00:08:07), -map (00:08:08), -" (00:08:09), -/ (00:08:10), -&gt; (00:08:11), -&lt; (00:08:12), -div (00:08:13), -id (00:08:14), -= (00:08:15), -" (00:08:16), -marker (00:08:17), -" (00:08:18), -&gt; (00:08:19), -&lt; (00:08:20), -/ (00:08:21), -div (00:08:22), -&gt; (00:08:23), -&lt; (00:08:24), -/ (00:08:25), -div (00:08:26), -&gt; (00:08:27), +Inventory (00:00:00), +Inventory (00:00:00), +System (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +output (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +name (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +stock (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +price (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
         </is>
       </c>
       <c r="L73" t="n">
@@ -5414,7 +5414,7 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>-place (00:04:49), -showMarkerAt (00:04:58), -( (00:04:59), -place (00:05:00), -. (00:05:01), -top (00:05:02), -, (00:05:03), -place (00:05:04), -. (00:05:05), -left (00:05:06), -) (00:05:07), -; (00:05:08), -function (00:05:46), -showMarkerAt (00:05:47), -( (00:05:48), -top (00:05:49), -, (00:05:50), -left (00:05:51), -) (00:05:52), -{ (00:05:53), -marker (00:05:54), -. (00:05:55), -style (00:05:56), -. (00:05:57), -top (00:05:58), -= (00:05:59), -top (00:06:00), -; (00:06:01), -marker (00:06:02), -. (00:06:03), -style (00:06:04), -. (00:06:05), -left (00:06:06), -= (00:06:07), -left (00:06:08), -; (00:06:09), -} (00:06:10), +try (00:00:00), +{ (00:00:00), +item (00:00:00), +displayItem (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +catch (00:00:00), +( (00:00:00), +error (00:00:00), +) (00:00:00), +{ (00:00:00), +console (00:00:00), +. (00:00:00), +error (00:00:00), +( (00:00:00), +" (00:00:00), +Invalid (00:00:00), +QR (00:00:00), +data (00:00:00), +: (00:00:00), +" (00:00:00), +, (00:00:00), +error (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +function (00:00:00), +displayItem (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +nameEl (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +name (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +stockEl (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +stock (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +priceEl (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +price (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +nameEl (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +Name (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +name (00:00:00), +; (00:00:00), +stockEl (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +In (00:00:00), +store (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +( (00:00:00), +item (00:00:00), +. (00:00:00), +in (00:00:00), +_ (00:00:00), +store (00:00:00), +? (00:00:00), +" (00:00:00), +Yes (00:00:00), +" (00:00:00), +: (00:00:00), +" (00:00:00), +No (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +priceEl (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +Price (00:00:00), +: (00:00:00), +€ (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +price (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+          <t>-place (00:04:49) ~0.00, -showMarkerAt (00:04:58), -( (00:04:59), -place (00:05:00), -. (00:05:01), -top (00:05:02), -, (00:05:03), -place (00:05:04), -. (00:05:05), -left (00:05:06), -) (00:05:07), -; (00:05:08), -function (00:05:46), -showMarkerAt (00:05:47), -( (00:05:48), -top (00:05:49), -, (00:05:50), -left (00:05:51), -) (00:05:52), -{ (00:05:53), -marker (00:05:54), -. (00:05:55), -style (00:05:56), -. (00:05:57), -top (00:05:58), -= (00:05:59), -top (00:06:00), -; (00:06:01), -marker (00:06:02), -. (00:06:03), -style (00:06:04), -. (00:06:05), -left (00:06:06), -= (00:06:07), -left (00:06:08), -; (00:06:09), -} (00:06:10), +try (00:00:00), +{ (00:00:00), +item (00:00:00), +displayItem (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +catch (00:00:00), +( (00:00:00), +error (00:00:00), +) (00:00:00), +{ (00:00:00), +console (00:00:00), +. (00:00:00), +error (00:00:00), +( (00:00:00), +" (00:00:00), +Invalid (00:00:00), +QR (00:00:00), +data (00:00:00), +: (00:00:00), +" (00:00:00), +, (00:00:00), +error (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +function (00:00:00), +displayItem (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +nameEl (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +name (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +stockEl (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +stock (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +priceEl (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +price (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +nameEl (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +Name (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +name (00:00:00), +; (00:00:00), +stockEl (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +In (00:00:00), +store (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +( (00:00:00), +item (00:00:00), +. (00:00:00), +in (00:00:00), +_ (00:00:00), +store (00:00:00), +? (00:00:00), +" (00:00:00), +Yes (00:00:00), +" (00:00:00), +: (00:00:00), +" (00:00:00), +No (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +priceEl (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +Price (00:00:00), +: (00:00:00), +€ (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +price (00:00:00), +; (00:00:00), +} (00:00:00)</t>
         </is>
       </c>
       <c r="P73" s="3" t="inlineStr">
@@ -5870,7 +5870,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>-3vw (00:01:28), +button (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +120px (00:00:00), +; (00:00:00), +height (00:00:00), +: (00:00:00), +50px (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +weight (00:00:00), +: (00:00:00), +bold (00:00:00), +; (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +10px (00:00:00), +; (00:00:00), +border (00:00:00), +: (00:00:00), +none (00:00:00), +; (00:00:00), +box (00:00:00), +- (00:00:00), +shadow (00:00:00), +: (00:00:00), +2px (00:00:00), +1px (00:00:00), +3px (00:00:00), +1px (00:00:00), +rgba (00:00:00), +( (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +. (00:00:00), +555 (00:00:00), +) (00:00:00), +; (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +crimson (00:00:00), +; (00:00:00), +letter (00:00:00), +- (00:00:00), +spacing (00:00:00), +: (00:00:00), +1px (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +22px (00:00:00), +; (00:00:00), +color (00:00:00), +: (00:00:00), +white (00:00:00), +; (00:00:00), +text (00:00:00), +- (00:00:00), +shadow (00:00:00), +: (00:00:00), +2px (00:00:00), +2px (00:00:00), +2px (00:00:00), +rgba (00:00:00), +( (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +. (00:00:00), +888 (00:00:00), +) (00:00:00), +; (00:00:00), +transition (00:00:00), +: (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +0 (00:00:00), +. (00:00:00), +5s (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +family (00:00:00), +: (00:00:00), +' (00:00:00), +Franklin (00:00:00), +Gothic (00:00:00), +Medium (00:00:00), +' (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +no (00:00:00), +{ (00:00:00), +margin (00:00:00), +- (00:00:00), +top (00:00:00), +: (00:00:00), +15px (00:00:00), +; (00:00:00), +width (00:00:00), +: (00:00:00), +200px (00:00:00), +; (00:00:00), +border (00:00:00), +: (00:00:00), +1px (00:00:00), +solid (00:00:00), +black (00:00:00), +; (00:00:00), +display (00:00:00), +: (00:00:00), +none (00:00:00), +; (00:00:00), +} (00:00:00), +p (00:00:00), +{ (00:00:00), +margin (00:00:00), +: (00:00:00), +0 (00:00:00), +; (00:00:00), +border (00:00:00), +: (00:00:00), +2px (00:00:00), +solid (00:00:00), +gray (00:00:00), +; (00:00:00), +justify (00:00:00), +- (00:00:00), +content (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +display (00:00:00), +: (00:00:00), +flex (00:00:00), +; (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +rgb (00:00:00), +( (00:00:00), +185 (00:00:00), +, (00:00:00), +185 (00:00:00), +, (00:00:00), +184 (00:00:00), +) (00:00:00), +; (00:00:00), +padding (00:00:00), +: (00:00:00), +15px (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +weight (00:00:00), +: (00:00:00), +bold (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +family (00:00:00), +: (00:00:00), +' (00:00:00), +Franklin (00:00:00), +Gothic (00:00:00), +Medium (00:00:00), +' (00:00:00), +; (00:00:00), +} (00:00:00), +button (00:00:00), +: (00:00:00), +hover (00:00:00), +{ (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +var (00:00:00), +( (00:00:00), +- (00:00:00), +- (00:00:00), +theme (00:00:00), +) (00:00:00), +; (00:00:00), +cursor (00:00:00), +: (00:00:00), +pointer (00:00:00), +; (00:00:00), +} (00:00:00), +3vh (00:00:00)</t>
+          <t>-3vw (00:01:28) ~0.67, +button (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +120px (00:00:00), +; (00:00:00), +height (00:00:00), +: (00:00:00), +50px (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +weight (00:00:00), +: (00:00:00), +bold (00:00:00), +; (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +10px (00:00:00), +; (00:00:00), +border (00:00:00), +: (00:00:00), +none (00:00:00), +; (00:00:00), +box (00:00:00), +- (00:00:00), +shadow (00:00:00), +: (00:00:00), +2px (00:00:00), +1px (00:00:00), +3px (00:00:00), +1px (00:00:00), +rgba (00:00:00), +( (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +. (00:00:00), +555 (00:00:00), +) (00:00:00), +; (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +crimson (00:00:00), +; (00:00:00), +letter (00:00:00), +- (00:00:00), +spacing (00:00:00), +: (00:00:00), +1px (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +22px (00:00:00), +; (00:00:00), +color (00:00:00), +: (00:00:00), +white (00:00:00), +; (00:00:00), +text (00:00:00), +- (00:00:00), +shadow (00:00:00), +: (00:00:00), +2px (00:00:00), +2px (00:00:00), +2px (00:00:00), +rgba (00:00:00), +( (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +. (00:00:00), +888 (00:00:00), +) (00:00:00), +; (00:00:00), +transition (00:00:00), +: (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +0 (00:00:00), +. (00:00:00), +5s (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +family (00:00:00), +: (00:00:00), +' (00:00:00), +Franklin (00:00:00), +Gothic (00:00:00), +Medium (00:00:00), +' (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +no (00:00:00), +{ (00:00:00), +margin (00:00:00), +- (00:00:00), +top (00:00:00), +: (00:00:00), +15px (00:00:00), +; (00:00:00), +width (00:00:00), +: (00:00:00), +200px (00:00:00), +; (00:00:00), +border (00:00:00), +: (00:00:00), +1px (00:00:00), +solid (00:00:00), +black (00:00:00), +; (00:00:00), +display (00:00:00), +: (00:00:00), +none (00:00:00), +; (00:00:00), +} (00:00:00), +p (00:00:00), +{ (00:00:00), +margin (00:00:00), +: (00:00:00), +0 (00:00:00), +; (00:00:00), +border (00:00:00), +: (00:00:00), +2px (00:00:00), +solid (00:00:00), +gray (00:00:00), +; (00:00:00), +justify (00:00:00), +- (00:00:00), +content (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +display (00:00:00), +: (00:00:00), +flex (00:00:00), +; (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +rgb (00:00:00), +( (00:00:00), +185 (00:00:00), +, (00:00:00), +185 (00:00:00), +, (00:00:00), +184 (00:00:00), +) (00:00:00), +; (00:00:00), +padding (00:00:00), +: (00:00:00), +15px (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +weight (00:00:00), +: (00:00:00), +bold (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +family (00:00:00), +: (00:00:00), +' (00:00:00), +Franklin (00:00:00), +Gothic (00:00:00), +Medium (00:00:00), +' (00:00:00), +; (00:00:00), +} (00:00:00), +button (00:00:00), +: (00:00:00), +hover (00:00:00), +{ (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +var (00:00:00), +( (00:00:00), +- (00:00:00), +- (00:00:00), +theme (00:00:00), +) (00:00:00), +; (00:00:00), +cursor (00:00:00), +: (00:00:00), +pointer (00:00:00), +; (00:00:00), +} (00:00:00), +3vh (00:00:00)</t>
         </is>
       </c>
       <c r="N82" t="n">
@@ -5935,7 +5935,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>-map (00:08:08), +Map (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemInfo (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemName (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemLatitude (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemLongitude (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
+          <t>-map (00:08:08) ~0.67, +Map (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemInfo (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemName (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemLatitude (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemLongitude (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
         </is>
       </c>
       <c r="L83" t="n">
@@ -6055,7 +6055,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>-Positioning (00:07:06), -Positioning (00:07:38), -&lt; (00:07:43), -div (00:07:44), -id (00:07:45), -= (00:07:46), -" (00:07:47), -mapContainer (00:07:48), -" (00:07:49), -&gt; (00:07:50), -&lt; (00:07:51), -img (00:07:52), -src (00:07:53), -= (00:07:54), -" (00:07:55), -map (00:07:56), -. (00:07:57), -png (00:07:58), -" (00:07:59), -id (00:08:00), -= (00:08:01), -" (00:08:02), -map (00:08:03), -" (00:08:04), -alt (00:08:05), -= (00:08:06), -" (00:08:07), -map (00:08:08), -" (00:08:09), -/ (00:08:10), -&gt; (00:08:11), -&lt; (00:08:12), -div (00:08:13), -id (00:08:14), -= (00:08:15), -" (00:08:16), -marker (00:08:17), -" (00:08:18), -&gt; (00:08:19), -&lt; (00:08:20), -/ (00:08:21), -div (00:08:22), -&gt; (00:08:23), -&lt; (00:08:24), -/ (00:08:25), -div (00:08:26), -&gt; (00:08:27), +Inventory (00:00:00), +System (00:00:00), +Inventory (00:00:00), +System (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +inventory (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemName (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Name (00:00:00), +: (00:00:00), +- (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemInStore (00:00:00), +" (00:00:00), +&gt; (00:00:00), +In (00:00:00), +store (00:00:00), +: (00:00:00), +- (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemPrice (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Price (00:00:00), +: (00:00:00), +- (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
+          <t>-Positioning (00:07:06) ~0.09, -Positioning (00:07:38) ~0.09, -&lt; (00:07:43), -div (00:07:44), -id (00:07:45), -= (00:07:46), -" (00:07:47), -mapContainer (00:07:48), -" (00:07:49), -&gt; (00:07:50), -&lt; (00:07:51), -img (00:07:52), -src (00:07:53), -= (00:07:54), -" (00:07:55), -map (00:07:56), -. (00:07:57), -png (00:07:58), -" (00:07:59), -id (00:08:00), -= (00:08:01), -" (00:08:02), -map (00:08:03), -" (00:08:04), -alt (00:08:05), -= (00:08:06), -" (00:08:07), -map (00:08:08), -" (00:08:09), -/ (00:08:10), -&gt; (00:08:11), -&lt; (00:08:12), -div (00:08:13), -id (00:08:14), -= (00:08:15), -" (00:08:16), -marker (00:08:17), -" (00:08:18), -&gt; (00:08:19), -&lt; (00:08:20), -/ (00:08:21), -div (00:08:22), -&gt; (00:08:23), -&lt; (00:08:24), -/ (00:08:25), -div (00:08:26), -&gt; (00:08:27), +Inventory (00:00:00), +System (00:00:00), +Inventory (00:00:00), +System (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +inventory (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemName (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Name (00:00:00), +: (00:00:00), +- (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemInStore (00:00:00), +" (00:00:00), +&gt; (00:00:00), +In (00:00:00), +store (00:00:00), +: (00:00:00), +- (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemPrice (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Price (00:00:00), +: (00:00:00), +- (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
         </is>
       </c>
       <c r="L86" t="n">
@@ -6071,7 +6071,7 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>-mapContainer (00:03:46), -. (00:03:47), -style (00:03:48), -. (00:03:49), -display (00:03:50), -= (00:03:51), -" (00:03:52), -none (00:03:53), -" (00:03:54), -; (00:03:55), -mapContainer (00:04:11), -. (00:04:12), -style (00:04:13), -. (00:04:14), -display (00:04:15), -= (00:04:16), -" (00:04:17), -block (00:04:18), -" (00:04:19), -; (00:04:20), -place (00:04:49), -showMarkerAt (00:04:58), -( (00:04:59), -place (00:05:00), -. (00:05:01), -top (00:05:02), -, (00:05:03), -place (00:05:04), -. (00:05:05), -left (00:05:06), -) (00:05:07), -; (00:05:08), -function (00:05:46), -showMarkerAt (00:05:47), -( (00:05:48), -top (00:05:49), -, (00:05:50), -left (00:05:51), -) (00:05:52), -{ (00:05:53), -marker (00:05:54), -. (00:05:55), -style (00:05:56), -. (00:05:57), -top (00:05:58), -= (00:05:59), -top (00:06:00), -; (00:06:01), -marker (00:06:02), -. (00:06:03), -style (00:06:04), -. (00:06:05), -left (00:06:06), -= (00:06:07), -left (00:06:08), -; (00:06:09), -} (00:06:10), +item (00:00:00), +showInventoryItem (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +; (00:00:00), +. (00:00:00), +catch (00:00:00), +( (00:00:00), +function (00:00:00), +( (00:00:00), +err (00:00:00), +) (00:00:00), +{ (00:00:00), +console (00:00:00), +. (00:00:00), +error (00:00:00), +( (00:00:00), +err (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +) (00:00:00), +function (00:00:00), +showInventoryItem (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +{ (00:00:00), +itemName (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Name (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +name (00:00:00), +; (00:00:00), +if (00:00:00), +( (00:00:00), +item (00:00:00), +. (00:00:00), +in (00:00:00), +_ (00:00:00), +store (00:00:00), +) (00:00:00), +{ (00:00:00), +itemInStore (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +In (00:00:00), +store (00:00:00), +: (00:00:00), +Yes (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00), +else (00:00:00), +{ (00:00:00), +itemInStore (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +In (00:00:00), +store (00:00:00), +: (00:00:00), +No (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00), +itemPrice (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Price (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +price (00:00:00), ++ (00:00:00), +" (00:00:00), +€ (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+          <t>-mapContainer (00:03:46), -. (00:03:47), -style (00:03:48), -. (00:03:49), -display (00:03:50), -= (00:03:51), -" (00:03:52), -none (00:03:53), -" (00:03:54), -; (00:03:55), -mapContainer (00:04:11), -. (00:04:12), -style (00:04:13), -. (00:04:14), -display (00:04:15), -= (00:04:16), -" (00:04:17), -block (00:04:18), -" (00:04:19), -; (00:04:20), -place (00:04:49) ~0.00, -showMarkerAt (00:04:58), -( (00:04:59), -place (00:05:00), -. (00:05:01), -top (00:05:02), -, (00:05:03), -place (00:05:04), -. (00:05:05), -left (00:05:06), -) (00:05:07), -; (00:05:08), -function (00:05:46), -showMarkerAt (00:05:47), -( (00:05:48), -top (00:05:49), -, (00:05:50), -left (00:05:51), -) (00:05:52), -{ (00:05:53), -marker (00:05:54), -. (00:05:55), -style (00:05:56), -. (00:05:57), -top (00:05:58), -= (00:05:59), -top (00:06:00), -; (00:06:01), -marker (00:06:02), -. (00:06:03), -style (00:06:04), -. (00:06:05), -left (00:06:06), -= (00:06:07), -left (00:06:08), -; (00:06:09), -} (00:06:10), +item (00:00:00), +showInventoryItem (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +; (00:00:00), +. (00:00:00), +catch (00:00:00), +( (00:00:00), +function (00:00:00), +( (00:00:00), +err (00:00:00), +) (00:00:00), +{ (00:00:00), +console (00:00:00), +. (00:00:00), +error (00:00:00), +( (00:00:00), +err (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +) (00:00:00), +function (00:00:00), +showInventoryItem (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +{ (00:00:00), +itemName (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Name (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +name (00:00:00), +; (00:00:00), +if (00:00:00), +( (00:00:00), +item (00:00:00), +. (00:00:00), +in (00:00:00), +_ (00:00:00), +store (00:00:00), +) (00:00:00), +{ (00:00:00), +itemInStore (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +In (00:00:00), +store (00:00:00), +: (00:00:00), +Yes (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00), +else (00:00:00), +{ (00:00:00), +itemInStore (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +In (00:00:00), +store (00:00:00), +: (00:00:00), +No (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00), +itemPrice (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Price (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +price (00:00:00), ++ (00:00:00), +" (00:00:00), +€ (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00)</t>
         </is>
       </c>
       <c r="P86" s="3" t="inlineStr">
@@ -6138,7 +6138,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>-QR (00:07:05), -Positioning (00:07:06), -QR (00:07:37), -Positioning (00:07:38), -&lt; (00:07:43), -div (00:07:44), -id (00:07:45), -= (00:07:46), -" (00:07:47), -mapContainer (00:07:48), -" (00:07:49), -&gt; (00:07:50), -&lt; (00:07:51), -img (00:07:52), -src (00:07:53), -= (00:07:54), -" (00:07:55), -map (00:07:56), -. (00:07:57), -png (00:07:58), -" (00:07:59), -id (00:08:00), -= (00:08:01), -" (00:08:02), -map (00:08:03), -" (00:08:04), -alt (00:08:05), -= (00:08:06), -" (00:08:07), -map (00:08:08), -" (00:08:09), -/ (00:08:10), -&gt; (00:08:11), -&lt; (00:08:12), -div (00:08:13), -id (00:08:14), -= (00:08:15), -" (00:08:16), -marker (00:08:17), -" (00:08:18), -&gt; (00:08:19), -&lt; (00:08:20), -/ (00:08:21), -div (00:08:22), -&gt; (00:08:23), -&lt; (00:08:24), -/ (00:08:25), -div (00:08:26), -&gt; (00:08:27), +Inventory (00:00:00), +Scanner (00:00:00), +Inventory (00:00:00), +Scanner (00:00:00), +&lt; (00:00:00), +section (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +inventoryCard (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemName (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Name (00:00:00), +: (00:00:00), +scan (00:00:00), +an (00:00:00), +item (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemStore (00:00:00), +" (00:00:00), +&gt; (00:00:00), +In (00:00:00), +store (00:00:00), +: (00:00:00), +- (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemPrice (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Price (00:00:00), +: (00:00:00), +- (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +section (00:00:00), +&gt; (00:00:00)</t>
+          <t>-QR (00:07:05) ~0.00, -Positioning (00:07:06) ~0.09, -QR (00:07:37) ~0.00, -Positioning (00:07:38) ~0.09, -&lt; (00:07:43), -div (00:07:44), -id (00:07:45), -= (00:07:46), -" (00:07:47), -mapContainer (00:07:48), -" (00:07:49), -&gt; (00:07:50), -&lt; (00:07:51), -img (00:07:52), -src (00:07:53), -= (00:07:54), -" (00:07:55), -map (00:07:56), -. (00:07:57), -png (00:07:58), -" (00:07:59), -id (00:08:00), -= (00:08:01), -" (00:08:02), -map (00:08:03), -" (00:08:04), -alt (00:08:05), -= (00:08:06), -" (00:08:07), -map (00:08:08), -" (00:08:09), -/ (00:08:10), -&gt; (00:08:11), -&lt; (00:08:12), -div (00:08:13), -id (00:08:14), -= (00:08:15), -" (00:08:16), -marker (00:08:17), -" (00:08:18), -&gt; (00:08:19), -&lt; (00:08:20), -/ (00:08:21), -div (00:08:22), -&gt; (00:08:23), -&lt; (00:08:24), -/ (00:08:25), -div (00:08:26), -&gt; (00:08:27), +Inventory (00:00:00), +Scanner (00:00:00), +Inventory (00:00:00), +Scanner (00:00:00), +&lt; (00:00:00), +section (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +inventoryCard (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemName (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Name (00:00:00), +: (00:00:00), +scan (00:00:00), +an (00:00:00), +item (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemStore (00:00:00), +" (00:00:00), +&gt; (00:00:00), +In (00:00:00), +store (00:00:00), +: (00:00:00), +- (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemPrice (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Price (00:00:00), +: (00:00:00), +- (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +section (00:00:00), +&gt; (00:00:00)</t>
         </is>
       </c>
       <c r="L87" t="n">
@@ -6146,7 +6146,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>-font (00:00:42), -- (00:00:43), -family (00:00:44), -: (00:00:45), -" (00:00:46), -Arial (00:00:47), -" (00:00:48), -; (00:00:49), -# (00:01:00), -map (00:01:01), -{ (00:01:02), -width (00:01:03), -: (00:01:04), -100 (00:01:05), -% (00:01:06), -; (00:01:07), -} (00:01:08), -# (00:01:09), -marker (00:01:10), -{ (00:01:11), -width (00:01:12), -: (00:01:13), -3vw (00:01:14), -; (00:01:15), -height (00:01:26), -: (00:01:27), -3vw (00:01:28), -; (00:01:29), -background (00:01:30), -- (00:01:31), -color (00:01:32), -: (00:01:33), -black (00:01:34), -; (00:01:35), -border (00:01:36), -- (00:01:37), -radius (00:01:38), -: (00:01:39), -50 (00:01:40), -% (00:01:41), -; (00:01:42), -outline (00:01:43), -: (00:01:44), -5px (00:01:45), -solid (00:01:46), -var (00:01:47), -( (00:01:48), -- (00:01:49), -- (00:01:50), -theme (00:01:51), -) (00:01:52), -; (00:01:53), -border (00:02:03), -: (00:02:04), -5px (00:02:05), -solid (00:02:06), -white (00:02:07), -; (00:02:08), -position (00:02:16), -: (00:02:17), -absolute (00:02:18), -; (00:02:19), -top (00:02:20), -: (00:02:21), -0 (00:02:22), -; (00:02:23), -left (00:02:24), -: (00:02:25), -0 (00:02:26), -; (00:02:27), -transform (00:02:28), -: (00:02:29), -translate (00:02:30), -( (00:02:31), -- (00:02:32), -50 (00:02:33), -% (00:02:34), -, (00:02:35), -- (00:02:36), -50 (00:02:37), -% (00:02:38), -) (00:02:39), -; (00:02:40), -} (00:02:41), -# (00:02:42), -mapContainer (00:02:43), -{ (00:02:44), -position (00:02:45), -: (00:02:46), -relative (00:02:47), -; (00:02:48), -display (00:02:49), -: (00:02:50), -none (00:02:51), -; (00:02:52), -} (00:02:53), -100 (00:02:59), +gap (00:00:00), +: (00:00:00), +20px (00:00:00), +; (00:00:00), +min (00:00:00), +- (00:00:00), +height (00:00:00), +: (00:00:00), +100vh (00:00:00), +; (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +f4f7f2 (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +family (00:00:00), +: (00:00:00), +Arial (00:00:00), +, (00:00:00), +sans (00:00:00), +- (00:00:00), +serif (00:00:00), +; (00:00:00), +} (00:00:00), +margin (00:00:00), +- (00:00:00), +top (00:00:00), +: (00:00:00), +40px (00:00:00), +; (00:00:00), +# (00:00:00), +inventoryCard (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +min (00:00:00), +( (00:00:00), +90 (00:00:00), +% (00:00:00), +, (00:00:00), +420px (00:00:00), +) (00:00:00), +; (00:00:00), +padding (00:00:00), +: (00:00:00), +24px (00:00:00), +; (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +white (00:00:00), +; (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +18px (00:00:00), +; (00:00:00), +box (00:00:00), +- (00:00:00), +shadow (00:00:00), +: (00:00:00), +0 (00:00:00), +10px (00:00:00), +25px (00:00:00), +rgba (00:00:00), +( (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +. (00:00:00), +12 (00:00:00), +) (00:00:00), +; (00:00:00), +border (00:00:00), +- (00:00:00), +top (00:00:00), +: (00:00:00), +6px (00:00:00), +solid (00:00:00), +var (00:00:00), +( (00:00:00), +- (00:00:00), +- (00:00:00), +theme (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +inventoryCard (00:00:00), +p (00:00:00), +{ (00:00:00), +margin (00:00:00), +: (00:00:00), +12px (00:00:00), +0 (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +1 (00:00:00), +. (00:00:00), +2rem (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +btn (00:00:00), +{ (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +var (00:00:00), +( (00:00:00), +- (00:00:00), +- (00:00:00), +theme (00:00:00), +) (00:00:00), +; (00:00:00), +color (00:00:00), +: (00:00:00), +white (00:00:00), +; (00:00:00), +padding (00:00:00), +: (00:00:00), +14px (00:00:00), +34px (00:00:00), +; (00:00:00), +border (00:00:00), +: (00:00:00), +none (00:00:00), +; (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +999px (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +1rem (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +weight (00:00:00), +: (00:00:00), +bold (00:00:00), +; (00:00:00), +letter (00:00:00), +- (00:00:00), +spacing (00:00:00), +: (00:00:00), +1px (00:00:00), +; (00:00:00), +box (00:00:00), +- (00:00:00), +shadow (00:00:00), +: (00:00:00), +0 (00:00:00), +8px (00:00:00), +18px (00:00:00), +rgba (00:00:00), +( (00:00:00), +34 (00:00:00), +, (00:00:00), +136 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +. (00:00:00), +3 (00:00:00), +) (00:00:00), +; (00:00:00), +transition (00:00:00), +: (00:00:00), +transform (00:00:00), +0 (00:00:00), +. (00:00:00), +2s (00:00:00), +ease (00:00:00), +, (00:00:00), +box (00:00:00), +- (00:00:00), +shadow (00:00:00), +0 (00:00:00), +. (00:00:00), +2s (00:00:00), +ease (00:00:00), +, (00:00:00), +filter (00:00:00), +0 (00:00:00), +. (00:00:00), +2s (00:00:00), +ease (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +btn (00:00:00), +: (00:00:00), +hover (00:00:00), +{ (00:00:00), +cursor (00:00:00), +: (00:00:00), +pointer (00:00:00), +; (00:00:00), +transform (00:00:00), +: (00:00:00), +translateY (00:00:00), +( (00:00:00), +- (00:00:00), +3px (00:00:00), +) (00:00:00), +; (00:00:00), +filter (00:00:00), +: (00:00:00), +brightness (00:00:00), +( (00:00:00), +1 (00:00:00), +. (00:00:00), +15 (00:00:00), +) (00:00:00), +; (00:00:00), +box (00:00:00), +- (00:00:00), +shadow (00:00:00), +: (00:00:00), +0 (00:00:00), +12px (00:00:00), +24px (00:00:00), +rgba (00:00:00), +( (00:00:00), +34 (00:00:00), +, (00:00:00), +136 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +. (00:00:00), +45 (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +min (00:00:00), +( (00:00:00), +90 (00:00:00), +, (00:00:00), +500px (00:00:00), +) (00:00:00)</t>
+          <t>-font (00:00:42), -- (00:00:43), -family (00:00:44), -: (00:00:45), -" (00:00:46), -Arial (00:00:47), -" (00:00:48), -; (00:00:49), -# (00:01:00), -map (00:01:01), -{ (00:01:02), -width (00:01:03), -: (00:01:04), -100 (00:01:05), -% (00:01:06), -; (00:01:07), -} (00:01:08), -# (00:01:09), -marker (00:01:10), -{ (00:01:11), -width (00:01:12), -: (00:01:13), -3vw (00:01:14), -; (00:01:15), -height (00:01:26), -: (00:01:27), -3vw (00:01:28), -; (00:01:29), -background (00:01:30), -- (00:01:31), -color (00:01:32), -: (00:01:33), -black (00:01:34), -; (00:01:35), -border (00:01:36), -- (00:01:37), -radius (00:01:38), -: (00:01:39), -50 (00:01:40), -% (00:01:41), -; (00:01:42), -outline (00:01:43), -: (00:01:44), -5px (00:01:45), -solid (00:01:46), -var (00:01:47), -( (00:01:48), -- (00:01:49), -- (00:01:50), -theme (00:01:51), -) (00:01:52), -; (00:01:53), -border (00:02:03), -: (00:02:04), -5px (00:02:05), -solid (00:02:06), -white (00:02:07), -; (00:02:08), -position (00:02:16), -: (00:02:17), -absolute (00:02:18), -; (00:02:19), -top (00:02:20), -: (00:02:21), -0 (00:02:22), -; (00:02:23), -left (00:02:24), -: (00:02:25), -0 (00:02:26), -; (00:02:27), -transform (00:02:28), -: (00:02:29), -translate (00:02:30), -( (00:02:31), -- (00:02:32), -50 (00:02:33), -% (00:02:34), -, (00:02:35), -- (00:02:36), -50 (00:02:37), -% (00:02:38), -) (00:02:39), -; (00:02:40), -} (00:02:41), -# (00:02:42), -mapContainer (00:02:43), -{ (00:02:44), -position (00:02:45), -: (00:02:46), -relative (00:02:47), -; (00:02:48), -display (00:02:49), -: (00:02:50), -none (00:02:51), -; (00:02:52), -} (00:02:53), -100 (00:02:59) ~0.33, +gap (00:00:00), +: (00:00:00), +20px (00:00:00), +; (00:00:00), +min (00:00:00), +- (00:00:00), +height (00:00:00), +: (00:00:00), +100vh (00:00:00), +; (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +f4f7f2 (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +family (00:00:00), +: (00:00:00), +Arial (00:00:00), +, (00:00:00), +sans (00:00:00), +- (00:00:00), +serif (00:00:00), +; (00:00:00), +} (00:00:00), +margin (00:00:00), +- (00:00:00), +top (00:00:00), +: (00:00:00), +40px (00:00:00), +; (00:00:00), +# (00:00:00), +inventoryCard (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +min (00:00:00), +( (00:00:00), +90 (00:00:00), +% (00:00:00), +, (00:00:00), +420px (00:00:00), +) (00:00:00), +; (00:00:00), +padding (00:00:00), +: (00:00:00), +24px (00:00:00), +; (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +white (00:00:00), +; (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +18px (00:00:00), +; (00:00:00), +box (00:00:00), +- (00:00:00), +shadow (00:00:00), +: (00:00:00), +0 (00:00:00), +10px (00:00:00), +25px (00:00:00), +rgba (00:00:00), +( (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +. (00:00:00), +12 (00:00:00), +) (00:00:00), +; (00:00:00), +border (00:00:00), +- (00:00:00), +top (00:00:00), +: (00:00:00), +6px (00:00:00), +solid (00:00:00), +var (00:00:00), +( (00:00:00), +- (00:00:00), +- (00:00:00), +theme (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +inventoryCard (00:00:00), +p (00:00:00), +{ (00:00:00), +margin (00:00:00), +: (00:00:00), +12px (00:00:00), +0 (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +1 (00:00:00), +. (00:00:00), +2rem (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +btn (00:00:00), +{ (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +var (00:00:00), +( (00:00:00), +- (00:00:00), +- (00:00:00), +theme (00:00:00), +) (00:00:00), +; (00:00:00), +color (00:00:00), +: (00:00:00), +white (00:00:00), +; (00:00:00), +padding (00:00:00), +: (00:00:00), +14px (00:00:00), +34px (00:00:00), +; (00:00:00), +border (00:00:00), +: (00:00:00), +none (00:00:00), +; (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +999px (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +1rem (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +weight (00:00:00), +: (00:00:00), +bold (00:00:00), +; (00:00:00), +letter (00:00:00), +- (00:00:00), +spacing (00:00:00), +: (00:00:00), +1px (00:00:00), +; (00:00:00), +box (00:00:00), +- (00:00:00), +shadow (00:00:00), +: (00:00:00), +0 (00:00:00), +8px (00:00:00), +18px (00:00:00), +rgba (00:00:00), +( (00:00:00), +34 (00:00:00), +, (00:00:00), +136 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +. (00:00:00), +3 (00:00:00), +) (00:00:00), +; (00:00:00), +transition (00:00:00), +: (00:00:00), +transform (00:00:00), +0 (00:00:00), +. (00:00:00), +2s (00:00:00), +ease (00:00:00), +, (00:00:00), +box (00:00:00), +- (00:00:00), +shadow (00:00:00), +0 (00:00:00), +. (00:00:00), +2s (00:00:00), +ease (00:00:00), +, (00:00:00), +filter (00:00:00), +0 (00:00:00), +. (00:00:00), +2s (00:00:00), +ease (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +btn (00:00:00), +: (00:00:00), +hover (00:00:00), +{ (00:00:00), +cursor (00:00:00), +: (00:00:00), +pointer (00:00:00), +; (00:00:00), +transform (00:00:00), +: (00:00:00), +translateY (00:00:00), +( (00:00:00), +- (00:00:00), +3px (00:00:00), +) (00:00:00), +; (00:00:00), +filter (00:00:00), +: (00:00:00), +brightness (00:00:00), +( (00:00:00), +1 (00:00:00), +. (00:00:00), +15 (00:00:00), +) (00:00:00), +; (00:00:00), +box (00:00:00), +- (00:00:00), +shadow (00:00:00), +: (00:00:00), +0 (00:00:00), +12px (00:00:00), +24px (00:00:00), +rgba (00:00:00), +( (00:00:00), +34 (00:00:00), +, (00:00:00), +136 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +. (00:00:00), +45 (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +min (00:00:00), +( (00:00:00), +90 (00:00:00), +, (00:00:00), +500px (00:00:00), +) (00:00:00)</t>
         </is>
       </c>
       <c r="N87" t="n">
@@ -6154,7 +6154,7 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>-mapContainer (00:03:46), -. (00:03:47), -style (00:03:48), -. (00:03:49), -display (00:03:50), -= (00:03:51), -" (00:03:52), -none (00:03:53), -" (00:03:54), -; (00:03:55), -mapContainer (00:04:11), -. (00:04:12), -style (00:04:13), -. (00:04:14), -display (00:04:15), -= (00:04:16), -" (00:04:17), -block (00:04:18), -" (00:04:19), -; (00:04:20), -place (00:04:49), -showMarkerAt (00:04:58), -( (00:04:59), -place (00:05:00), -. (00:05:01), -top (00:05:02), -, (00:05:03), -place (00:05:04), -. (00:05:05), -left (00:05:06), -) (00:05:07), -; (00:05:08), -function (00:05:46), -showMarkerAt (00:05:47), -( (00:05:48), -top (00:05:49), -, (00:05:50), -left (00:05:51), -) (00:05:52), -{ (00:05:53), -marker (00:05:54), -. (00:05:55), -style (00:05:56), -. (00:05:57), -top (00:05:58), -= (00:05:59), -top (00:06:00), -; (00:06:01), -marker (00:06:02), -. (00:06:03), -style (00:06:04), -. (00:06:05), -left (00:06:06), -= (00:06:07), -left (00:06:08), -; (00:06:09), -} (00:06:10), +item (00:00:00), +showInventoryItem (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +; (00:00:00), +. (00:00:00), +catch (00:00:00), +( (00:00:00), +function (00:00:00), +( (00:00:00), +err (00:00:00), +) (00:00:00), +{ (00:00:00), +console (00:00:00), +. (00:00:00), +error (00:00:00), +( (00:00:00), +err (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +) (00:00:00), +function (00:00:00), +showInventoryItem (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +{ (00:00:00), +itemName (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Name (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +name (00:00:00), +; (00:00:00), +if (00:00:00), +( (00:00:00), +item (00:00:00), +. (00:00:00), +in (00:00:00), +_ (00:00:00), +store (00:00:00), +) (00:00:00), +{ (00:00:00), +itemStore (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +In (00:00:00), +store (00:00:00), +: (00:00:00), +yes (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00), +else (00:00:00), +{ (00:00:00), +itemStore (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +In (00:00:00), +store (00:00:00), +: (00:00:00), +no (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00), +itemPrice (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Price (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +price (00:00:00), ++ (00:00:00), +" (00:00:00), +€ (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+          <t>-mapContainer (00:03:46), -. (00:03:47), -style (00:03:48), -. (00:03:49), -display (00:03:50), -= (00:03:51), -" (00:03:52), -none (00:03:53), -" (00:03:54), -; (00:03:55), -mapContainer (00:04:11), -. (00:04:12), -style (00:04:13), -. (00:04:14), -display (00:04:15), -= (00:04:16), -" (00:04:17), -block (00:04:18), -" (00:04:19), -; (00:04:20), -place (00:04:49) ~0.00, -showMarkerAt (00:04:58), -( (00:04:59), -place (00:05:00), -. (00:05:01), -top (00:05:02), -, (00:05:03), -place (00:05:04), -. (00:05:05), -left (00:05:06), -) (00:05:07), -; (00:05:08), -function (00:05:46), -showMarkerAt (00:05:47), -( (00:05:48), -top (00:05:49), -, (00:05:50), -left (00:05:51), -) (00:05:52), -{ (00:05:53), -marker (00:05:54), -. (00:05:55), -style (00:05:56), -. (00:05:57), -top (00:05:58), -= (00:05:59), -top (00:06:00), -; (00:06:01), -marker (00:06:02), -. (00:06:03), -style (00:06:04), -. (00:06:05), -left (00:06:06), -= (00:06:07), -left (00:06:08), -; (00:06:09), -} (00:06:10), +item (00:00:00), +showInventoryItem (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +; (00:00:00), +. (00:00:00), +catch (00:00:00), +( (00:00:00), +function (00:00:00), +( (00:00:00), +err (00:00:00), +) (00:00:00), +{ (00:00:00), +console (00:00:00), +. (00:00:00), +error (00:00:00), +( (00:00:00), +err (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +) (00:00:00), +function (00:00:00), +showInventoryItem (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +{ (00:00:00), +itemName (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Name (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +name (00:00:00), +; (00:00:00), +if (00:00:00), +( (00:00:00), +item (00:00:00), +. (00:00:00), +in (00:00:00), +_ (00:00:00), +store (00:00:00), +) (00:00:00), +{ (00:00:00), +itemStore (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +In (00:00:00), +store (00:00:00), +: (00:00:00), +yes (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00), +else (00:00:00), +{ (00:00:00), +itemStore (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +In (00:00:00), +store (00:00:00), +: (00:00:00), +no (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00), +itemPrice (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Price (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +price (00:00:00), ++ (00:00:00), +" (00:00:00), +€ (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00)</t>
         </is>
       </c>
       <c r="P87" s="3" t="inlineStr">
@@ -6304,7 +6304,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>-QR (00:07:05), -Positioning (00:07:06), -QR (00:07:37), -Positioning (00:07:38), -&lt; (00:07:43), -div (00:07:44), -id (00:07:45), -= (00:07:46), -" (00:07:47), -mapContainer (00:07:48), -" (00:07:49), -&gt; (00:07:50), -&lt; (00:07:51), -img (00:07:52), -src (00:07:53), -= (00:07:54), -" (00:07:55), -map (00:07:56), -. (00:07:57), -png (00:07:58), -" (00:07:59), -id (00:08:00), -= (00:08:01), -" (00:08:02), -map (00:08:03), -" (00:08:04), -alt (00:08:05), -= (00:08:06), -" (00:08:07), -map (00:08:08), -" (00:08:09), -/ (00:08:10), -&gt; (00:08:11), -&lt; (00:08:12), -div (00:08:13), -id (00:08:14), -= (00:08:15), -" (00:08:16), -marker (00:08:17), -" (00:08:18), -&gt; (00:08:19), -&lt; (00:08:20), -/ (00:08:21), -div (00:08:22), -&gt; (00:08:23), -&lt; (00:08:24), -/ (00:08:25), -div (00:08:26), -&gt; (00:08:27), +Inventory (00:00:00), +System (00:00:00), +Inventory (00:00:00), +System (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +inventory (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +name (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +stock (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +price (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
+          <t>-QR (00:07:05) ~0.00, -Positioning (00:07:06) ~0.18, -QR (00:07:37) ~0.00, -Positioning (00:07:38) ~0.18, -&lt; (00:07:43), -div (00:07:44), -id (00:07:45), -= (00:07:46), -" (00:07:47), -mapContainer (00:07:48), -" (00:07:49), -&gt; (00:07:50), -&lt; (00:07:51), -img (00:07:52), -src (00:07:53), -= (00:07:54), -" (00:07:55), -map (00:07:56), -. (00:07:57), -png (00:07:58), -" (00:07:59), -id (00:08:00), -= (00:08:01), -" (00:08:02), -map (00:08:03), -" (00:08:04), -alt (00:08:05), -= (00:08:06), -" (00:08:07), -map (00:08:08), -" (00:08:09), -/ (00:08:10), -&gt; (00:08:11), -&lt; (00:08:12), -div (00:08:13), -id (00:08:14), -= (00:08:15), -" (00:08:16), -marker (00:08:17), -" (00:08:18), -&gt; (00:08:19), -&lt; (00:08:20), -/ (00:08:21), -div (00:08:22), -&gt; (00:08:23), -&lt; (00:08:24), -/ (00:08:25), -div (00:08:26), -&gt; (00:08:27), +Inventory (00:00:00), +System (00:00:00), +Inventory (00:00:00), +System (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +inventory (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +name (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +stock (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +price (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
         </is>
       </c>
       <c r="L89" t="n">
@@ -6320,7 +6320,7 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>-mapContainer (00:03:46), -mapContainer (00:04:11), -place (00:04:49), -showMarkerAt (00:04:58), -( (00:04:59), -place (00:05:00), -. (00:05:01), -top (00:05:02), -, (00:05:03), -place (00:05:04), -. (00:05:05), -left (00:05:06), -) (00:05:07), -; (00:05:08), -function (00:05:46), -showMarkerAt (00:05:47), -( (00:05:48), -top (00:05:49), -, (00:05:50), -left (00:05:51), -) (00:05:52), -{ (00:05:53), -marker (00:05:54), -. (00:05:55), -style (00:05:56), -. (00:05:57), -top (00:05:58), -= (00:05:59), -top (00:06:00), -; (00:06:01), -marker (00:06:02), -. (00:06:03), -style (00:06:04), -. (00:06:05), -left (00:06:06), -= (00:06:07), -left (00:06:08), -; (00:06:09), -} (00:06:10), +inventory (00:00:00), +inventory (00:00:00), +item (00:00:00), +showItem (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +; (00:00:00), +function (00:00:00), +showItem (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +{ (00:00:00), +name (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Name (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +name (00:00:00), +; (00:00:00), +stock (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +item (00:00:00), +. (00:00:00), +in (00:00:00), +_ (00:00:00), +store (00:00:00), +? (00:00:00), +" (00:00:00), +In (00:00:00), +store (00:00:00), +: (00:00:00), +yes (00:00:00), +" (00:00:00), +: (00:00:00), +" (00:00:00), +In (00:00:00), +store (00:00:00), +: (00:00:00), +no (00:00:00), +" (00:00:00), +; (00:00:00), +price (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Price (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +price (00:00:00), ++ (00:00:00), +" (00:00:00), +€ (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+          <t>-mapContainer (00:03:46) ~0.17, -mapContainer (00:04:11) ~0.17, -place (00:04:49) ~0.00, -showMarkerAt (00:04:58), -( (00:04:59), -place (00:05:00), -. (00:05:01), -top (00:05:02), -, (00:05:03), -place (00:05:04), -. (00:05:05), -left (00:05:06), -) (00:05:07), -; (00:05:08), -function (00:05:46), -showMarkerAt (00:05:47), -( (00:05:48), -top (00:05:49), -, (00:05:50), -left (00:05:51), -) (00:05:52), -{ (00:05:53), -marker (00:05:54), -. (00:05:55), -style (00:05:56), -. (00:05:57), -top (00:05:58), -= (00:05:59), -top (00:06:00), -; (00:06:01), -marker (00:06:02), -. (00:06:03), -style (00:06:04), -. (00:06:05), -left (00:06:06), -= (00:06:07), -left (00:06:08), -; (00:06:09), -} (00:06:10), +inventory (00:00:00), +inventory (00:00:00), +item (00:00:00), +showItem (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +; (00:00:00), +function (00:00:00), +showItem (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +{ (00:00:00), +name (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Name (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +name (00:00:00), +; (00:00:00), +stock (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +item (00:00:00), +. (00:00:00), +in (00:00:00), +_ (00:00:00), +store (00:00:00), +? (00:00:00), +" (00:00:00), +In (00:00:00), +store (00:00:00), +: (00:00:00), +yes (00:00:00), +" (00:00:00), +: (00:00:00), +" (00:00:00), +In (00:00:00), +store (00:00:00), +: (00:00:00), +no (00:00:00), +" (00:00:00), +; (00:00:00), +price (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Price (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +price (00:00:00), ++ (00:00:00), +" (00:00:00), +€ (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00)</t>
         </is>
       </c>
       <c r="P89" s="3" t="inlineStr">
@@ -6470,7 +6470,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>-Positioning (00:07:06), -Positioning (00:07:38), -onclick (00:08:35), -= (00:08:36), -" (00:08:37), -toggleScanner (00:08:38), -( (00:08:39), -) (00:08:40), -" (00:08:41), +, (00:00:00), +user (00:00:00), +- (00:00:00), +scalable (00:00:00), += (00:00:00), +yes (00:00:00), +Inventory (00:00:00), +System (00:00:00), +📦 (00:00:00), +Inventory (00:00:00), +System (00:00:00), +store (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +inventoryPanel (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +inventoryHeader (00:00:00), +" (00:00:00), +&gt; (00:00:00), +📋 (00:00:00), +PRODUCT (00:00:00), +DETAILS (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +inventoryInfo (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +info (00:00:00), +- (00:00:00), +placeholder (00:00:00), +" (00:00:00), +&gt; (00:00:00), +🔍 (00:00:00), +Scan (00:00:00), +a (00:00:00), +QR (00:00:00), +code (00:00:00), +to (00:00:00), +see (00:00:00), +inventory (00:00:00), +data (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +scan (00:00:00), +- (00:00:00), +button (00:00:00), +" (00:00:00), +📷 (00:00:00), +QR (00:00:00), +@ (00:00:00), +2 (00:00:00), +. (00:00:00), +3 (00:00:00), +. (00:00:00), +8 (00:00:00), +/ (00:00:00), +html5 (00:00:00), +- (00:00:00), +qrcode (00:00:00), +. (00:00:00), +min (00:00:00), +. (00:00:00), +js (00:00:00)</t>
+          <t>-Positioning (00:07:06) ~0.09, -Positioning (00:07:38) ~0.09, -onclick (00:08:35), -= (00:08:36), -" (00:08:37), -toggleScanner (00:08:38), -( (00:08:39), -) (00:08:40), -" (00:08:41), +, (00:00:00), +user (00:00:00), +- (00:00:00), +scalable (00:00:00), += (00:00:00), +yes (00:00:00), +Inventory (00:00:00), +System (00:00:00), +📦 (00:00:00), +Inventory (00:00:00), +System (00:00:00), +store (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +inventoryPanel (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +inventoryHeader (00:00:00), +" (00:00:00), +&gt; (00:00:00), +📋 (00:00:00), +PRODUCT (00:00:00), +DETAILS (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +inventoryInfo (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +info (00:00:00), +- (00:00:00), +placeholder (00:00:00), +" (00:00:00), +&gt; (00:00:00), +🔍 (00:00:00), +Scan (00:00:00), +a (00:00:00), +QR (00:00:00), +code (00:00:00), +to (00:00:00), +see (00:00:00), +inventory (00:00:00), +data (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +scan (00:00:00), +- (00:00:00), +button (00:00:00), +" (00:00:00), +📷 (00:00:00), +QR (00:00:00), +@ (00:00:00), +2 (00:00:00), +. (00:00:00), +3 (00:00:00), +. (00:00:00), +8 (00:00:00), +/ (00:00:00), +html5 (00:00:00), +- (00:00:00), +qrcode (00:00:00), +. (00:00:00), +min (00:00:00), +. (00:00:00), +js (00:00:00)</t>
         </is>
       </c>
       <c r="L91" t="n">
@@ -6636,7 +6636,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>-QR (00:07:05), -Positioning (00:07:06), -QR (00:07:37), -Positioning (00:07:38), -&lt; (00:07:43), -div (00:07:44), -id (00:07:45), -= (00:07:46), -" (00:07:47), -mapContainer (00:07:48), -" (00:07:49), -&gt; (00:07:50), -&lt; (00:07:51), -img (00:07:52), -src (00:07:53), -= (00:07:54), -" (00:07:55), -map (00:07:56), -. (00:07:57), -png (00:07:58), -" (00:07:59), -id (00:08:00), -= (00:08:01), -" (00:08:02), -map (00:08:03), -" (00:08:04), -alt (00:08:05), -= (00:08:06), -" (00:08:07), -map (00:08:08), -" (00:08:09), -/ (00:08:10), -&gt; (00:08:11), -&lt; (00:08:12), -div (00:08:13), -id (00:08:14), -= (00:08:15), -" (00:08:16), -marker (00:08:17), -" (00:08:18), -&gt; (00:08:19), -&lt; (00:08:20), -/ (00:08:21), -div (00:08:22), -&gt; (00:08:23), -&lt; (00:08:24), -/ (00:08:25), -div (00:08:26), -&gt; (00:08:27), +Inventory (00:00:00), +Scanner (00:00:00), +Inventory (00:00:00), +Scanner (00:00:00), +ITEM (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +inventory (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemName (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Name (00:00:00), +: (00:00:00), +- (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemStore (00:00:00), +" (00:00:00), +&gt; (00:00:00), +In (00:00:00), +store (00:00:00), +: (00:00:00), +- (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemPrice (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Price (00:00:00), +: (00:00:00), +- (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
+          <t>-QR (00:07:05) ~0.00, -Positioning (00:07:06) ~0.09, -QR (00:07:37) ~0.00, -Positioning (00:07:38) ~0.09, -&lt; (00:07:43), -div (00:07:44), -id (00:07:45), -= (00:07:46), -" (00:07:47), -mapContainer (00:07:48), -" (00:07:49), -&gt; (00:07:50), -&lt; (00:07:51), -img (00:07:52), -src (00:07:53), -= (00:07:54), -" (00:07:55), -map (00:07:56), -. (00:07:57), -png (00:07:58), -" (00:07:59), -id (00:08:00), -= (00:08:01), -" (00:08:02), -map (00:08:03), -" (00:08:04), -alt (00:08:05), -= (00:08:06), -" (00:08:07), -map (00:08:08), -" (00:08:09), -/ (00:08:10), -&gt; (00:08:11), -&lt; (00:08:12), -div (00:08:13), -id (00:08:14), -= (00:08:15), -" (00:08:16), -marker (00:08:17), -" (00:08:18), -&gt; (00:08:19), -&lt; (00:08:20), -/ (00:08:21), -div (00:08:22), -&gt; (00:08:23), -&lt; (00:08:24), -/ (00:08:25), -div (00:08:26), -&gt; (00:08:27), +Inventory (00:00:00), +Scanner (00:00:00), +Inventory (00:00:00), +Scanner (00:00:00), +ITEM (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +inventory (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemName (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Name (00:00:00), +: (00:00:00), +- (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemStore (00:00:00), +" (00:00:00), +&gt; (00:00:00), +In (00:00:00), +store (00:00:00), +: (00:00:00), +- (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemPrice (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Price (00:00:00), +: (00:00:00), +- (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
         </is>
       </c>
       <c r="L93" t="n">
@@ -6652,7 +6652,7 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>-mapContainer (00:03:46), -. (00:03:47), -style (00:03:48), -. (00:03:49), -display (00:03:50), -= (00:03:51), -" (00:03:52), -none (00:03:53), -" (00:03:54), -; (00:03:55), -mapContainer (00:04:11), -. (00:04:12), -style (00:04:13), -. (00:04:14), -display (00:04:15), -= (00:04:16), -" (00:04:17), -block (00:04:18), -" (00:04:19), -; (00:04:20), -place (00:04:49), -showMarkerAt (00:04:58), -( (00:04:59), -place (00:05:00), -. (00:05:01), -top (00:05:02), -, (00:05:03), -place (00:05:04), -. (00:05:05), -left (00:05:06), -) (00:05:07), -; (00:05:08), -function (00:05:46), -showMarkerAt (00:05:47), -( (00:05:48), -top (00:05:49), -, (00:05:50), -left (00:05:51), -) (00:05:52), -{ (00:05:53), -marker (00:05:54), -. (00:05:55), -style (00:05:56), -. (00:05:57), -top (00:05:58), -= (00:05:59), -top (00:06:00), -; (00:06:01), -marker (00:06:02), -. (00:06:03), -style (00:06:04), -. (00:06:05), -left (00:06:06), -= (00:06:07), -left (00:06:08), -; (00:06:09), -} (00:06:10), +ITEM (00:00:00), +item (00:00:00), +showInventoryItem (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +; (00:00:00), +function (00:00:00), +showInventoryItem (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +{ (00:00:00), +itemName (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Name (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +name (00:00:00), +; (00:00:00), +itemStore (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +In (00:00:00), +store (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +( (00:00:00), +item (00:00:00), +. (00:00:00), +inStock (00:00:00), +? (00:00:00), +" (00:00:00), +yes (00:00:00), +" (00:00:00), +: (00:00:00), +" (00:00:00), +no (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +itemPrice (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Price (00:00:00), +: (00:00:00), +€ (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +price (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+          <t>-mapContainer (00:03:46), -. (00:03:47), -style (00:03:48), -. (00:03:49), -display (00:03:50), -= (00:03:51), -" (00:03:52), -none (00:03:53), -" (00:03:54), -; (00:03:55), -mapContainer (00:04:11), -. (00:04:12), -style (00:04:13), -. (00:04:14), -display (00:04:15), -= (00:04:16), -" (00:04:17), -block (00:04:18), -" (00:04:19), -; (00:04:20), -place (00:04:49) ~0.00, -showMarkerAt (00:04:58), -( (00:04:59), -place (00:05:00), -. (00:05:01), -top (00:05:02), -, (00:05:03), -place (00:05:04), -. (00:05:05), -left (00:05:06), -) (00:05:07), -; (00:05:08), -function (00:05:46), -showMarkerAt (00:05:47), -( (00:05:48), -top (00:05:49), -, (00:05:50), -left (00:05:51), -) (00:05:52), -{ (00:05:53), -marker (00:05:54), -. (00:05:55), -style (00:05:56), -. (00:05:57), -top (00:05:58), -= (00:05:59), -top (00:06:00), -; (00:06:01), -marker (00:06:02), -. (00:06:03), -style (00:06:04), -. (00:06:05), -left (00:06:06), -= (00:06:07), -left (00:06:08), -; (00:06:09), -} (00:06:10), +ITEM (00:00:00), +item (00:00:00), +showInventoryItem (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +; (00:00:00), +function (00:00:00), +showInventoryItem (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +{ (00:00:00), +itemName (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Name (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +name (00:00:00), +; (00:00:00), +itemStore (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +In (00:00:00), +store (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +( (00:00:00), +item (00:00:00), +. (00:00:00), +inStock (00:00:00), +? (00:00:00), +" (00:00:00), +yes (00:00:00), +" (00:00:00), +: (00:00:00), +" (00:00:00), +no (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +itemPrice (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Price (00:00:00), +: (00:00:00), +€ (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +price (00:00:00), +; (00:00:00), +} (00:00:00)</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
@@ -6714,7 +6714,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>-QR (00:07:05), -Positioning (00:07:06), -QR (00:07:37), -Positioning (00:07:38), -&lt; (00:07:43), -div (00:07:44), -id (00:07:45), -= (00:07:46), -" (00:07:47), -mapContainer (00:07:48), -" (00:07:49), -&gt; (00:07:50), -&lt; (00:07:51), -img (00:07:52), -src (00:07:53), -= (00:07:54), -" (00:07:55), -map (00:07:56), -. (00:07:57), -png (00:07:58), -" (00:07:59), -id (00:08:00), -= (00:08:01), -" (00:08:02), -map (00:08:03), -" (00:08:04), -alt (00:08:05), -= (00:08:06), -" (00:08:07), -map (00:08:08), -" (00:08:09), -/ (00:08:10), -&gt; (00:08:11), -&lt; (00:08:12), -div (00:08:13), -id (00:08:14), -= (00:08:15), -" (00:08:16), -marker (00:08:17), -" (00:08:18), -&gt; (00:08:19), -&lt; (00:08:20), -/ (00:08:21), -div (00:08:22), -&gt; (00:08:23), -&lt; (00:08:24), -/ (00:08:25), -div (00:08:26), -&gt; (00:08:27), +Inventory (00:00:00), +System (00:00:00), +Inventory (00:00:00), +System (00:00:00), +&lt; (00:00:00), +section (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +inventoryCard (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemName (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Name (00:00:00), +: (00:00:00), +scan (00:00:00), +an (00:00:00), +item (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemStore (00:00:00), +" (00:00:00), +&gt; (00:00:00), +In (00:00:00), +store (00:00:00), +: (00:00:00), +- (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemPrice (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Price (00:00:00), +: (00:00:00), +- (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +section (00:00:00), +&gt; (00:00:00), +ITEM (00:00:00)</t>
+          <t>-QR (00:07:05) ~0.00, -Positioning (00:07:06) ~0.18, -QR (00:07:37) ~0.00, -Positioning (00:07:38) ~0.18, -&lt; (00:07:43), -div (00:07:44), -id (00:07:45), -= (00:07:46), -" (00:07:47), -mapContainer (00:07:48), -" (00:07:49), -&gt; (00:07:50), -&lt; (00:07:51), -img (00:07:52), -src (00:07:53), -= (00:07:54), -" (00:07:55), -map (00:07:56), -. (00:07:57), -png (00:07:58), -" (00:07:59), -id (00:08:00), -= (00:08:01), -" (00:08:02), -map (00:08:03), -" (00:08:04), -alt (00:08:05), -= (00:08:06), -" (00:08:07), -map (00:08:08), -" (00:08:09), -/ (00:08:10), -&gt; (00:08:11), -&lt; (00:08:12), -div (00:08:13), -id (00:08:14), -= (00:08:15), -" (00:08:16), -marker (00:08:17), -" (00:08:18), -&gt; (00:08:19), -&lt; (00:08:20), -/ (00:08:21), -div (00:08:22), -&gt; (00:08:23), -&lt; (00:08:24), -/ (00:08:25), -div (00:08:26), -&gt; (00:08:27), +Inventory (00:00:00), +System (00:00:00), +Inventory (00:00:00), +System (00:00:00), +&lt; (00:00:00), +section (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +inventoryCard (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemName (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Name (00:00:00), +: (00:00:00), +scan (00:00:00), +an (00:00:00), +item (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemStore (00:00:00), +" (00:00:00), +&gt; (00:00:00), +In (00:00:00), +store (00:00:00), +: (00:00:00), +- (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +itemPrice (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Price (00:00:00), +: (00:00:00), +- (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +section (00:00:00), +&gt; (00:00:00), +ITEM (00:00:00)</t>
         </is>
       </c>
       <c r="L94" t="n">
@@ -6730,7 +6730,7 @@
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>-mapContainer (00:03:46), -. (00:03:47), -style (00:03:48), -. (00:03:49), -display (00:03:50), -= (00:03:51), -" (00:03:52), -none (00:03:53), -" (00:03:54), -; (00:03:55), -mapContainer (00:04:11), -. (00:04:12), -style (00:04:13), -. (00:04:14), -display (00:04:15), -= (00:04:16), -" (00:04:17), -block (00:04:18), -" (00:04:19), -; (00:04:20), -place (00:04:49), -showMarkerAt (00:04:58), -( (00:04:59), -place (00:05:00), -. (00:05:01), -top (00:05:02), -, (00:05:03), -place (00:05:04), -. (00:05:05), -left (00:05:06), -) (00:05:07), -; (00:05:08), -function (00:05:46), -showMarkerAt (00:05:47), -( (00:05:48), -top (00:05:49), -, (00:05:50), -left (00:05:51), -) (00:05:52), -{ (00:05:53), -marker (00:05:54), -. (00:05:55), -style (00:05:56), -. (00:05:57), -top (00:05:58), -= (00:05:59), -top (00:06:00), -; (00:06:01), -marker (00:06:02), -. (00:06:03), -style (00:06:04), -. (00:06:05), -left (00:06:06), -= (00:06:07), -left (00:06:08), -; (00:06:09), -} (00:06:10), +ITEM (00:00:00), +item (00:00:00), +showInventoryItem (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +; (00:00:00), +. (00:00:00), +catch (00:00:00), +( (00:00:00), +function (00:00:00), +( (00:00:00), +err (00:00:00), +) (00:00:00), +{ (00:00:00), +console (00:00:00), +. (00:00:00), +error (00:00:00), +( (00:00:00), +err (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +) (00:00:00), +function (00:00:00), +showInventoryItem (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +{ (00:00:00), +itemName (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Name (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +name (00:00:00), +; (00:00:00), +itemStore (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +In (00:00:00), +store (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +( (00:00:00), +item (00:00:00), +. (00:00:00), +inStock (00:00:00), +? (00:00:00), +" (00:00:00), +yes (00:00:00), +" (00:00:00), +: (00:00:00), +" (00:00:00), +no (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +itemPrice (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Price (00:00:00), +: (00:00:00), +€ (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +price (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+          <t>-mapContainer (00:03:46), -. (00:03:47), -style (00:03:48), -. (00:03:49), -display (00:03:50), -= (00:03:51), -" (00:03:52), -none (00:03:53), -" (00:03:54), -; (00:03:55), -mapContainer (00:04:11), -. (00:04:12), -style (00:04:13), -. (00:04:14), -display (00:04:15), -= (00:04:16), -" (00:04:17), -block (00:04:18), -" (00:04:19), -; (00:04:20), -place (00:04:49) ~0.00, -showMarkerAt (00:04:58), -( (00:04:59), -place (00:05:00), -. (00:05:01), -top (00:05:02), -, (00:05:03), -place (00:05:04), -. (00:05:05), -left (00:05:06), -) (00:05:07), -; (00:05:08), -function (00:05:46), -showMarkerAt (00:05:47), -( (00:05:48), -top (00:05:49), -, (00:05:50), -left (00:05:51), -) (00:05:52), -{ (00:05:53), -marker (00:05:54), -. (00:05:55), -style (00:05:56), -. (00:05:57), -top (00:05:58), -= (00:05:59), -top (00:06:00), -; (00:06:01), -marker (00:06:02), -. (00:06:03), -style (00:06:04), -. (00:06:05), -left (00:06:06), -= (00:06:07), -left (00:06:08), -; (00:06:09), -} (00:06:10), +ITEM (00:00:00), +item (00:00:00), +showInventoryItem (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +; (00:00:00), +. (00:00:00), +catch (00:00:00), +( (00:00:00), +function (00:00:00), +( (00:00:00), +err (00:00:00), +) (00:00:00), +{ (00:00:00), +console (00:00:00), +. (00:00:00), +error (00:00:00), +( (00:00:00), +err (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +) (00:00:00), +function (00:00:00), +showInventoryItem (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +{ (00:00:00), +itemName (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Name (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +name (00:00:00), +; (00:00:00), +itemStore (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +In (00:00:00), +store (00:00:00), +: (00:00:00), +" (00:00:00), ++ (00:00:00), +( (00:00:00), +item (00:00:00), +. (00:00:00), +inStock (00:00:00), +? (00:00:00), +" (00:00:00), +yes (00:00:00), +" (00:00:00), +: (00:00:00), +" (00:00:00), +no (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +itemPrice (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Price (00:00:00), +: (00:00:00), +€ (00:00:00), +" (00:00:00), ++ (00:00:00), +item (00:00:00), +. (00:00:00), +price (00:00:00), +; (00:00:00), +} (00:00:00)</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
@@ -6959,7 +6959,7 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>-place (00:04:49), -showMarkerAt (00:04:58), -( (00:04:59), -place (00:05:00), -. (00:05:01), -top (00:05:02), -, (00:05:03), -place (00:05:04), -. (00:05:05), -left (00:05:06), -) (00:05:07), -; (00:05:08), +const (00:00:00), +mapContainer (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +mapContainer (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +btn (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +btn (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +itemName (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +itemName (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +itemAvailability (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +itemAvailability (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +itemPrice (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +itemPrice (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +try (00:00:00), +{ (00:00:00), +data (00:00:00), +displayInventory (00:00:00), +( (00:00:00), +data (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +catch (00:00:00), +( (00:00:00), +e (00:00:00), +) (00:00:00), +{ (00:00:00), +console (00:00:00), +. (00:00:00), +error (00:00:00), +( (00:00:00), +" (00:00:00), +Scanned (00:00:00), +data (00:00:00), +is (00:00:00), +not (00:00:00), +valid (00:00:00), +JSON (00:00:00), +: (00:00:00), +" (00:00:00), +, (00:00:00), +e (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +function (00:00:00), +displayInventory (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +{ (00:00:00), +itemName (00:00:00), +. (00:00:00), +innerHTML (00:00:00), += (00:00:00), +` (00:00:00), +&lt; (00:00:00), +strong (00:00:00), +&gt; (00:00:00), +Product (00:00:00), +Name (00:00:00), +: (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +strong (00:00:00), +&gt; (00:00:00), +$ (00:00:00), +{ (00:00:00), +item (00:00:00), +. (00:00:00), +name (00:00:00), +| (00:00:00), +| (00:00:00), +" (00:00:00), +N (00:00:00), +/ (00:00:00), +A (00:00:00), +" (00:00:00), +} (00:00:00), +` (00:00:00), +; (00:00:00), +if (00:00:00), +( (00:00:00), +item (00:00:00), +. (00:00:00), +in (00:00:00), +_ (00:00:00), +store (00:00:00), += (00:00:00), += (00:00:00), += (00:00:00), +true (00:00:00), +| (00:00:00), +| (00:00:00), +item (00:00:00), +. (00:00:00), +in (00:00:00), +_ (00:00:00), +store (00:00:00), += (00:00:00), += (00:00:00), += (00:00:00), +" (00:00:00), +true (00:00:00), +" (00:00:00), +) (00:00:00), +{ (00:00:00), +itemAvailability (00:00:00), +. (00:00:00), +innerHTML (00:00:00), += (00:00:00), +` (00:00:00), +&lt; (00:00:00), +strong (00:00:00), +&gt; (00:00:00), +Availability (00:00:00), +: (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +strong (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +span (00:00:00), +style (00:00:00), += (00:00:00), +" (00:00:00), +color (00:00:00), +: (00:00:00), +green (00:00:00), +; (00:00:00), +" (00:00:00), +&gt; (00:00:00), +In (00:00:00), +Stock (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +span (00:00:00), +&gt; (00:00:00), +` (00:00:00), +; (00:00:00), +} (00:00:00), +else (00:00:00), +{ (00:00:00), +itemAvailability (00:00:00), +. (00:00:00), +innerHTML (00:00:00), += (00:00:00), +` (00:00:00), +&lt; (00:00:00), +strong (00:00:00), +&gt; (00:00:00), +Availability (00:00:00), +: (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +strong (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +span (00:00:00), +style (00:00:00), += (00:00:00), +" (00:00:00), +color (00:00:00), +: (00:00:00), +red (00:00:00), +; (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Out (00:00:00), +of (00:00:00), +Stock (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +span (00:00:00), +&gt; (00:00:00), +` (00:00:00), +; (00:00:00), +} (00:00:00), +if (00:00:00), +( (00:00:00), +item (00:00:00), +. (00:00:00), +price (00:00:00), +! (00:00:00), += (00:00:00), += (00:00:00), +undefined (00:00:00), +) (00:00:00), +{ (00:00:00), +itemAvailability (00:00:00), +. (00:00:00), +innerHTML (00:00:00), ++ (00:00:00), += (00:00:00), +` (00:00:00), +( (00:00:00), +$ (00:00:00), +{ (00:00:00), +item (00:00:00), +. (00:00:00), +in (00:00:00), +_ (00:00:00), +store (00:00:00), +? (00:00:00), +' (00:00:00), +Available (00:00:00), +' (00:00:00), +: (00:00:00), +' (00:00:00), +Unavailable (00:00:00), +' (00:00:00), +} (00:00:00), +) (00:00:00), +` (00:00:00), +; (00:00:00), +itemPrice (00:00:00), +. (00:00:00), +innerHTML (00:00:00), += (00:00:00), +` (00:00:00), +&lt; (00:00:00), +strong (00:00:00), +&gt; (00:00:00), +Price (00:00:00), +: (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +strong (00:00:00), +&gt; (00:00:00), +€ (00:00:00), +$ (00:00:00), +{ (00:00:00), +parseFloat (00:00:00), +( (00:00:00), +item (00:00:00), +. (00:00:00), +price (00:00:00), +) (00:00:00), +. (00:00:00), +toFixed (00:00:00), +( (00:00:00), +2 (00:00:00), +) (00:00:00), +} (00:00:00), +` (00:00:00), +; (00:00:00), +} (00:00:00), +else (00:00:00), +{ (00:00:00), +itemPrice (00:00:00), +. (00:00:00), +innerHTML (00:00:00), += (00:00:00), +` (00:00:00), +&lt; (00:00:00), +strong (00:00:00), +&gt; (00:00:00), +Price (00:00:00), +: (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +strong (00:00:00), +&gt; (00:00:00), +N (00:00:00), +/ (00:00:00), +A (00:00:00), +` (00:00:00), +; (00:00:00), +} (00:00:00), +} (00:00:00), +const (00:00:00), +marker (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +marker (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +if (00:00:00), +( (00:00:00), +marker (00:00:00), +) (00:00:00), +{ (00:00:00), +} (00:00:00)</t>
+          <t>-place (00:04:49) ~0.20, -showMarkerAt (00:04:58), -( (00:04:59), -place (00:05:00), -. (00:05:01), -top (00:05:02), -, (00:05:03), -place (00:05:04), -. (00:05:05), -left (00:05:06), -) (00:05:07), -; (00:05:08), +const (00:00:00), +mapContainer (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +mapContainer (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +btn (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +btn (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +itemName (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +itemName (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +itemAvailability (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +itemAvailability (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +itemPrice (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +itemPrice (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +try (00:00:00), +{ (00:00:00), +data (00:00:00), +displayInventory (00:00:00), +( (00:00:00), +data (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +catch (00:00:00), +( (00:00:00), +e (00:00:00), +) (00:00:00), +{ (00:00:00), +console (00:00:00), +. (00:00:00), +error (00:00:00), +( (00:00:00), +" (00:00:00), +Scanned (00:00:00), +data (00:00:00), +is (00:00:00), +not (00:00:00), +valid (00:00:00), +JSON (00:00:00), +: (00:00:00), +" (00:00:00), +, (00:00:00), +e (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +function (00:00:00), +displayInventory (00:00:00), +( (00:00:00), +item (00:00:00), +) (00:00:00), +{ (00:00:00), +itemName (00:00:00), +. (00:00:00), +innerHTML (00:00:00), += (00:00:00), +` (00:00:00), +&lt; (00:00:00), +strong (00:00:00), +&gt; (00:00:00), +Product (00:00:00), +Name (00:00:00), +: (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +strong (00:00:00), +&gt; (00:00:00), +$ (00:00:00), +{ (00:00:00), +item (00:00:00), +. (00:00:00), +name (00:00:00), +| (00:00:00), +| (00:00:00), +" (00:00:00), +N (00:00:00), +/ (00:00:00), +A (00:00:00), +" (00:00:00), +} (00:00:00), +` (00:00:00), +; (00:00:00), +if (00:00:00), +( (00:00:00), +item (00:00:00), +. (00:00:00), +in (00:00:00), +_ (00:00:00), +store (00:00:00), += (00:00:00), += (00:00:00), += (00:00:00), +true (00:00:00), +| (00:00:00), +| (00:00:00), +item (00:00:00), +. (00:00:00), +in (00:00:00), +_ (00:00:00), +store (00:00:00), += (00:00:00), += (00:00:00), += (00:00:00), +" (00:00:00), +true (00:00:00), +" (00:00:00), +) (00:00:00), +{ (00:00:00), +itemAvailability (00:00:00), +. (00:00:00), +innerHTML (00:00:00), += (00:00:00), +` (00:00:00), +&lt; (00:00:00), +strong (00:00:00), +&gt; (00:00:00), +Availability (00:00:00), +: (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +strong (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +span (00:00:00), +style (00:00:00), += (00:00:00), +" (00:00:00), +color (00:00:00), +: (00:00:00), +green (00:00:00), +; (00:00:00), +" (00:00:00), +&gt; (00:00:00), +In (00:00:00), +Stock (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +span (00:00:00), +&gt; (00:00:00), +` (00:00:00), +; (00:00:00), +} (00:00:00), +else (00:00:00), +{ (00:00:00), +itemAvailability (00:00:00), +. (00:00:00), +innerHTML (00:00:00), += (00:00:00), +` (00:00:00), +&lt; (00:00:00), +strong (00:00:00), +&gt; (00:00:00), +Availability (00:00:00), +: (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +strong (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +span (00:00:00), +style (00:00:00), += (00:00:00), +" (00:00:00), +color (00:00:00), +: (00:00:00), +red (00:00:00), +; (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Out (00:00:00), +of (00:00:00), +Stock (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +span (00:00:00), +&gt; (00:00:00), +` (00:00:00), +; (00:00:00), +} (00:00:00), +if (00:00:00), +( (00:00:00), +item (00:00:00), +. (00:00:00), +price (00:00:00), +! (00:00:00), += (00:00:00), += (00:00:00), +undefined (00:00:00), +) (00:00:00), +{ (00:00:00), +itemAvailability (00:00:00), +. (00:00:00), +innerHTML (00:00:00), ++ (00:00:00), += (00:00:00), +` (00:00:00), +( (00:00:00), +$ (00:00:00), +{ (00:00:00), +item (00:00:00), +. (00:00:00), +in (00:00:00), +_ (00:00:00), +store (00:00:00), +? (00:00:00), +' (00:00:00), +Available (00:00:00), +' (00:00:00), +: (00:00:00), +' (00:00:00), +Unavailable (00:00:00), +' (00:00:00), +} (00:00:00), +) (00:00:00), +` (00:00:00), +; (00:00:00), +itemPrice (00:00:00), +. (00:00:00), +innerHTML (00:00:00), += (00:00:00), +` (00:00:00), +&lt; (00:00:00), +strong (00:00:00), +&gt; (00:00:00), +Price (00:00:00), +: (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +strong (00:00:00), +&gt; (00:00:00), +€ (00:00:00), +$ (00:00:00), +{ (00:00:00), +parseFloat (00:00:00), +( (00:00:00), +item (00:00:00), +. (00:00:00), +price (00:00:00), +) (00:00:00), +. (00:00:00), +toFixed (00:00:00), +( (00:00:00), +2 (00:00:00), +) (00:00:00), +} (00:00:00), +` (00:00:00), +; (00:00:00), +} (00:00:00), +else (00:00:00), +{ (00:00:00), +itemPrice (00:00:00), +. (00:00:00), +innerHTML (00:00:00), += (00:00:00), +` (00:00:00), +&lt; (00:00:00), +strong (00:00:00), +&gt; (00:00:00), +Price (00:00:00), +: (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +strong (00:00:00), +&gt; (00:00:00), +N (00:00:00), +/ (00:00:00), +A (00:00:00), +` (00:00:00), +; (00:00:00), +} (00:00:00), +} (00:00:00), +const (00:00:00), +marker (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +marker (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +if (00:00:00), +( (00:00:00), +marker (00:00:00), +) (00:00:00), +{ (00:00:00), +} (00:00:00)</t>
         </is>
       </c>
       <c r="P97" s="6" t="inlineStr">
